--- a/database/event/6972/event_6972_evp_summary.xlsx
+++ b/database/event/6972/event_6972_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -504,81 +492,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5574</v>
+        <v>5.923</v>
       </c>
       <c r="C2" t="n">
-        <v>6.045920000000001</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.523865479096971</v>
+        <v>1.9714</v>
       </c>
       <c r="E2" t="n">
-        <v>96.5778</v>
+        <v>5.923</v>
       </c>
       <c r="F2" t="n">
-        <v>22.68977827902711</v>
+        <v>3.6965</v>
       </c>
       <c r="G2" t="n">
-        <v>73.88804766872684</v>
+        <v>2.2265</v>
       </c>
       <c r="H2" t="n">
-        <v>22.68977827902711</v>
+        <v>3.6965</v>
       </c>
       <c r="I2" t="n">
-        <v>21.20192396564828</v>
+        <v>2.9961</v>
       </c>
       <c r="J2" t="n">
-        <v>73.88804766872684</v>
+        <v>2.2265</v>
       </c>
       <c r="K2" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="L2" t="n">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>95.09</v>
+        <v>5.2226</v>
       </c>
       <c r="N2" t="n">
-        <v>330</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1139</v>
+        <v>5.7099</v>
       </c>
       <c r="C3" t="n">
-        <v>5.691120000000001</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.272836700197408</v>
+        <v>1.8853</v>
       </c>
       <c r="E3" t="n">
-        <v>85.6551</v>
+        <v>5.7099</v>
       </c>
       <c r="F3" t="n">
-        <v>35.16309397112996</v>
+        <v>4.2158</v>
       </c>
       <c r="G3" t="n">
-        <v>50.49201932000776</v>
+        <v>1.4941</v>
       </c>
       <c r="H3" t="n">
-        <v>36.24393285600059</v>
+        <v>4.4007</v>
       </c>
       <c r="I3" t="n">
-        <v>31.49063018636117</v>
+        <v>3.5669</v>
       </c>
       <c r="J3" t="n">
-        <v>50.49201932000776</v>
+        <v>1.4941</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -587,7 +575,7 @@
         <v>168</v>
       </c>
       <c r="M3" t="n">
-        <v>81.98260000000001</v>
+        <v>5.061</v>
       </c>
       <c r="N3" t="n">
         <v>274</v>
@@ -596,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8929</v>
+        <v>5.7067</v>
       </c>
       <c r="C4" t="n">
-        <v>5.514320000000001</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.154478100665356</v>
+        <v>1.884</v>
       </c>
       <c r="E4" t="n">
-        <v>80.5051</v>
+        <v>5.7067</v>
       </c>
       <c r="F4" t="n">
-        <v>40.48342949946199</v>
+        <v>3.2326</v>
       </c>
       <c r="G4" t="n">
-        <v>40.02168872419634</v>
+        <v>2.4741</v>
       </c>
       <c r="H4" t="n">
-        <v>44.04028856530169</v>
+        <v>3.2326</v>
       </c>
       <c r="I4" t="n">
-        <v>38.26451301575392</v>
+        <v>2.6201</v>
       </c>
       <c r="J4" t="n">
-        <v>40.02168872419634</v>
+        <v>2.4741</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -633,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>78.28619999999999</v>
+        <v>5.0942</v>
       </c>
       <c r="N4" t="n">
         <v>274</v>
@@ -642,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0194</v>
+        <v>5.3527</v>
       </c>
       <c r="C5" t="n">
-        <v>4.81552</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.727089382264241</v>
+        <v>1.741</v>
       </c>
       <c r="E5" t="n">
-        <v>61.9087</v>
+        <v>5.3527</v>
       </c>
       <c r="F5" t="n">
-        <v>26.03301751104252</v>
+        <v>1.7331</v>
       </c>
       <c r="G5" t="n">
-        <v>35.87565059944923</v>
+        <v>3.6196</v>
       </c>
       <c r="H5" t="n">
-        <v>26.03301751104252</v>
+        <v>1.7331</v>
       </c>
       <c r="I5" t="n">
-        <v>28.80702757369459</v>
+        <v>1.7331</v>
       </c>
       <c r="J5" t="n">
-        <v>35.87565059944923</v>
+        <v>3.6196</v>
       </c>
       <c r="K5" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="M5" t="n">
-        <v>64.6827</v>
+        <v>5.3527</v>
       </c>
       <c r="N5" t="n">
-        <v>215</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3773</v>
+        <v>4.8476</v>
       </c>
       <c r="C6" t="n">
-        <v>4.30184</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.450327338298477</v>
+        <v>1.537</v>
       </c>
       <c r="E6" t="n">
-        <v>49.8663</v>
+        <v>4.8476</v>
       </c>
       <c r="F6" t="n">
-        <v>-26.95791788956309</v>
+        <v>4.2433</v>
       </c>
       <c r="G6" t="n">
-        <v>76.82417280046974</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-26.95791788956309</v>
+        <v>4.5112</v>
       </c>
       <c r="I6" t="n">
-        <v>-25.190185568936</v>
+        <v>3.6564</v>
       </c>
       <c r="J6" t="n">
-        <v>76.82417280046974</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L6" t="n">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>51.634</v>
+        <v>4.2607</v>
       </c>
       <c r="N6" t="n">
-        <v>330</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.1187</v>
+        <v>4.1196</v>
       </c>
       <c r="C7" t="n">
-        <v>4.094959999999999</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.346968614792905</v>
+        <v>1.2429</v>
       </c>
       <c r="E7" t="n">
-        <v>45.3689</v>
+        <v>4.1196</v>
       </c>
       <c r="F7" t="n">
-        <v>36.6964680947561</v>
+        <v>3.0336</v>
       </c>
       <c r="G7" t="n">
-        <v>8.672463272790154</v>
+        <v>1.086</v>
       </c>
       <c r="H7" t="n">
-        <v>38.3373564981839</v>
+        <v>3.0336</v>
       </c>
       <c r="I7" t="n">
-        <v>42.42248464962973</v>
+        <v>2.4588</v>
       </c>
       <c r="J7" t="n">
-        <v>8.672463272790154</v>
+        <v>1.086</v>
       </c>
       <c r="K7" t="n">
         <v>135</v>
@@ -771,7 +759,7 @@
         <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>51.0949</v>
+        <v>3.5448</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -780,44 +768,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9516</v>
+        <v>2.8977</v>
       </c>
       <c r="C8" t="n">
-        <v>3.96128</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.282490663330248</v>
+        <v>0.7492</v>
       </c>
       <c r="E8" t="n">
-        <v>42.5634</v>
+        <v>2.8977</v>
       </c>
       <c r="F8" t="n">
-        <v>45.98768757249605</v>
+        <v>1.4181</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.42430758276862</v>
+        <v>1.4796</v>
       </c>
       <c r="H8" t="n">
-        <v>53.87535024552668</v>
+        <v>1.4181</v>
       </c>
       <c r="I8" t="n">
-        <v>46.80973054119531</v>
+        <v>1.4247</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.42430758276862</v>
+        <v>1.4796</v>
       </c>
       <c r="K8" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L8" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="M8" t="n">
-        <v>43.3854</v>
+        <v>2.9043</v>
       </c>
       <c r="N8" t="n">
         <v>274</v>
@@ -826,182 +814,182 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.7937</v>
+        <v>2.7441</v>
       </c>
       <c r="C9" t="n">
-        <v>3.834960000000001</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.223203133919489</v>
+        <v>0.6872</v>
       </c>
       <c r="E9" t="n">
-        <v>39.9837</v>
+        <v>2.7441</v>
       </c>
       <c r="F9" t="n">
-        <v>3.577728625891865</v>
+        <v>2.8837</v>
       </c>
       <c r="G9" t="n">
-        <v>36.40594456402874</v>
+        <v>-0.1396</v>
       </c>
       <c r="H9" t="n">
-        <v>3.577728625891865</v>
+        <v>2.8837</v>
       </c>
       <c r="I9" t="n">
-        <v>3.049867025350443</v>
+        <v>2.3373</v>
       </c>
       <c r="J9" t="n">
-        <v>36.40594456402874</v>
+        <v>-0.1396</v>
       </c>
       <c r="K9" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M9" t="n">
-        <v>39.4558</v>
+        <v>2.1977</v>
       </c>
       <c r="N9" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3497</v>
+        <v>2.6051</v>
       </c>
       <c r="C10" t="n">
-        <v>3.479760000000001</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1.064637783671352</v>
+        <v>0.631</v>
       </c>
       <c r="E10" t="n">
-        <v>33.0842</v>
+        <v>2.6051</v>
       </c>
       <c r="F10" t="n">
-        <v>33.08421024527922</v>
+        <v>1.338</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.2671</v>
       </c>
       <c r="H10" t="n">
-        <v>33.58711207547807</v>
+        <v>1.338</v>
       </c>
       <c r="I10" t="n">
-        <v>32.76119948345812</v>
+        <v>1.338</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.2671</v>
       </c>
       <c r="K10" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>32.7612</v>
+        <v>2.6051</v>
       </c>
       <c r="N10" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2325</v>
+        <v>2.5654</v>
       </c>
       <c r="C11" t="n">
-        <v>3.386</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1.024695680186351</v>
+        <v>0.615</v>
       </c>
       <c r="E11" t="n">
-        <v>31.3463</v>
+        <v>2.5654</v>
       </c>
       <c r="F11" t="n">
-        <v>11.62344386422772</v>
+        <v>-0.9701</v>
       </c>
       <c r="G11" t="n">
-        <v>19.7228137798398</v>
+        <v>3.5355</v>
       </c>
       <c r="H11" t="n">
-        <v>11.62344386422772</v>
+        <v>-0.9701</v>
       </c>
       <c r="I11" t="n">
-        <v>12.38563690450495</v>
+        <v>-0.9701</v>
       </c>
       <c r="J11" t="n">
-        <v>19.7228137798398</v>
+        <v>3.5355</v>
       </c>
       <c r="K11" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="M11" t="n">
-        <v>32.1085</v>
+        <v>2.5654</v>
       </c>
       <c r="N11" t="n">
-        <v>274</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.1649</v>
+        <v>2.3489</v>
       </c>
       <c r="C12" t="n">
-        <v>3.33192</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.002005900669307</v>
+        <v>0.5275</v>
       </c>
       <c r="E12" t="n">
-        <v>30.359</v>
+        <v>2.3489</v>
       </c>
       <c r="F12" t="n">
-        <v>21.74113425372404</v>
+        <v>1.2827</v>
       </c>
       <c r="G12" t="n">
-        <v>8.617850365341805</v>
+        <v>1.0662</v>
       </c>
       <c r="H12" t="n">
-        <v>21.74113425372404</v>
+        <v>1.2827</v>
       </c>
       <c r="I12" t="n">
-        <v>18.88983795815367</v>
+        <v>1.2887</v>
       </c>
       <c r="J12" t="n">
-        <v>8.617850365341805</v>
+        <v>1.0662</v>
       </c>
       <c r="K12" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L12" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="M12" t="n">
-        <v>27.5077</v>
+        <v>2.3549</v>
       </c>
       <c r="N12" t="n">
         <v>274</v>
@@ -1010,44 +998,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9057</v>
+        <v>2.2734</v>
       </c>
       <c r="C13" t="n">
-        <v>3.12456</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9173575610323944</v>
+        <v>0.497</v>
       </c>
       <c r="E13" t="n">
-        <v>26.6758</v>
+        <v>2.2734</v>
       </c>
       <c r="F13" t="n">
-        <v>19.01036153155049</v>
+        <v>1.6001</v>
       </c>
       <c r="G13" t="n">
-        <v>7.665421923223395</v>
+        <v>0.6733</v>
       </c>
       <c r="H13" t="n">
-        <v>19.01036153155049</v>
+        <v>1.6001</v>
       </c>
       <c r="I13" t="n">
-        <v>20.25694261558659</v>
+        <v>1.2969</v>
       </c>
       <c r="J13" t="n">
-        <v>7.665421923223395</v>
+        <v>0.6733</v>
       </c>
       <c r="K13" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L13" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="M13" t="n">
-        <v>27.9224</v>
+        <v>1.9702</v>
       </c>
       <c r="N13" t="n">
         <v>274</v>
@@ -1056,458 +1044,458 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.7597</v>
+        <v>2.1138</v>
       </c>
       <c r="C14" t="n">
-        <v>3.00776</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8712553036633636</v>
+        <v>0.4326</v>
       </c>
       <c r="E14" t="n">
-        <v>24.6698</v>
+        <v>2.1138</v>
       </c>
       <c r="F14" t="n">
-        <v>24.66979150329024</v>
+        <v>0.3475</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.7663</v>
       </c>
       <c r="H14" t="n">
-        <v>24.66979150329024</v>
+        <v>0.3475</v>
       </c>
       <c r="I14" t="n">
-        <v>24.06315728599622</v>
+        <v>0.3475</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.7663</v>
       </c>
       <c r="K14" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M14" t="n">
-        <v>24.0632</v>
+        <v>2.1138</v>
       </c>
       <c r="N14" t="n">
-        <v>119</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5939</v>
+        <v>1.9756</v>
       </c>
       <c r="C15" t="n">
-        <v>2.87512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8202620934574517</v>
+        <v>0.3767</v>
       </c>
       <c r="E15" t="n">
-        <v>22.451</v>
+        <v>1.9756</v>
       </c>
       <c r="F15" t="n">
-        <v>8.309927840829182</v>
+        <v>1.9756</v>
       </c>
       <c r="G15" t="n">
-        <v>14.14105757592683</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>8.309927840829182</v>
+        <v>1.9756</v>
       </c>
       <c r="I15" t="n">
-        <v>7.083872913493728</v>
+        <v>1.9756</v>
       </c>
       <c r="J15" t="n">
-        <v>14.14105757592683</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>21.2249</v>
+        <v>1.9756</v>
       </c>
       <c r="N15" t="n">
-        <v>164</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.289</v>
+        <v>1.8091</v>
       </c>
       <c r="C16" t="n">
-        <v>2.6312</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7300875560128997</v>
+        <v>0.3095</v>
       </c>
       <c r="E16" t="n">
-        <v>18.5273</v>
+        <v>1.8091</v>
       </c>
       <c r="F16" t="n">
-        <v>18.52732946874933</v>
+        <v>1.5938</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.2153</v>
       </c>
       <c r="H16" t="n">
-        <v>18.52732946874933</v>
+        <v>1.5938</v>
       </c>
       <c r="I16" t="n">
-        <v>20.1978263880628</v>
+        <v>1.5938</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.2153</v>
       </c>
       <c r="K16" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>20.1978</v>
+        <v>1.8091</v>
       </c>
       <c r="N16" t="n">
-        <v>133</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.1399</v>
+        <v>1.6444</v>
       </c>
       <c r="C17" t="n">
-        <v>2.51192</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6876058360796894</v>
+        <v>0.2429</v>
       </c>
       <c r="E17" t="n">
-        <v>16.6789</v>
+        <v>1.6444</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.26993475900237</v>
+        <v>1.6444</v>
       </c>
       <c r="G17" t="n">
-        <v>32.94880835737935</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-16.26993475900237</v>
+        <v>1.6444</v>
       </c>
       <c r="I17" t="n">
-        <v>-17.33681572680581</v>
+        <v>1.6444</v>
       </c>
       <c r="J17" t="n">
-        <v>32.94880835737935</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="L17" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>15.612</v>
+        <v>1.6444</v>
       </c>
       <c r="N17" t="n">
-        <v>274</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8298</v>
+        <v>1.4792</v>
       </c>
       <c r="C18" t="n">
-        <v>2.26384</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6026037000373946</v>
+        <v>0.1762</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9803</v>
+        <v>1.4792</v>
       </c>
       <c r="F18" t="n">
-        <v>22.08845506994149</v>
+        <v>1.1441</v>
       </c>
       <c r="G18" t="n">
-        <v>-9.1081769523642</v>
+        <v>0.3351</v>
       </c>
       <c r="H18" t="n">
-        <v>22.08845506994149</v>
+        <v>1.1441</v>
       </c>
       <c r="I18" t="n">
-        <v>23.53687835321634</v>
+        <v>1.1441</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.1081769523642</v>
+        <v>0.3351</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L18" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>14.4287</v>
+        <v>1.4792</v>
       </c>
       <c r="N18" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3249</v>
+        <v>1.3097</v>
       </c>
       <c r="C19" t="n">
-        <v>1.85992</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.473269625969085</v>
+        <v>0.1077</v>
       </c>
       <c r="E19" t="n">
-        <v>7.3527</v>
+        <v>1.3097</v>
       </c>
       <c r="F19" t="n">
-        <v>24.21339198415695</v>
+        <v>-0.488</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.86067152730064</v>
+        <v>1.7977</v>
       </c>
       <c r="H19" t="n">
-        <v>24.21339198415695</v>
+        <v>-0.488</v>
       </c>
       <c r="I19" t="n">
-        <v>26.79350752345236</v>
+        <v>-0.4903</v>
       </c>
       <c r="J19" t="n">
-        <v>-16.86067152730064</v>
+        <v>1.7977</v>
       </c>
       <c r="K19" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="M19" t="n">
-        <v>9.9328</v>
+        <v>1.3074</v>
       </c>
       <c r="N19" t="n">
-        <v>215</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5899</v>
+        <v>1.2037</v>
       </c>
       <c r="C20" t="n">
-        <v>1.27192</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3033989253738827</v>
+        <v>0.0649</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0387</v>
+        <v>1.2037</v>
       </c>
       <c r="F20" t="n">
-        <v>7.017135110198993</v>
+        <v>1.2037</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.055793679736503</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7.017135110198993</v>
+        <v>1.2037</v>
       </c>
       <c r="I20" t="n">
-        <v>7.764862621941508</v>
+        <v>1.2037</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.055793679736503</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7091</v>
+        <v>1.2037</v>
       </c>
       <c r="N20" t="n">
-        <v>187</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9341</v>
+        <v>1.1176</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7472800000000001</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1684497888438259</v>
+        <v>0.0301</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9105</v>
+        <v>1.1176</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.7831331129284</v>
+        <v>1.3168</v>
       </c>
       <c r="G21" t="n">
-        <v>4.872595438381829</v>
+        <v>-0.1992</v>
       </c>
       <c r="H21" t="n">
-        <v>-10.7831331129284</v>
+        <v>1.3168</v>
       </c>
       <c r="I21" t="n">
-        <v>-11.93215549381421</v>
+        <v>1.3168</v>
       </c>
       <c r="J21" t="n">
-        <v>4.872595438381829</v>
+        <v>-0.1992</v>
       </c>
       <c r="K21" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L21" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.0596</v>
+        <v>1.1176</v>
       </c>
       <c r="N21" t="n">
-        <v>215</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0252</v>
+        <v>1.0694</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.02016</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.004215646850189714</v>
+        <v>0.0107</v>
       </c>
       <c r="E22" t="n">
-        <v>-13.4235</v>
+        <v>1.0694</v>
       </c>
       <c r="F22" t="n">
-        <v>3.679133949301569</v>
+        <v>1.455</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.10265458971661</v>
+        <v>-0.3856</v>
       </c>
       <c r="H22" t="n">
-        <v>3.679133949301569</v>
+        <v>1.455</v>
       </c>
       <c r="I22" t="n">
-        <v>3.136310907601337</v>
+        <v>1.4617</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.10265458971661</v>
+        <v>-0.3856</v>
       </c>
       <c r="K22" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L22" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="M22" t="n">
-        <v>-13.9663</v>
+        <v>1.0761</v>
       </c>
       <c r="N22" t="n">
-        <v>164</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4923</v>
+        <v>0.8567</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.39384</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08551443302447648</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-16.961</v>
+        <v>0.8567</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.958899154467161</v>
+        <v>0.837</v>
       </c>
       <c r="G23" t="n">
-        <v>-10.00207756809976</v>
+        <v>0.0197</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.958899154467161</v>
+        <v>0.837</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.415220410497795</v>
+        <v>0.6784</v>
       </c>
       <c r="J23" t="n">
-        <v>-10.00207756809976</v>
+        <v>0.0197</v>
       </c>
       <c r="K23" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L23" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="M23" t="n">
-        <v>-17.4173</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>274</v>
@@ -1516,461 +1504,461 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.545</v>
+        <v>0.7435</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.4360000000000001</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09508435965662687</v>
+        <v>-0.121</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.3774</v>
+        <v>0.7435</v>
       </c>
       <c r="F24" t="n">
-        <v>18.72944613682505</v>
+        <v>1.7435</v>
       </c>
       <c r="G24" t="n">
-        <v>-36.10682754098309</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>18.72944613682505</v>
+        <v>1.7435</v>
       </c>
       <c r="I24" t="n">
-        <v>16.27312533199554</v>
+        <v>1.7435</v>
       </c>
       <c r="J24" t="n">
-        <v>-36.10682754098309</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L24" t="n">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="M24" t="n">
-        <v>-19.8337</v>
+        <v>0.7435</v>
       </c>
       <c r="N24" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7311</v>
+        <v>0.2477</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.58488</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.129586965839946</v>
+        <v>-0.3213</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.8787</v>
+        <v>0.2477</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.404834575398497</v>
+        <v>-0.0248</v>
       </c>
       <c r="G25" t="n">
-        <v>-15.47381714086016</v>
+        <v>0.2725</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.404834575398497</v>
+        <v>-0.0248</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.181566734388759</v>
+        <v>-0.0248</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.47381714086016</v>
+        <v>0.2725</v>
       </c>
       <c r="K25" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L25" t="n">
-        <v>216</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.6554</v>
+        <v>0.2477</v>
       </c>
       <c r="N25" t="n">
-        <v>330</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9962</v>
+        <v>0.0693</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.79696</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1806214809000611</v>
+        <v>-0.3934</v>
       </c>
       <c r="E26" t="n">
-        <v>-21.0993</v>
+        <v>0.0693</v>
       </c>
       <c r="F26" t="n">
-        <v>-21.09925505112339</v>
+        <v>0.2747</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.2054</v>
       </c>
       <c r="H26" t="n">
-        <v>-21.09925505112339</v>
+        <v>0.2747</v>
       </c>
       <c r="I26" t="n">
-        <v>-20.58042091052199</v>
+        <v>0.2747</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.2054</v>
       </c>
       <c r="K26" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>-20.5804</v>
+        <v>0.0693</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.1493</v>
+        <v>-0.163</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.91944</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2111208047990656</v>
+        <v>-0.4872</v>
       </c>
       <c r="E27" t="n">
-        <v>-22.4263</v>
+        <v>-0.163</v>
       </c>
       <c r="F27" t="n">
-        <v>16.51855520562651</v>
+        <v>0.1194</v>
       </c>
       <c r="G27" t="n">
-        <v>-38.94489057252191</v>
+        <v>-0.2824</v>
       </c>
       <c r="H27" t="n">
-        <v>16.51855520562651</v>
+        <v>0.1194</v>
       </c>
       <c r="I27" t="n">
-        <v>14.08139132282916</v>
+        <v>0.12</v>
       </c>
       <c r="J27" t="n">
-        <v>-38.94489057252191</v>
+        <v>-0.2824</v>
       </c>
       <c r="K27" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L27" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="M27" t="n">
-        <v>-24.8635</v>
+        <v>-0.1624</v>
       </c>
       <c r="N27" t="n">
-        <v>164</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.4889</v>
+        <v>-0.2823</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.19112</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2816473795795135</v>
+        <v>-0.5354</v>
       </c>
       <c r="E28" t="n">
-        <v>-25.4951</v>
+        <v>-0.2823</v>
       </c>
       <c r="F28" t="n">
-        <v>-14.50265095149389</v>
+        <v>-0.2823</v>
       </c>
       <c r="G28" t="n">
-        <v>-10.99242224840673</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-14.50265095149389</v>
+        <v>-0.2823</v>
       </c>
       <c r="I28" t="n">
-        <v>-16.04801539714487</v>
+        <v>-0.2823</v>
       </c>
       <c r="J28" t="n">
-        <v>-10.99242224840673</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-27.0404</v>
+        <v>-0.2823</v>
       </c>
       <c r="N28" t="n">
-        <v>187</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.5991</v>
+        <v>-0.5817</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.27928</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3053990424151232</v>
+        <v>-0.6564</v>
       </c>
       <c r="E29" t="n">
-        <v>-26.5286</v>
+        <v>-0.5817</v>
       </c>
       <c r="F29" t="n">
-        <v>-26.52855067370849</v>
+        <v>-1.0443</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.4626</v>
       </c>
       <c r="H29" t="n">
-        <v>-26.52855067370849</v>
+        <v>-1.0443</v>
       </c>
       <c r="I29" t="n">
-        <v>-28.92046917707565</v>
+        <v>-0.8464</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.4626</v>
       </c>
       <c r="K29" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
-        <v>-28.9205</v>
+        <v>-0.3838</v>
       </c>
       <c r="N29" t="n">
-        <v>133</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.7983</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.43864</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3494869288852419</v>
+        <v>-0.6667</v>
       </c>
       <c r="E30" t="n">
-        <v>-28.4469</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-28.44689373246709</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-28.44689373246709</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-31.01177759359117</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-31.0118</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.933</v>
+        <v>-0.6357</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.5464</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3801190457213742</v>
+        <v>-0.6782</v>
       </c>
       <c r="E31" t="n">
-        <v>-29.7798</v>
+        <v>-0.6357</v>
       </c>
       <c r="F31" t="n">
-        <v>-29.77975210723869</v>
+        <v>-0.6357</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-29.77975210723869</v>
+        <v>-0.6357</v>
       </c>
       <c r="I31" t="n">
-        <v>-29.04746312099511</v>
+        <v>-0.6357</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-29.0475</v>
+        <v>-0.6357</v>
       </c>
       <c r="N31" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.1762</v>
+        <v>-0.7286</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.74096</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.437193274236177</v>
+        <v>-0.7157</v>
       </c>
       <c r="E32" t="n">
-        <v>-32.2632</v>
+        <v>-0.7286</v>
       </c>
       <c r="F32" t="n">
-        <v>-10.53372008151328</v>
+        <v>-0.7286</v>
       </c>
       <c r="G32" t="n">
-        <v>-21.72943413164359</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-10.53372008151328</v>
+        <v>-0.7286</v>
       </c>
       <c r="I32" t="n">
-        <v>-11.65616566396961</v>
+        <v>-0.7286</v>
       </c>
       <c r="J32" t="n">
-        <v>-21.72943413164359</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L32" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-33.3856</v>
+        <v>-0.7286</v>
       </c>
       <c r="N32" t="n">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.4962</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.99696</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5159373646043852</v>
+        <v>-0.8146</v>
       </c>
       <c r="E33" t="n">
-        <v>-35.6895</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-35.68945089622637</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.9023</v>
       </c>
       <c r="H33" t="n">
-        <v>-35.68945089622637</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-34.81184144795851</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.9023</v>
       </c>
       <c r="K33" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M33" t="n">
-        <v>-34.8118</v>
+        <v>-0.9732999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34">
@@ -1980,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.6822</v>
+        <v>-1.204</v>
       </c>
       <c r="C34" t="n">
-        <v>-2.14576</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5636616484700536</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-37.766</v>
+        <v>-1.204</v>
       </c>
       <c r="F34" t="n">
-        <v>-37.76602013140576</v>
+        <v>-1.204</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-37.76602013140576</v>
+        <v>-1.204</v>
       </c>
       <c r="I34" t="n">
-        <v>-41.1711530940735</v>
+        <v>-1.204</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2013,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-41.1712</v>
+        <v>-1.204</v>
       </c>
       <c r="N34" t="n">
         <v>133</v>
@@ -2022,185 +2010,185 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.79</v>
+        <v>-1.233</v>
       </c>
       <c r="C35" t="n">
-        <v>-3.032</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8807392665102102</v>
+        <v>-0.9195</v>
       </c>
       <c r="E35" t="n">
-        <v>-51.5626</v>
+        <v>-1.233</v>
       </c>
       <c r="F35" t="n">
-        <v>-15.84136987158222</v>
+        <v>-1.233</v>
       </c>
       <c r="G35" t="n">
-        <v>-35.7212664361809</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-15.84136987158222</v>
+        <v>-1.233</v>
       </c>
       <c r="I35" t="n">
-        <v>-13.50411857905369</v>
+        <v>-1.233</v>
       </c>
       <c r="J35" t="n">
-        <v>-35.7212664361809</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="L35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-49.2254</v>
+        <v>-1.233</v>
       </c>
       <c r="N35" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Altekz</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-4.5709</v>
+        <v>-1.6041</v>
       </c>
       <c r="C36" t="n">
-        <v>-3.65672</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.14216260183525</v>
+        <v>-1.0694</v>
       </c>
       <c r="E36" t="n">
-        <v>-62.9376</v>
+        <v>-1.6041</v>
       </c>
       <c r="F36" t="n">
-        <v>-62.93763476812732</v>
+        <v>-0.6041</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>-62.93763476812732</v>
+        <v>-0.6041</v>
       </c>
       <c r="I36" t="n">
-        <v>-68.61233954230273</v>
+        <v>-0.6041</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K36" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M36" t="n">
-        <v>-68.6123</v>
+        <v>-1.6041</v>
       </c>
       <c r="N36" t="n">
-        <v>133</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Altekz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-4.8599</v>
+        <v>-1.7327</v>
       </c>
       <c r="C37" t="n">
-        <v>-3.88792</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.247884001448089</v>
+        <v>-1.1213</v>
       </c>
       <c r="E37" t="n">
-        <v>-67.5378</v>
+        <v>-1.7327</v>
       </c>
       <c r="F37" t="n">
-        <v>-44.45381968999857</v>
+        <v>-1.7327</v>
       </c>
       <c r="G37" t="n">
-        <v>-23.08394289888498</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-44.45381968999857</v>
+        <v>-1.7327</v>
       </c>
       <c r="I37" t="n">
-        <v>-49.19070211598202</v>
+        <v>-1.7327</v>
       </c>
       <c r="J37" t="n">
-        <v>-23.08394289888498</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L37" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-72.27460000000001</v>
+        <v>-1.7327</v>
       </c>
       <c r="N37" t="n">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4.8716</v>
+        <v>-2.0705</v>
       </c>
       <c r="C38" t="n">
-        <v>-3.89728</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.252249698718884</v>
+        <v>-1.2578</v>
       </c>
       <c r="E38" t="n">
-        <v>-67.7277</v>
+        <v>-2.0705</v>
       </c>
       <c r="F38" t="n">
-        <v>-7.698665021685787</v>
+        <v>-1.8282</v>
       </c>
       <c r="G38" t="n">
-        <v>-60.02905688996429</v>
+        <v>-0.2423</v>
       </c>
       <c r="H38" t="n">
-        <v>-7.698665021685787</v>
+        <v>-1.8282</v>
       </c>
       <c r="I38" t="n">
-        <v>-8.519014573176896</v>
+        <v>-1.8282</v>
       </c>
       <c r="J38" t="n">
-        <v>-60.02905688996429</v>
+        <v>-0.2423</v>
       </c>
       <c r="K38" t="n">
         <v>135</v>
       </c>
       <c r="L38" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="M38" t="n">
-        <v>-68.54810000000001</v>
+        <v>-2.0705</v>
       </c>
       <c r="N38" t="n">
-        <v>215</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39">
@@ -2210,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.928</v>
+        <v>-2.123</v>
       </c>
       <c r="C39" t="n">
-        <v>-3.9424</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.273531368556055</v>
+        <v>-1.279</v>
       </c>
       <c r="E39" t="n">
-        <v>-68.6537</v>
+        <v>-2.123</v>
       </c>
       <c r="F39" t="n">
-        <v>-41.2358265124092</v>
+        <v>-1.3253</v>
       </c>
       <c r="G39" t="n">
-        <v>-27.41789904513119</v>
+        <v>-0.7977</v>
       </c>
       <c r="H39" t="n">
-        <v>-41.2358265124092</v>
+        <v>-1.3253</v>
       </c>
       <c r="I39" t="n">
-        <v>-38.53183788864467</v>
+        <v>-1.3253</v>
       </c>
       <c r="J39" t="n">
-        <v>-27.41789904513119</v>
+        <v>-0.7977</v>
       </c>
       <c r="K39" t="n">
         <v>114</v>
@@ -2243,7 +2231,7 @@
         <v>216</v>
       </c>
       <c r="M39" t="n">
-        <v>-65.94970000000001</v>
+        <v>-2.123</v>
       </c>
       <c r="N39" t="n">
         <v>330</v>
@@ -2252,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.1961</v>
+        <v>-2.9518</v>
       </c>
       <c r="C40" t="n">
-        <v>-4.15688</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.377428301210182</v>
+        <v>-1.6138</v>
       </c>
       <c r="E40" t="n">
-        <v>-73.17449999999999</v>
+        <v>-2.9518</v>
       </c>
       <c r="F40" t="n">
-        <v>-24.76354141528847</v>
+        <v>-1.9518</v>
       </c>
       <c r="G40" t="n">
-        <v>-48.41092613151562</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-24.76354141528847</v>
+        <v>-1.9518</v>
       </c>
       <c r="I40" t="n">
-        <v>-27.40227943495036</v>
+        <v>-1.582</v>
       </c>
       <c r="J40" t="n">
-        <v>-48.41092613151562</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
         <v>135</v>
       </c>
       <c r="L40" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>-75.81319999999999</v>
+        <v>-2.582</v>
       </c>
       <c r="N40" t="n">
-        <v>187</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-8.986000000000001</v>
+        <v>-4.7605</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.188800000000001</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.471274435562019</v>
+        <v>-2.3445</v>
       </c>
       <c r="E41" t="n">
-        <v>-164.2815</v>
+        <v>-4.7605</v>
       </c>
       <c r="F41" t="n">
-        <v>-53.83763768420711</v>
+        <v>-2.2999</v>
       </c>
       <c r="G41" t="n">
-        <v>-110.4438327048579</v>
+        <v>-2.4606</v>
       </c>
       <c r="H41" t="n">
-        <v>-53.83763768420711</v>
+        <v>-2.2999</v>
       </c>
       <c r="I41" t="n">
-        <v>-50.30730078688205</v>
+        <v>-2.2999</v>
       </c>
       <c r="J41" t="n">
-        <v>-110.4438327048579</v>
+        <v>-2.4606</v>
       </c>
       <c r="K41" t="n">
         <v>114</v>
@@ -2335,7 +2323,7 @@
         <v>216</v>
       </c>
       <c r="M41" t="n">
-        <v>-160.7511</v>
+        <v>-4.7605</v>
       </c>
       <c r="N41" t="n">
         <v>330</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.58405275923697</v>
+        <v>1.0031</v>
       </c>
       <c r="J2" t="n">
-        <v>39.60131898092425</v>
+        <v>25.0775</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>1.094112613979648</v>
+        <v>0.6249</v>
       </c>
       <c r="J3" t="n">
-        <v>27.3528153494912</v>
+        <v>15.6225</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9716953788353356</v>
+        <v>0.5592</v>
       </c>
       <c r="J4" t="n">
-        <v>24.29238447088339</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>1.19</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8370465376081878</v>
+        <v>0.4727</v>
       </c>
       <c r="J5" t="n">
-        <v>20.9261634402047</v>
+        <v>11.8175</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4519510446945659</v>
+        <v>0.1365</v>
       </c>
       <c r="J6" t="n">
-        <v>11.29877611736415</v>
+        <v>3.4125</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>0.99</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2785817686818791</v>
+        <v>0.0629</v>
       </c>
       <c r="J7" t="n">
-        <v>-6.964544217046977</v>
+        <v>1.5725</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4983568742783412</v>
+        <v>-0.1184</v>
       </c>
       <c r="J8" t="n">
-        <v>-12.45892185695853</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8663333145712279</v>
+        <v>-0.32</v>
       </c>
       <c r="J9" t="n">
-        <v>-21.6583328642807</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.237349664910704</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-30.93374162276761</v>
+        <v>-13.1175</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.302456733040901</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-32.56141832602253</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01991855481889215</v>
+        <v>0.2989</v>
       </c>
       <c r="J12" t="n">
-        <v>0.517882425291196</v>
+        <v>7.7714</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1388125071009723</v>
+        <v>0.2155</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.60912518462528</v>
+        <v>5.603</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4159749231228301</v>
+        <v>-0.0009</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.81534800119358</v>
+        <v>-0.0234</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7516723718780542</v>
+        <v>-0.1876</v>
       </c>
       <c r="J15" t="n">
-        <v>-19.54348166882941</v>
+        <v>-4.8776</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.457847787257321</v>
+        <v>-0.6369</v>
       </c>
       <c r="J16" t="n">
-        <v>-37.90404246869035</v>
+        <v>-16.5594</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>1.231507564782341</v>
+        <v>0.5083</v>
       </c>
       <c r="J17" t="n">
-        <v>32.01919668434088</v>
+        <v>13.2158</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>1.181713535454303</v>
+        <v>0.4822</v>
       </c>
       <c r="J18" t="n">
-        <v>30.72455192181188</v>
+        <v>12.5372</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.156054556145277</v>
+        <v>0.4689</v>
       </c>
       <c r="J19" t="n">
-        <v>30.0574184597772</v>
+        <v>12.1914</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.118857203125855</v>
+        <v>-0.0275</v>
       </c>
       <c r="J20" t="n">
-        <v>3.09028728127223</v>
+        <v>-0.715</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.84</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4374355519954746</v>
+        <v>-0.3571</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.37332435188234</v>
+        <v>-9.284599999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>1.484057464846565</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>37.10143662116413</v>
+        <v>24.3825</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.28</v>
       </c>
       <c r="I23" t="n">
-        <v>1.153426791540123</v>
+        <v>0.721</v>
       </c>
       <c r="J23" t="n">
-        <v>28.83566978850308</v>
+        <v>18.025</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9808587717059134</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>24.52146929264784</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7359225398526542</v>
+        <v>0.4648</v>
       </c>
       <c r="J25" t="n">
-        <v>18.39806349631635</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>1.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3794159361958668</v>
+        <v>0.1616</v>
       </c>
       <c r="J26" t="n">
-        <v>9.485398404896669</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7822100214673927</v>
+        <v>0.7187</v>
       </c>
       <c r="J27" t="n">
-        <v>19.55525053668482</v>
+        <v>17.9675</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1492408663531221</v>
+        <v>0.2623</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.731021658828051</v>
+        <v>6.5575</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.203584860903377</v>
+        <v>-0.4483</v>
       </c>
       <c r="J29" t="n">
-        <v>-30.08962152258443</v>
+        <v>-11.2075</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.447693459051044</v>
+        <v>-0.61</v>
       </c>
       <c r="J30" t="n">
-        <v>-36.19233647627611</v>
+        <v>-15.25</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.48</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.66797563529408</v>
+        <v>-0.7698</v>
       </c>
       <c r="J31" t="n">
-        <v>-41.69939088235201</v>
+        <v>-19.245</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>1.034234265232931</v>
+        <v>0.5658</v>
       </c>
       <c r="J32" t="n">
-        <v>27.92432516128913</v>
+        <v>15.2766</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9576048904612009</v>
+        <v>0.5152</v>
       </c>
       <c r="J33" t="n">
-        <v>25.85533204245242</v>
+        <v>13.9104</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8089256705554215</v>
+        <v>0.4219</v>
       </c>
       <c r="J34" t="n">
-        <v>21.84099310499638</v>
+        <v>11.3913</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07491587025375743</v>
+        <v>0.0249</v>
       </c>
       <c r="J35" t="n">
-        <v>2.022728496851451</v>
+        <v>0.6723</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5632177423841906</v>
+        <v>-0.5538</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.20687904437315</v>
+        <v>-14.9526</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4608580558769549</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
-        <v>12.44316750867778</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.04759844470273202</v>
+        <v>0.2317</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.285158006973764</v>
+        <v>6.2559</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1643881351982153</v>
+        <v>0.1398</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.438479650351813</v>
+        <v>3.7746</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.83</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6767784884547557</v>
+        <v>-0.3369</v>
       </c>
       <c r="J40" t="n">
-        <v>-18.2730191882784</v>
+        <v>-9.096299999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9742042175335781</v>
+        <v>-0.6322</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.30351387340661</v>
+        <v>-17.0694</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.09055393867937733</v>
+        <v>0.4441</v>
       </c>
       <c r="J42" t="n">
-        <v>2.263848466984433</v>
+        <v>11.1025</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2136737338088478</v>
+        <v>0.1916</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.341843345221196</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7362034350609324</v>
+        <v>-0.3282</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.40508587652331</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8483189880487479</v>
+        <v>-0.4324</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.2079747012187</v>
+        <v>-10.81</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9191670261679276</v>
+        <v>-0.5017</v>
       </c>
       <c r="J46" t="n">
-        <v>-22.97917565419819</v>
+        <v>-12.5425</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9402478069545592</v>
+        <v>1.1727</v>
       </c>
       <c r="J47" t="n">
-        <v>23.50619517386398</v>
+        <v>29.3175</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9000955218242496</v>
+        <v>1.1113</v>
       </c>
       <c r="J48" t="n">
-        <v>22.50238804560624</v>
+        <v>27.7825</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5917065154352108</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>14.79266288588027</v>
+        <v>17.5775</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1606539554485861</v>
+        <v>0.1522</v>
       </c>
       <c r="J50" t="n">
-        <v>4.016348886214653</v>
+        <v>3.805</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>0.005289095412338119</v>
+        <v>-0.2018</v>
       </c>
       <c r="J51" t="n">
-        <v>0.132227385308453</v>
+        <v>-5.045</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.73</v>
       </c>
       <c r="I52" t="n">
-        <v>1.158562263249149</v>
+        <v>0.9923</v>
       </c>
       <c r="J52" t="n">
-        <v>32.43974337097616</v>
+        <v>27.7844</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08302052418095049</v>
+        <v>0.2679</v>
       </c>
       <c r="J53" t="n">
-        <v>2.324574677066614</v>
+        <v>7.5012</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.6324959420602181</v>
+        <v>-0.2948</v>
       </c>
       <c r="J54" t="n">
-        <v>-17.70988637768611</v>
+        <v>-8.2544</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6945256155945252</v>
+        <v>-0.355</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.44671723664671</v>
+        <v>-9.94</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.77</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7801072211211768</v>
+        <v>-0.4394</v>
       </c>
       <c r="J56" t="n">
-        <v>-21.84300219139295</v>
+        <v>-12.3032</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8947465927463943</v>
+        <v>1.2543</v>
       </c>
       <c r="J57" t="n">
-        <v>25.05290459689904</v>
+        <v>35.1204</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.33</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6814193539789674</v>
+        <v>0.9171</v>
       </c>
       <c r="J58" t="n">
-        <v>19.07974191141109</v>
+        <v>25.6788</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.02668108358943784</v>
+        <v>0.1011</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.7470703405042595</v>
+        <v>2.8308</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.87</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3658155209992779</v>
+        <v>-0.5242</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.24283458797978</v>
+        <v>-14.6776</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5256786398832087</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.71900191672984</v>
+        <v>-22.3132</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4504503797128789</v>
+        <v>0.9727</v>
       </c>
       <c r="J62" t="n">
-        <v>13.06306101167349</v>
+        <v>28.2083</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3248118970215853</v>
+        <v>0.6445</v>
       </c>
       <c r="J63" t="n">
-        <v>9.419545013625974</v>
+        <v>18.6905</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.06</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1478588509151795</v>
+        <v>0.239</v>
       </c>
       <c r="J64" t="n">
-        <v>4.287906676540206</v>
+        <v>6.931</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5999633698140929</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-17.39893772460869</v>
+        <v>-19.778</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6230137906697248</v>
+        <v>-0.7065</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.06739992942202</v>
+        <v>-20.4885</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.43</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8105565907479588</v>
+        <v>0.6833</v>
       </c>
       <c r="J67" t="n">
-        <v>23.50614113169081</v>
+        <v>19.8157</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4436458533783619</v>
+        <v>0.3993</v>
       </c>
       <c r="J68" t="n">
-        <v>12.8657297479725</v>
+        <v>11.5797</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5361074501515797</v>
+        <v>-0.3233</v>
       </c>
       <c r="J69" t="n">
-        <v>-15.54711605439581</v>
+        <v>-9.3757</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6341880932016883</v>
+        <v>-0.4112</v>
       </c>
       <c r="J70" t="n">
-        <v>-18.39145470284896</v>
+        <v>-11.9248</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7222060653541528</v>
+        <v>-0.4932</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.94397589527043</v>
+        <v>-14.3028</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.05879253654793886</v>
+        <v>0.3831</v>
       </c>
       <c r="J72" t="n">
-        <v>1.587398486794349</v>
+        <v>10.3437</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2670286099620557</v>
+        <v>0.1274</v>
       </c>
       <c r="J73" t="n">
-        <v>-7.209772468975504</v>
+        <v>3.4398</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.9952984829715905</v>
+        <v>-0.347</v>
       </c>
       <c r="J74" t="n">
-        <v>-26.87305904023295</v>
+        <v>-9.369</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.019777932185194</v>
+        <v>-0.3622</v>
       </c>
       <c r="J75" t="n">
-        <v>-27.53400416900023</v>
+        <v>-9.779400000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.067062678268719</v>
+        <v>-0.3919</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.81069231325542</v>
+        <v>-10.5813</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>1.420075883705319</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>38.34204886004361</v>
+        <v>25.8714</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6852857853069022</v>
+        <v>0.407</v>
       </c>
       <c r="J78" t="n">
-        <v>18.50271620328636</v>
+        <v>10.989</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4213310513279055</v>
+        <v>0.2742</v>
       </c>
       <c r="J79" t="n">
-        <v>11.37593838585345</v>
+        <v>7.4034</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1554894513062455</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>4.198215185268629</v>
+        <v>2.6244</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4057110992452488</v>
+        <v>-0.4083</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.95419967962172</v>
+        <v>-11.0241</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.41</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4659430175356667</v>
+        <v>1.0998</v>
       </c>
       <c r="J82" t="n">
-        <v>16.773948631284</v>
+        <v>39.5928</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3397790249352902</v>
+        <v>0.7664</v>
       </c>
       <c r="J83" t="n">
-        <v>12.23204489767045</v>
+        <v>27.5904</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.08356136108465653</v>
+        <v>0.2218</v>
       </c>
       <c r="J84" t="n">
-        <v>3.008208999047635</v>
+        <v>7.9848</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.605911256953292</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>-21.81280525031851</v>
+        <v>-21.4668</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6534555722049141</v>
+        <v>-0.647</v>
       </c>
       <c r="J86" t="n">
-        <v>-23.52440059937691</v>
+        <v>-23.292</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5491872613530736</v>
+        <v>0.4699</v>
       </c>
       <c r="J87" t="n">
-        <v>19.77074140871065</v>
+        <v>16.9164</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.08663028681686279</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.11869032540706</v>
+        <v>2.6064</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3961566360361241</v>
+        <v>-0.2078</v>
       </c>
       <c r="J89" t="n">
-        <v>-14.26163889730047</v>
+        <v>-7.4808</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.89</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4356130000233271</v>
+        <v>-0.2423</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.68206800083978</v>
+        <v>-8.722799999999999</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4545057283814914</v>
+        <v>-0.2589</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.36220622173369</v>
+        <v>-9.320399999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6114957043836855</v>
+        <v>1.0029</v>
       </c>
       <c r="J92" t="n">
-        <v>22.01384535781268</v>
+        <v>36.1044</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.07419255250869977</v>
+        <v>0.3199</v>
       </c>
       <c r="J93" t="n">
-        <v>2.670931890313192</v>
+        <v>11.5164</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.04569841504923088</v>
+        <v>0.2864</v>
       </c>
       <c r="J94" t="n">
-        <v>1.645142941772312</v>
+        <v>10.3104</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1711802822020997</v>
+        <v>-0.1186</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.162490159275591</v>
+        <v>-4.2696</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4365415454197772</v>
+        <v>-0.7147</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.71549563511198</v>
+        <v>-25.7292</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7940888459385909</v>
+        <v>0.7587</v>
       </c>
       <c r="J97" t="n">
-        <v>28.58719845378927</v>
+        <v>27.3132</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.51</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7683730299323752</v>
+        <v>0.736</v>
       </c>
       <c r="J98" t="n">
-        <v>27.66142907756551</v>
+        <v>26.496</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2784758050457563</v>
+        <v>-0.0527</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.02512898164722</v>
+        <v>-1.8972</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4873084436977599</v>
+        <v>-0.3365</v>
       </c>
       <c r="J100" t="n">
-        <v>-17.54310397311936</v>
+        <v>-12.114</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.73</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6166915259595062</v>
+        <v>-0.5014</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.20089493454222</v>
+        <v>-18.0504</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.44</v>
       </c>
       <c r="I102" t="n">
-        <v>0.978954458640136</v>
+        <v>1.1264</v>
       </c>
       <c r="J102" t="n">
-        <v>23.49490700736326</v>
+        <v>27.0336</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6616015367695661</v>
+        <v>0.6016</v>
       </c>
       <c r="J103" t="n">
-        <v>15.87843688246959</v>
+        <v>14.4384</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4637467897365316</v>
+        <v>0.3572</v>
       </c>
       <c r="J104" t="n">
-        <v>11.12992295367676</v>
+        <v>8.572800000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2558814698624122</v>
+        <v>-0.0008</v>
       </c>
       <c r="J105" t="n">
-        <v>6.141155276697893</v>
+        <v>-0.0192</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1241543803376854</v>
+        <v>-0.342</v>
       </c>
       <c r="J106" t="n">
-        <v>2.979705128104451</v>
+        <v>-8.208</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3257810879266445</v>
+        <v>0.5084</v>
       </c>
       <c r="J107" t="n">
-        <v>7.818746110239468</v>
+        <v>12.2016</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>0.89</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2948969003362245</v>
+        <v>-0.1465</v>
       </c>
       <c r="J108" t="n">
-        <v>-7.077525608069388</v>
+        <v>-3.516</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5633488125682782</v>
+        <v>-0.4009</v>
       </c>
       <c r="J109" t="n">
-        <v>-13.52037150163868</v>
+        <v>-9.621600000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5633488125682782</v>
+        <v>-0.4009</v>
       </c>
       <c r="J110" t="n">
-        <v>-13.52037150163868</v>
+        <v>-9.621600000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.89174110830844</v>
+        <v>-0.7977</v>
       </c>
       <c r="J111" t="n">
-        <v>-21.40178659940256</v>
+        <v>-19.1448</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3652197914901422</v>
+        <v>0.9659</v>
       </c>
       <c r="J112" t="n">
-        <v>10.95659374470426</v>
+        <v>28.977</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.131814399255044</v>
+        <v>-0.1112</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.954431977651319</v>
+        <v>-3.336</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.98</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1585739210016632</v>
+        <v>-0.1554</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.757217630049897</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1840967965899973</v>
+        <v>-0.1948</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.522903897699919</v>
+        <v>-5.844</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1840967965899973</v>
+        <v>-0.1948</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.522903897699919</v>
+        <v>-5.844</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2468935812175031</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>7.406807436525093</v>
+        <v>15.228</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1386352021444415</v>
+        <v>0.326</v>
       </c>
       <c r="J118" t="n">
-        <v>4.159056064333246</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2935625875139805</v>
+        <v>-0.0593</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.806877625419416</v>
+        <v>-1.779</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4260984012169323</v>
+        <v>-0.1684</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.78295203650797</v>
+        <v>-5.052</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7273048179758012</v>
+        <v>-0.4061</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.81914453927403</v>
+        <v>-12.183</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5662610497168201</v>
+        <v>1.0968</v>
       </c>
       <c r="J122" t="n">
-        <v>12.45774309377004</v>
+        <v>24.1296</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.42</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5523845035401739</v>
+        <v>1.0549</v>
       </c>
       <c r="J123" t="n">
-        <v>12.15245907788383</v>
+        <v>23.2078</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2316245137890992</v>
+        <v>0.262</v>
       </c>
       <c r="J124" t="n">
-        <v>5.095739303360182</v>
+        <v>5.764</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2220639799416684</v>
+        <v>0.2333</v>
       </c>
       <c r="J125" t="n">
-        <v>4.885407558716704</v>
+        <v>5.1326</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>0.09709650087438824</v>
+        <v>-0.2977</v>
       </c>
       <c r="J126" t="n">
-        <v>2.136123019236541</v>
+        <v>-6.5494</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.09934293740851415</v>
+        <v>0.3318</v>
       </c>
       <c r="J127" t="n">
-        <v>-2.185544622987311</v>
+        <v>7.2996</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.4682268573807731</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>-10.30099086237701</v>
+        <v>-1.6258</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.5097658974577158</v>
+        <v>-0.1107</v>
       </c>
       <c r="J129" t="n">
-        <v>-11.21484974406975</v>
+        <v>-2.4354</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-1.20871734510189</v>
+        <v>-0.6116</v>
       </c>
       <c r="J130" t="n">
-        <v>-26.59178159224158</v>
+        <v>-13.4552</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.32437461673494</v>
+        <v>-0.713</v>
       </c>
       <c r="J131" t="n">
-        <v>-29.13624156816868</v>
+        <v>-15.686</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3336486185524336</v>
+        <v>0.6076</v>
       </c>
       <c r="J132" t="n">
-        <v>11.67770164933518</v>
+        <v>21.266</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3336486185524336</v>
+        <v>0.6076</v>
       </c>
       <c r="J133" t="n">
-        <v>11.67770164933518</v>
+        <v>21.266</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3336486185524336</v>
+        <v>0.6076</v>
       </c>
       <c r="J134" t="n">
-        <v>11.67770164933518</v>
+        <v>21.266</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.28238925709871</v>
+        <v>0.5423</v>
       </c>
       <c r="J135" t="n">
-        <v>9.883623998454851</v>
+        <v>18.9805</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1889872587679823</v>
+        <v>0.3982</v>
       </c>
       <c r="J136" t="n">
-        <v>6.61455405687938</v>
+        <v>13.937</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>0.98</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.08454531459755091</v>
+        <v>0.0046</v>
       </c>
       <c r="J137" t="n">
-        <v>-2.959086010914282</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>0.91</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1654196324532802</v>
+        <v>-0.138</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.789687135864808</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1929834732847679</v>
+        <v>-0.1765</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.754421564966878</v>
+        <v>-6.1775</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2669103740789601</v>
+        <v>-0.2616</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.341863092763605</v>
+        <v>-9.156000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3962055113089177</v>
+        <v>-0.4501</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.86719289581212</v>
+        <v>-15.7535</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6154127094630771</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>16.00073044604001</v>
+        <v>25.5684</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4330821928133342</v>
+        <v>0.6339</v>
       </c>
       <c r="J143" t="n">
-        <v>11.26013701314669</v>
+        <v>16.4814</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3532988341145055</v>
+        <v>0.4999</v>
       </c>
       <c r="J144" t="n">
-        <v>9.185769686977144</v>
+        <v>12.9974</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.02188698417492458</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>0.5690615885480391</v>
+        <v>-2.5506</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.08983369864758672</v>
+        <v>-0.369</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.335676164837255</v>
+        <v>-9.593999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.142625114860708</v>
+        <v>0.3906</v>
       </c>
       <c r="J147" t="n">
-        <v>3.708252986378408</v>
+        <v>10.1556</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.09550923630315358</v>
+        <v>0.1637</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.483240143881993</v>
+        <v>4.2562</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.287498445162599</v>
+        <v>-0.147</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.474959574227575</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3693565679953163</v>
+        <v>-0.2716</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.603270767878223</v>
+        <v>-7.0616</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4092369100419069</v>
+        <v>-0.3343</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.64015966108958</v>
+        <v>-8.691800000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1985520758203759</v>
+        <v>0.5819</v>
       </c>
       <c r="J152" t="n">
-        <v>5.956562274611276</v>
+        <v>17.457</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.189230209664408</v>
+        <v>0.5555</v>
       </c>
       <c r="J153" t="n">
-        <v>5.67690628993224</v>
+        <v>16.665</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1245918547130434</v>
+        <v>0.3842</v>
       </c>
       <c r="J154" t="n">
-        <v>3.737755641391301</v>
+        <v>11.526</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.05</v>
       </c>
       <c r="I155" t="n">
-        <v>0.02024015761347741</v>
+        <v>0.1366</v>
       </c>
       <c r="J155" t="n">
-        <v>0.6072047284043224</v>
+        <v>4.098</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1677611938106246</v>
+        <v>-0.2896</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.032835814318738</v>
+        <v>-8.688000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1848135867827816</v>
+        <v>0.4672</v>
       </c>
       <c r="J157" t="n">
-        <v>5.54440760348345</v>
+        <v>14.016</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1414607278281267</v>
+        <v>0.3836</v>
       </c>
       <c r="J158" t="n">
-        <v>4.243821834843801</v>
+        <v>11.508</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.009448445386648741</v>
+        <v>0.1553</v>
       </c>
       <c r="J159" t="n">
-        <v>-0.2834533615994622</v>
+        <v>4.659</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3208801488291143</v>
+        <v>-0.1927</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.626404464873428</v>
+        <v>-5.781</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7376267605263332</v>
+        <v>-0.6938</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.12880281579</v>
+        <v>-20.814</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.224665003469916</v>
+        <v>0.4831</v>
       </c>
       <c r="J162" t="n">
-        <v>6.739950104097479</v>
+        <v>14.493</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.06418289662929964</v>
+        <v>0.2284</v>
       </c>
       <c r="J163" t="n">
-        <v>1.925486898878989</v>
+        <v>6.852</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.08176879635324126</v>
+        <v>-0.0067</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.453063890597238</v>
+        <v>-0.201</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3153151527614408</v>
+        <v>-0.263</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.459454582843225</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6408525794119021</v>
+        <v>-0.6874</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.22557738235706</v>
+        <v>-20.622</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.371222051888218</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>11.13666155664654</v>
+        <v>21.336</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.179076846727407</v>
+        <v>0.3061</v>
       </c>
       <c r="J168" t="n">
-        <v>5.372305401822211</v>
+        <v>9.183</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1523616150670221</v>
+        <v>0.2581</v>
       </c>
       <c r="J169" t="n">
-        <v>4.570848452010663</v>
+        <v>7.743</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.152680981734626</v>
+        <v>-0.1835</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.580429452038779</v>
+        <v>-5.505</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4504796058099613</v>
+        <v>-0.4966</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.51438817429884</v>
+        <v>-14.898</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2371638900358858</v>
+        <v>0.6741</v>
       </c>
       <c r="J172" t="n">
-        <v>7.114916701076575</v>
+        <v>20.223</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.193928858882129</v>
+        <v>0.5457</v>
       </c>
       <c r="J173" t="n">
-        <v>5.817865766463869</v>
+        <v>16.371</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.05343459153491494</v>
+        <v>0.1933</v>
       </c>
       <c r="J174" t="n">
-        <v>1.603037746047448</v>
+        <v>5.799</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1337364293582418</v>
+        <v>-0.2432</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.012092880747253</v>
+        <v>-7.296</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.95</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1501195140668405</v>
+        <v>-0.2774</v>
       </c>
       <c r="J176" t="n">
-        <v>-4.503585422005215</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>0.309976216522081</v>
+        <v>0.7277</v>
       </c>
       <c r="J177" t="n">
-        <v>9.299286495662431</v>
+        <v>21.831</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2382696290945429</v>
+        <v>-0.1162</v>
       </c>
       <c r="J178" t="n">
-        <v>-7.148088872836287</v>
+        <v>-3.486</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2927630970146021</v>
+        <v>-0.1758</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.782892910438063</v>
+        <v>-5.274</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.84</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4281488596011258</v>
+        <v>-0.3254</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.84446578803377</v>
+        <v>-9.762</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4545298552897656</v>
+        <v>-0.3554</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.63589565869297</v>
+        <v>-10.662</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>0.93</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2314745942227595</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>-5.323915667123468</v>
+        <v>-1.4536</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2910390350326924</v>
+        <v>-0.1697</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.693897805751924</v>
+        <v>-3.9031</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3242110154785711</v>
+        <v>-0.2213</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.456853356007136</v>
+        <v>-5.0899</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4921393138182907</v>
+        <v>-0.4369</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.31920421782069</v>
+        <v>-10.0487</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5984766080385747</v>
+        <v>-0.6056</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.76496198488722</v>
+        <v>-13.9288</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>2.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.697068487973078</v>
+        <v>2.0593</v>
       </c>
       <c r="J187" t="n">
-        <v>16.03257522338079</v>
+        <v>47.3639</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.33</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3020716150950715</v>
+        <v>0.8006</v>
       </c>
       <c r="J188" t="n">
-        <v>6.947647147186644</v>
+        <v>18.4138</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.26</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2267602062923108</v>
+        <v>0.6065</v>
       </c>
       <c r="J189" t="n">
-        <v>5.215484744723148</v>
+        <v>13.9495</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.01365673690688127</v>
+        <v>-0.5296</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.3141049488582691</v>
+        <v>-12.1808</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3319764465885967</v>
+        <v>-0.9948</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.635458271537725</v>
+        <v>-22.8804</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3646781024559724</v>
+        <v>0.4462</v>
       </c>
       <c r="J192" t="n">
-        <v>10.5756649712232</v>
+        <v>12.9398</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2768240105382747</v>
+        <v>0.3466</v>
       </c>
       <c r="J193" t="n">
-        <v>8.027896305609964</v>
+        <v>10.0514</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>0.95</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1258366681715415</v>
+        <v>-0.1437</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.649263376974702</v>
+        <v>-4.1673</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1258366681715415</v>
+        <v>-0.1437</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.649263376974702</v>
+        <v>-4.1673</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2932597455309985</v>
+        <v>-0.4168</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.504532620398956</v>
+        <v>-12.0872</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.23</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1105487337382027</v>
+        <v>0.3831</v>
       </c>
       <c r="J197" t="n">
-        <v>3.205913278407877</v>
+        <v>11.1099</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0788169752585289</v>
+        <v>0.3239</v>
       </c>
       <c r="J198" t="n">
-        <v>2.285692282497338</v>
+        <v>9.3931</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>1.19</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0788169752585289</v>
+        <v>0.3239</v>
       </c>
       <c r="J199" t="n">
-        <v>2.285692282497338</v>
+        <v>9.3931</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.02973604851187138</v>
+        <v>0.1802</v>
       </c>
       <c r="J200" t="n">
-        <v>-0.8623454068442701</v>
+        <v>5.2258</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4542855340430189</v>
+        <v>-0.2435</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.17428048724755</v>
+        <v>-7.0615</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0183404930175718</v>
+        <v>0.2162</v>
       </c>
       <c r="J202" t="n">
-        <v>0.5318742975095823</v>
+        <v>6.2698</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.02770471769241875</v>
+        <v>0.138</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.8034368130801438</v>
+        <v>4.002</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1196560254514013</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.470024738090639</v>
+        <v>-2.0445</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2876004103665645</v>
+        <v>-0.2897</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.34041190063037</v>
+        <v>-8.401300000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5151202723299773</v>
+        <v>-0.6533</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.93848789756934</v>
+        <v>-18.9457</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3712179929997276</v>
+        <v>1.2967</v>
       </c>
       <c r="J207" t="n">
-        <v>10.7653217969921</v>
+        <v>37.6043</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.23</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2001949248902632</v>
+        <v>0.6387</v>
       </c>
       <c r="J208" t="n">
-        <v>5.805652821817632</v>
+        <v>18.5223</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.13</v>
       </c>
       <c r="I209" t="n">
-        <v>0.09516074745707404</v>
+        <v>0.3403</v>
       </c>
       <c r="J209" t="n">
-        <v>2.759661676255147</v>
+        <v>9.8687</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0009479223348561654</v>
+        <v>-0.0529</v>
       </c>
       <c r="J210" t="n">
-        <v>0.0274897477108288</v>
+        <v>-1.5341</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.95</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.09616872014980565</v>
+        <v>-0.3182</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.788892884344364</v>
+        <v>-9.2278</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5403281660477326</v>
+        <v>1.1753</v>
       </c>
       <c r="J212" t="n">
-        <v>15.66951681538425</v>
+        <v>34.0837</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.08</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1084245624852161</v>
+        <v>0.2431</v>
       </c>
       <c r="J213" t="n">
-        <v>3.144312312071268</v>
+        <v>7.0499</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I214" t="n">
-        <v>0.08986716224120983</v>
+        <v>0.2086</v>
       </c>
       <c r="J214" t="n">
-        <v>2.606147704995085</v>
+        <v>6.0494</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.08288352332074547</v>
+        <v>-0.2181</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.403622176301619</v>
+        <v>-6.3249</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1684502535049198</v>
+        <v>-0.4401</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.885057351642675</v>
+        <v>-12.7629</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3980647259555639</v>
+        <v>0.5085</v>
       </c>
       <c r="J217" t="n">
-        <v>11.54387705271135</v>
+        <v>14.7465</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2192293597180932</v>
+        <v>0.3409</v>
       </c>
       <c r="J218" t="n">
-        <v>6.357651431824701</v>
+        <v>9.886100000000001</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2231993039512613</v>
+        <v>-0.1537</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.472779814586576</v>
+        <v>-4.4573</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2713865734797298</v>
+        <v>-0.2266</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.870210630912165</v>
+        <v>-6.5714</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.68</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4696641249629735</v>
+        <v>-0.5454</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.62025962392623</v>
+        <v>-15.8166</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4162526428101888</v>
+        <v>0.9549</v>
       </c>
       <c r="J222" t="n">
-        <v>14.98509514116679</v>
+        <v>34.3764</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3975764509915587</v>
+        <v>0.9099</v>
       </c>
       <c r="J223" t="n">
-        <v>14.31275223569611</v>
+        <v>32.7564</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.85</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2297281081164871</v>
+        <v>-0.5339</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.270211892193535</v>
+        <v>-19.2204</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.78</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2942484277949907</v>
+        <v>-0.7139</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.59294340061966</v>
+        <v>-25.7004</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3514051138186696</v>
+        <v>-0.8798</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.65058409747211</v>
+        <v>-31.6728</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5409185101228812</v>
+        <v>0.621</v>
       </c>
       <c r="J227" t="n">
-        <v>19.47306636442372</v>
+        <v>22.356</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I228" t="n">
-        <v>0.517767399598941</v>
+        <v>0.5967</v>
       </c>
       <c r="J228" t="n">
-        <v>18.63962638556188</v>
+        <v>21.4812</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.18</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2166044007815056</v>
+        <v>0.3124</v>
       </c>
       <c r="J229" t="n">
-        <v>7.7977584281342</v>
+        <v>11.2464</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3286857448232544</v>
+        <v>-0.335</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.83268681363716</v>
+        <v>-12.06</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.415468303930504</v>
+        <v>-0.4741</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.95685894149814</v>
+        <v>-17.0676</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5357620938108825</v>
+        <v>1.2866</v>
       </c>
       <c r="J232" t="n">
-        <v>11.25100397002853</v>
+        <v>27.0186</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5034532740207303</v>
+        <v>1.1869</v>
       </c>
       <c r="J233" t="n">
-        <v>10.57251875443534</v>
+        <v>24.9249</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>0.442681072051459</v>
+        <v>1.0177</v>
       </c>
       <c r="J234" t="n">
-        <v>9.296302513080638</v>
+        <v>21.3717</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3699545820388349</v>
+        <v>0.8643</v>
       </c>
       <c r="J235" t="n">
-        <v>7.769046222815533</v>
+        <v>18.1503</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>1.04</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1152758763678685</v>
+        <v>-0.0129</v>
       </c>
       <c r="J236" t="n">
-        <v>2.420793403725237</v>
+        <v>-0.2709</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>0.91</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2717506063028105</v>
+        <v>-0.0645</v>
       </c>
       <c r="J237" t="n">
-        <v>-5.706762732359021</v>
+        <v>-1.3545</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>0.87</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.305629538595471</v>
+        <v>-0.1331</v>
       </c>
       <c r="J238" t="n">
-        <v>-6.418220310504892</v>
+        <v>-2.7951</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>0.74</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4367805532894189</v>
+        <v>-0.3473</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.172391619077796</v>
+        <v>-7.2933</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.63</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5847506298512259</v>
+        <v>-0.5393</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.27976322687574</v>
+        <v>-11.3253</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.43</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7394779813784829</v>
+        <v>-0.8041</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.52903760894814</v>
+        <v>-16.8861</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5485476846204317</v>
+        <v>1.2928</v>
       </c>
       <c r="J242" t="n">
-        <v>12.0680490616495</v>
+        <v>28.4416</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4680313461888039</v>
+        <v>1.028</v>
       </c>
       <c r="J243" t="n">
-        <v>10.29668961615369</v>
+        <v>22.616</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.28</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3190096010164631</v>
+        <v>0.6582</v>
       </c>
       <c r="J244" t="n">
-        <v>7.018211222362188</v>
+        <v>14.4804</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>1.24</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2801380829622664</v>
+        <v>0.5562</v>
       </c>
       <c r="J245" t="n">
-        <v>6.163037825169861</v>
+        <v>12.2364</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>0.09987722099186902</v>
+        <v>-0.2136</v>
       </c>
       <c r="J246" t="n">
-        <v>2.197298861821118</v>
+        <v>-4.6992</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1540846523340079</v>
+        <v>0.6293</v>
       </c>
       <c r="J247" t="n">
-        <v>3.389862351348173</v>
+        <v>13.8446</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>0.71</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4619587734890793</v>
+        <v>-0.4181</v>
       </c>
       <c r="J248" t="n">
-        <v>-10.16309301675975</v>
+        <v>-9.1982</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.5870469355916381</v>
+        <v>-0.5996</v>
       </c>
       <c r="J249" t="n">
-        <v>-12.91503258301604</v>
+        <v>-13.1912</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.58</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5955168170696862</v>
+        <v>-0.6133</v>
       </c>
       <c r="J250" t="n">
-        <v>-13.1013699755331</v>
+        <v>-13.4926</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6929370065055203</v>
+        <v>-0.7815</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.24461414312145</v>
+        <v>-17.193</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5892681922824637</v>
+        <v>1.8231</v>
       </c>
       <c r="J252" t="n">
-        <v>13.55316842249667</v>
+        <v>41.9313</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.58</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4504432600402909</v>
+        <v>1.2764</v>
       </c>
       <c r="J253" t="n">
-        <v>10.36019498092669</v>
+        <v>29.3572</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.49</v>
       </c>
       <c r="I254" t="n">
-        <v>0.393148113927533</v>
+        <v>1.0924</v>
       </c>
       <c r="J254" t="n">
-        <v>9.04240662033326</v>
+        <v>25.1252</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1201831882368021</v>
+        <v>0.2111</v>
       </c>
       <c r="J255" t="n">
-        <v>2.764213329446448</v>
+        <v>4.8553</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>1.03</v>
       </c>
       <c r="I256" t="n">
-        <v>0.07216168785462093</v>
+        <v>-0.052</v>
       </c>
       <c r="J256" t="n">
-        <v>1.659718820656281</v>
+        <v>-1.196</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>0.79</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.3162070482634896</v>
+        <v>-0.2428</v>
       </c>
       <c r="J257" t="n">
-        <v>-7.272762110060261</v>
+        <v>-5.5844</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>0.68</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.4404471301241603</v>
+        <v>-0.4264</v>
       </c>
       <c r="J258" t="n">
-        <v>-10.13028399285569</v>
+        <v>-9.8072</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4797584102324421</v>
+        <v>-0.4706</v>
       </c>
       <c r="J259" t="n">
-        <v>-11.03444343534617</v>
+        <v>-10.8238</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4930701479657996</v>
+        <v>-0.488</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.34061340321339</v>
+        <v>-11.224</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5475757152741538</v>
+        <v>-0.5662</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.59424145130554</v>
+        <v>-13.0226</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4400986956308997</v>
+        <v>1.1756</v>
       </c>
       <c r="J262" t="n">
-        <v>9.682171303879793</v>
+        <v>25.8632</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3986865211315201</v>
+        <v>1.0304</v>
       </c>
       <c r="J263" t="n">
-        <v>8.771103464893443</v>
+        <v>22.6688</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3021772646441538</v>
+        <v>0.7336</v>
       </c>
       <c r="J264" t="n">
-        <v>6.647899822171383</v>
+        <v>16.1392</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>1.05</v>
       </c>
       <c r="I265" t="n">
-        <v>0.0806139059443358</v>
+        <v>0.0625</v>
       </c>
       <c r="J265" t="n">
-        <v>1.773505930775388</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>0.05737039839390328</v>
+        <v>-0.0422</v>
       </c>
       <c r="J266" t="n">
-        <v>1.262148764665872</v>
+        <v>-0.9284</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.23</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.01937713954324538</v>
+        <v>0.4457</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.4262970699513984</v>
+        <v>9.805400000000001</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2041672055166572</v>
+        <v>0.1782</v>
       </c>
       <c r="J268" t="n">
-        <v>-4.491678521366458</v>
+        <v>3.9204</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4002482227786681</v>
+        <v>-0.1692</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.805460901130697</v>
+        <v>-3.7224</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5206860315541819</v>
+        <v>-0.3544</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.455092694192</v>
+        <v>-7.7968</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.7</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6124773903962968</v>
+        <v>-0.5093</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.47450258871853</v>
+        <v>-11.2046</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.25</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4094614491785351</v>
+        <v>0.7368</v>
       </c>
       <c r="J272" t="n">
-        <v>11.05545912782045</v>
+        <v>19.8936</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3770292212041292</v>
+        <v>0.6634</v>
       </c>
       <c r="J273" t="n">
-        <v>10.17978897251149</v>
+        <v>17.9118</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1852616911721331</v>
+        <v>0.2872</v>
       </c>
       <c r="J274" t="n">
-        <v>5.002065661647594</v>
+        <v>7.7544</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1056016784812086</v>
+        <v>0.1422</v>
       </c>
       <c r="J275" t="n">
-        <v>2.851245318992633</v>
+        <v>3.8394</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.1852050849372333</v>
+        <v>-0.5998</v>
       </c>
       <c r="J276" t="n">
-        <v>-5.000537293305299</v>
+        <v>-16.1946</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2190472357890857</v>
+        <v>0.4564</v>
       </c>
       <c r="J277" t="n">
-        <v>5.914275366305313</v>
+        <v>12.3228</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2190472357890857</v>
+        <v>0.4564</v>
       </c>
       <c r="J278" t="n">
-        <v>5.914275366305313</v>
+        <v>12.3228</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1164269121775285</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.143526628793268</v>
+        <v>1.9548</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2444524255630001</v>
+        <v>-0.132</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.600215490201002</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.49</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6338452640904723</v>
+        <v>-0.7743</v>
       </c>
       <c r="J281" t="n">
-        <v>-17.11382213044275</v>
+        <v>-20.9061</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.41</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5700767459179173</v>
+        <v>1.0998</v>
       </c>
       <c r="J282" t="n">
-        <v>15.39207213978377</v>
+        <v>29.6946</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3142448893617278</v>
+        <v>0.4859</v>
       </c>
       <c r="J283" t="n">
-        <v>8.484612012766652</v>
+        <v>13.1193</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2221795628987999</v>
+        <v>0.3026</v>
       </c>
       <c r="J284" t="n">
-        <v>5.998848198267599</v>
+        <v>8.170199999999999</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>0.88</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1231985457873754</v>
+        <v>-0.4904</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.326360736259134</v>
+        <v>-13.2408</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1341256564843275</v>
+        <v>-0.5175</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.621392725076843</v>
+        <v>-13.9725</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.09</v>
       </c>
       <c r="I287" t="n">
-        <v>0.03763727114460694</v>
+        <v>0.2261</v>
       </c>
       <c r="J287" t="n">
-        <v>1.016206320904387</v>
+        <v>6.1047</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.03768921758182921</v>
+        <v>0.1524</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.017608874709389</v>
+        <v>4.1148</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1102525749438423</v>
+        <v>0.0261</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.976819523483742</v>
+        <v>0.7047</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2515481048991846</v>
+        <v>-0.1771</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.791798832277983</v>
+        <v>-4.7817</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.74</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4398340045082861</v>
+        <v>-0.4587</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.87551812172373</v>
+        <v>-12.3849</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>0.78</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.5216229133003488</v>
+        <v>-0.1758</v>
       </c>
       <c r="J292" t="n">
-        <v>-9.910835352706627</v>
+        <v>-3.3402</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.7805082045727375</v>
+        <v>-0.5017</v>
       </c>
       <c r="J293" t="n">
-        <v>-14.82965588688201</v>
+        <v>-9.532299999999999</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>0.48</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.966336957897416</v>
+        <v>-0.673</v>
       </c>
       <c r="J294" t="n">
-        <v>-18.36040220005091</v>
+        <v>-12.787</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.43</v>
       </c>
       <c r="I295" t="n">
-        <v>-1.035822799622848</v>
+        <v>-0.7487</v>
       </c>
       <c r="J295" t="n">
-        <v>-19.6806331928341</v>
+        <v>-14.2253</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.084385410057726</v>
+        <v>-0.8054</v>
       </c>
       <c r="J296" t="n">
-        <v>-20.6033227910968</v>
+        <v>-15.3026</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>2.26</v>
       </c>
       <c r="I297" t="n">
-        <v>1.552018443358125</v>
+        <v>2.0593</v>
       </c>
       <c r="J297" t="n">
-        <v>29.48835042380437</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>1.8</v>
       </c>
       <c r="I298" t="n">
-        <v>1.188620080438311</v>
+        <v>1.6177</v>
       </c>
       <c r="J298" t="n">
-        <v>22.58378152832791</v>
+        <v>30.7363</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>1.34</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5380233432518717</v>
+        <v>0.672</v>
       </c>
       <c r="J299" t="n">
-        <v>10.22244352178556</v>
+        <v>12.768</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>1.3</v>
       </c>
       <c r="I300" t="n">
-        <v>0.4962415630173752</v>
+        <v>0.587</v>
       </c>
       <c r="J300" t="n">
-        <v>9.428589697330128</v>
+        <v>11.153</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>1.22</v>
       </c>
       <c r="I301" t="n">
-        <v>0.416598871628034</v>
+        <v>0.4111</v>
       </c>
       <c r="J301" t="n">
-        <v>7.915378560932646</v>
+        <v>7.8109</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.16</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1089901802089217</v>
+        <v>0.3287</v>
       </c>
       <c r="J302" t="n">
-        <v>3.269705406267651</v>
+        <v>9.861000000000001</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.06463595708154989</v>
+        <v>0.2494</v>
       </c>
       <c r="J303" t="n">
-        <v>1.939078712446497</v>
+        <v>7.482</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.01527157872679568</v>
+        <v>0.1793</v>
       </c>
       <c r="J304" t="n">
-        <v>0.4581473618038703</v>
+        <v>5.379</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4088150303449805</v>
+        <v>-0.274</v>
       </c>
       <c r="J305" t="n">
-        <v>-12.26445091034942</v>
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5980667816961753</v>
+        <v>-0.4783</v>
       </c>
       <c r="J306" t="n">
-        <v>-17.94200345088526</v>
+        <v>-14.349</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.33</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5848918478807205</v>
+        <v>0.9204</v>
       </c>
       <c r="J307" t="n">
-        <v>17.54675543642161</v>
+        <v>27.612</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.07</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1044159692213273</v>
+        <v>0.2103</v>
       </c>
       <c r="J308" t="n">
-        <v>3.13247907663982</v>
+        <v>6.309</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.05704696407463386</v>
+        <v>0.1408</v>
       </c>
       <c r="J309" t="n">
-        <v>1.711408922239016</v>
+        <v>4.224</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>1.04</v>
       </c>
       <c r="I310" t="n">
-        <v>0.03435970773193871</v>
+        <v>0.105</v>
       </c>
       <c r="J310" t="n">
-        <v>1.030791231958161</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.97</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.0951246160822809</v>
+        <v>-0.2171</v>
       </c>
       <c r="J311" t="n">
-        <v>-2.853738482468427</v>
+        <v>-6.513</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6972/event_6972_evp_summary.xlsx
+++ b/database/event/6972/event_6972_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>5.923</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.2544</v>
       </c>
       <c r="D2" t="n">
         <v>1.9714</v>
@@ -545,7 +545,7 @@
         <v>5.7099</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.1733</v>
       </c>
       <c r="D3" t="n">
         <v>1.8853</v>
@@ -591,7 +591,7 @@
         <v>5.7067</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.172</v>
       </c>
       <c r="D4" t="n">
         <v>1.884</v>
@@ -637,7 +637,7 @@
         <v>5.3527</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.0373</v>
       </c>
       <c r="D5" t="n">
         <v>1.741</v>
@@ -683,7 +683,7 @@
         <v>4.8476</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.8451</v>
       </c>
       <c r="D6" t="n">
         <v>1.537</v>
@@ -729,7 +729,7 @@
         <v>4.1196</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.568</v>
       </c>
       <c r="D7" t="n">
         <v>1.2429</v>
@@ -775,7 +775,7 @@
         <v>2.8977</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.1029</v>
       </c>
       <c r="D8" t="n">
         <v>0.7492</v>
@@ -821,7 +821,7 @@
         <v>2.7441</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.0444</v>
       </c>
       <c r="D9" t="n">
         <v>0.6872</v>
@@ -867,7 +867,7 @@
         <v>2.6051</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.9915</v>
       </c>
       <c r="D10" t="n">
         <v>0.631</v>
@@ -913,7 +913,7 @@
         <v>2.5654</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.9764</v>
       </c>
       <c r="D11" t="n">
         <v>0.615</v>
@@ -959,7 +959,7 @@
         <v>2.3489</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="D12" t="n">
         <v>0.5275</v>
@@ -1005,7 +1005,7 @@
         <v>2.2734</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.8653</v>
       </c>
       <c r="D13" t="n">
         <v>0.497</v>
@@ -1051,7 +1051,7 @@
         <v>2.1138</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.8045</v>
       </c>
       <c r="D14" t="n">
         <v>0.4326</v>
@@ -1097,7 +1097,7 @@
         <v>1.9756</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.7519</v>
       </c>
       <c r="D15" t="n">
         <v>0.3767</v>
@@ -1143,7 +1143,7 @@
         <v>1.8091</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.6886</v>
       </c>
       <c r="D16" t="n">
         <v>0.3095</v>
@@ -1189,7 +1189,7 @@
         <v>1.6444</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.6259</v>
       </c>
       <c r="D17" t="n">
         <v>0.2429</v>
@@ -1235,7 +1235,7 @@
         <v>1.4792</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>0.1762</v>
@@ -1281,7 +1281,7 @@
         <v>1.3097</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.4985</v>
       </c>
       <c r="D19" t="n">
         <v>0.1077</v>
@@ -1327,7 +1327,7 @@
         <v>1.2037</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.4581</v>
       </c>
       <c r="D20" t="n">
         <v>0.0649</v>
@@ -1373,7 +1373,7 @@
         <v>1.1176</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="D21" t="n">
         <v>0.0301</v>
@@ -1419,7 +1419,7 @@
         <v>1.0694</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.407</v>
       </c>
       <c r="D22" t="n">
         <v>0.0107</v>
@@ -1465,7 +1465,7 @@
         <v>0.8567</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.3261</v>
       </c>
       <c r="D23" t="n">
         <v>-0.07530000000000001</v>
@@ -1511,7 +1511,7 @@
         <v>0.7435</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="D24" t="n">
         <v>-0.121</v>
@@ -1557,7 +1557,7 @@
         <v>0.2477</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3213</v>
@@ -1603,7 +1603,7 @@
         <v>0.0693</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0264</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3934</v>
@@ -1649,7 +1649,7 @@
         <v>-0.163</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.062</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4872</v>
@@ -1695,7 +1695,7 @@
         <v>-0.2823</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.1074</v>
       </c>
       <c r="D28" t="n">
         <v>-0.5354</v>
@@ -1741,7 +1741,7 @@
         <v>-0.5817</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.2214</v>
       </c>
       <c r="D29" t="n">
         <v>-0.6564</v>
@@ -1787,7 +1787,7 @@
         <v>-0.6074000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.2312</v>
       </c>
       <c r="D30" t="n">
         <v>-0.6667</v>
@@ -1833,7 +1833,7 @@
         <v>-0.6357</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.242</v>
       </c>
       <c r="D31" t="n">
         <v>-0.6782</v>
@@ -1879,7 +1879,7 @@
         <v>-0.7286</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.2773</v>
       </c>
       <c r="D32" t="n">
         <v>-0.7157</v>
@@ -1925,7 +1925,7 @@
         <v>-0.9733000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.3704</v>
       </c>
       <c r="D33" t="n">
         <v>-0.8146</v>
@@ -1971,7 +1971,7 @@
         <v>-1.204</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.4583</v>
       </c>
       <c r="D34" t="n">
         <v>-0.9078000000000001</v>
@@ -2017,7 +2017,7 @@
         <v>-1.233</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.4693</v>
       </c>
       <c r="D35" t="n">
         <v>-0.9195</v>
@@ -2063,7 +2063,7 @@
         <v>-1.6041</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.6105</v>
       </c>
       <c r="D36" t="n">
         <v>-1.0694</v>
@@ -2109,7 +2109,7 @@
         <v>-1.7327</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.6595</v>
       </c>
       <c r="D37" t="n">
         <v>-1.1213</v>
@@ -2155,7 +2155,7 @@
         <v>-2.0705</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.7881</v>
       </c>
       <c r="D38" t="n">
         <v>-1.2578</v>
@@ -2201,7 +2201,7 @@
         <v>-2.123</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="D39" t="n">
         <v>-1.279</v>
@@ -2247,7 +2247,7 @@
         <v>-2.9518</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-1.1235</v>
       </c>
       <c r="D40" t="n">
         <v>-1.6138</v>
@@ -2293,7 +2293,7 @@
         <v>-4.7605</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-1.8119</v>
       </c>
       <c r="D41" t="n">
         <v>-2.3445</v>

--- a/database/event/6972/event_6972_evp_summary.xlsx
+++ b/database/event/6972/event_6972_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.2544</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9714</v>
+        <v>1.9158</v>
       </c>
       <c r="E2" t="n">
         <v>5.923</v>
@@ -548,7 +548,7 @@
         <v>2.1733</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8853</v>
+        <v>1.8309</v>
       </c>
       <c r="E3" t="n">
         <v>5.7099</v>
@@ -594,7 +594,7 @@
         <v>2.172</v>
       </c>
       <c r="D4" t="n">
-        <v>1.884</v>
+        <v>1.8296</v>
       </c>
       <c r="E4" t="n">
         <v>5.7067</v>
@@ -640,7 +640,7 @@
         <v>2.0373</v>
       </c>
       <c r="D5" t="n">
-        <v>1.741</v>
+        <v>1.6886</v>
       </c>
       <c r="E5" t="n">
         <v>5.3527</v>
@@ -686,7 +686,7 @@
         <v>1.8451</v>
       </c>
       <c r="D6" t="n">
-        <v>1.537</v>
+        <v>1.4874</v>
       </c>
       <c r="E6" t="n">
         <v>4.8476</v>
@@ -732,7 +732,7 @@
         <v>1.568</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2429</v>
+        <v>1.1973</v>
       </c>
       <c r="E7" t="n">
         <v>4.1196</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8977</v>
+        <v>2.8924</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1029</v>
+        <v>1.1009</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7492</v>
+        <v>0.7084</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8977</v>
+        <v>2.8924</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4181</v>
+        <v>1.4128</v>
       </c>
       <c r="G8" t="n">
         <v>1.4796</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4181</v>
+        <v>1.4128</v>
       </c>
       <c r="I8" t="n">
         <v>1.4247</v>
@@ -824,7 +824,7 @@
         <v>1.0444</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6872</v>
+        <v>0.6493</v>
       </c>
       <c r="E9" t="n">
         <v>2.7441</v>
@@ -870,7 +870,7 @@
         <v>0.9915</v>
       </c>
       <c r="D10" t="n">
-        <v>0.631</v>
+        <v>0.594</v>
       </c>
       <c r="E10" t="n">
         <v>2.6051</v>
@@ -916,7 +916,7 @@
         <v>0.9764</v>
       </c>
       <c r="D11" t="n">
-        <v>0.615</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>2.5654</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3489</v>
+        <v>2.3441</v>
       </c>
       <c r="C12" t="n">
-        <v>0.894</v>
+        <v>0.8922</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5275</v>
+        <v>0.49</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3489</v>
+        <v>2.3441</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2827</v>
+        <v>1.2779</v>
       </c>
       <c r="G12" t="n">
         <v>1.0662</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2827</v>
+        <v>1.2779</v>
       </c>
       <c r="I12" t="n">
         <v>1.2887</v>
@@ -1008,7 +1008,7 @@
         <v>0.8653</v>
       </c>
       <c r="D13" t="n">
-        <v>0.497</v>
+        <v>0.4618</v>
       </c>
       <c r="E13" t="n">
         <v>2.2734</v>
@@ -1054,7 +1054,7 @@
         <v>0.8045</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4326</v>
+        <v>0.3982</v>
       </c>
       <c r="E14" t="n">
         <v>2.1138</v>
@@ -1100,7 +1100,7 @@
         <v>0.7519</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3767</v>
+        <v>0.3432</v>
       </c>
       <c r="E15" t="n">
         <v>1.9756</v>
@@ -1146,7 +1146,7 @@
         <v>0.6886</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3095</v>
+        <v>0.2768</v>
       </c>
       <c r="E16" t="n">
         <v>1.8091</v>
@@ -1192,7 +1192,7 @@
         <v>0.6259</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2429</v>
+        <v>0.2112</v>
       </c>
       <c r="E17" t="n">
         <v>1.6444</v>
@@ -1238,7 +1238,7 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1762</v>
+        <v>0.1454</v>
       </c>
       <c r="E18" t="n">
         <v>1.4792</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3097</v>
+        <v>1.3115</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4985</v>
+        <v>0.4992</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1077</v>
+        <v>0.0786</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3097</v>
+        <v>1.3115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.488</v>
+        <v>-0.4862</v>
       </c>
       <c r="G19" t="n">
         <v>1.7977</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.488</v>
+        <v>-0.4862</v>
       </c>
       <c r="I19" t="n">
         <v>-0.4903</v>
@@ -1330,7 +1330,7 @@
         <v>0.4581</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0649</v>
+        <v>0.0356</v>
       </c>
       <c r="E20" t="n">
         <v>1.2037</v>
@@ -1376,7 +1376,7 @@
         <v>0.4254</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0301</v>
+        <v>0.0013</v>
       </c>
       <c r="E21" t="n">
         <v>1.1176</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0694</v>
+        <v>1.0639</v>
       </c>
       <c r="C22" t="n">
-        <v>0.407</v>
+        <v>0.4049</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0107</v>
+        <v>-0.0201</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0694</v>
+        <v>1.0639</v>
       </c>
       <c r="F22" t="n">
-        <v>1.455</v>
+        <v>1.4495</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3856</v>
       </c>
       <c r="H22" t="n">
-        <v>1.455</v>
+        <v>1.4495</v>
       </c>
       <c r="I22" t="n">
         <v>1.4617</v>
@@ -1468,7 +1468,7 @@
         <v>0.3261</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.1026</v>
       </c>
       <c r="E23" t="n">
         <v>0.8567</v>
@@ -1514,7 +1514,7 @@
         <v>0.283</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.121</v>
+        <v>-0.1477</v>
       </c>
       <c r="E24" t="n">
         <v>0.7435</v>
@@ -1560,7 +1560,7 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3213</v>
+        <v>-0.3452</v>
       </c>
       <c r="E25" t="n">
         <v>0.2477</v>
@@ -1606,7 +1606,7 @@
         <v>0.0264</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3934</v>
+        <v>-0.4163</v>
       </c>
       <c r="E26" t="n">
         <v>0.0693</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.163</v>
+        <v>-0.1634</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.062</v>
+        <v>-0.0622</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4872</v>
+        <v>-0.509</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.163</v>
+        <v>-0.1634</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1194</v>
+        <v>0.119</v>
       </c>
       <c r="G27" t="n">
         <v>-0.2824</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1194</v>
+        <v>0.119</v>
       </c>
       <c r="I27" t="n">
         <v>0.12</v>
@@ -1698,7 +1698,7 @@
         <v>-0.1074</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5354</v>
+        <v>-0.5564</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2823</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2214</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6564</v>
+        <v>-0.6757</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5817</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2312</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6667</v>
+        <v>-0.6859</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6074000000000001</v>
@@ -1836,7 +1836,7 @@
         <v>-0.242</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6782</v>
+        <v>-0.6972</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6357</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2773</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7157</v>
+        <v>-0.7342</v>
       </c>
       <c r="E32" t="n">
         <v>-0.7286</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3704</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8146</v>
+        <v>-0.8317</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9733000000000001</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4583</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.9236</v>
       </c>
       <c r="E34" t="n">
         <v>-1.204</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4693</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9195</v>
+        <v>-0.9351</v>
       </c>
       <c r="E35" t="n">
         <v>-1.233</v>
@@ -2066,7 +2066,7 @@
         <v>-0.6105</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0694</v>
+        <v>-1.083</v>
       </c>
       <c r="E36" t="n">
         <v>-1.6041</v>
@@ -2112,7 +2112,7 @@
         <v>-0.6595</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1213</v>
+        <v>-1.1342</v>
       </c>
       <c r="E37" t="n">
         <v>-1.7327</v>
@@ -2158,7 +2158,7 @@
         <v>-0.7881</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2578</v>
+        <v>-1.2688</v>
       </c>
       <c r="E38" t="n">
         <v>-2.0705</v>
@@ -2204,7 +2204,7 @@
         <v>-0.8080000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.279</v>
+        <v>-1.2897</v>
       </c>
       <c r="E39" t="n">
         <v>-2.123</v>
@@ -2250,7 +2250,7 @@
         <v>-1.1235</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6138</v>
+        <v>-1.6199</v>
       </c>
       <c r="E40" t="n">
         <v>-2.9518</v>
@@ -2296,7 +2296,7 @@
         <v>-1.8119</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3445</v>
+        <v>-2.3405</v>
       </c>
       <c r="E41" t="n">
         <v>-4.7605</v>

--- a/database/event/6972/event_6972_evp_summary.xlsx
+++ b/database/event/6972/event_6972_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.923</v>
+        <v>5.4569</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2544</v>
+        <v>2.077</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9158</v>
+        <v>1.8255</v>
       </c>
       <c r="E2" t="n">
-        <v>5.923</v>
+        <v>5.4569</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6965</v>
+        <v>3.0884</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2265</v>
+        <v>2.3685</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6965</v>
+        <v>5.3953</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9961</v>
+        <v>2.8053</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2265</v>
+        <v>2.3685</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>5.2226</v>
+        <v>5.1738</v>
       </c>
       <c r="N2" t="n">
         <v>274</v>
@@ -538,81 +538,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7099</v>
+        <v>5.2681</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1733</v>
+        <v>2.0051</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8309</v>
+        <v>1.7403</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7099</v>
+        <v>5.2681</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2158</v>
+        <v>2.0532</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4941</v>
+        <v>3.2149</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4007</v>
+        <v>2.0532</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5669</v>
+        <v>2.0532</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4941</v>
+        <v>3.2149</v>
       </c>
       <c r="K3" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="L3" t="n">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="M3" t="n">
-        <v>5.061</v>
+        <v>5.2681</v>
       </c>
       <c r="N3" t="n">
-        <v>274</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7067</v>
+        <v>5.1581</v>
       </c>
       <c r="C4" t="n">
-        <v>2.172</v>
+        <v>1.9632</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8296</v>
+        <v>1.6906</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7067</v>
+        <v>5.1581</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2326</v>
+        <v>3.1593</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4741</v>
+        <v>1.9988</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2326</v>
+        <v>5.6451</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6201</v>
+        <v>2.9352</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4741</v>
+        <v>1.9988</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -621,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0942</v>
+        <v>4.934</v>
       </c>
       <c r="N4" t="n">
         <v>274</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3527</v>
+        <v>5.1216</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0373</v>
+        <v>1.9493</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6886</v>
+        <v>1.6741</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3527</v>
+        <v>5.1216</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7331</v>
+        <v>3.6418</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6196</v>
+        <v>1.4798</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7331</v>
+        <v>7.3453</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7331</v>
+        <v>3.8192</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6196</v>
+        <v>1.4798</v>
       </c>
       <c r="K5" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="L5" t="n">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3527</v>
+        <v>5.298999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>330</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8476</v>
+        <v>4.3087</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8451</v>
+        <v>1.6399</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4874</v>
+        <v>1.3071</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8476</v>
+        <v>4.3087</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2433</v>
+        <v>3.6881</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6206</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5112</v>
+        <v>7.5084</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6564</v>
+        <v>3.904</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6206</v>
       </c>
       <c r="K6" t="n">
         <v>135</v>
@@ -713,7 +713,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2607</v>
+        <v>4.5246</v>
       </c>
       <c r="N6" t="n">
         <v>215</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1196</v>
+        <v>4.1218</v>
       </c>
       <c r="C7" t="n">
-        <v>1.568</v>
+        <v>1.5688</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1973</v>
+        <v>1.2228</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1196</v>
+        <v>4.1218</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0336</v>
+        <v>3.0877</v>
       </c>
       <c r="G7" t="n">
-        <v>1.086</v>
+        <v>1.0341</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0336</v>
+        <v>5.3928</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4588</v>
+        <v>2.804</v>
       </c>
       <c r="J7" t="n">
-        <v>1.086</v>
+        <v>1.0341</v>
       </c>
       <c r="K7" t="n">
         <v>135</v>
@@ -759,7 +759,7 @@
         <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5448</v>
+        <v>3.8381</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -768,44 +768,44 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8924</v>
+        <v>3.1889</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1009</v>
+        <v>1.2137</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7084</v>
+        <v>0.8016</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8924</v>
+        <v>3.1889</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4128</v>
+        <v>2.3402</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4796</v>
+        <v>0.8487</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4128</v>
+        <v>2.7591</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4247</v>
+        <v>1.4346</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4796</v>
+        <v>0.8487</v>
       </c>
       <c r="K8" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L8" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9043</v>
+        <v>2.2833</v>
       </c>
       <c r="N8" t="n">
         <v>274</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7441</v>
+        <v>2.9366</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0444</v>
+        <v>1.1177</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6493</v>
+        <v>0.6877</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7441</v>
+        <v>2.9366</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8837</v>
+        <v>2.8544</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1396</v>
+        <v>0.0822</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8837</v>
+        <v>4.571</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3373</v>
+        <v>2.3767</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1396</v>
+        <v>0.0822</v>
       </c>
       <c r="K9" t="n">
         <v>135</v>
@@ -851,7 +851,7 @@
         <v>80</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1977</v>
+        <v>2.4589</v>
       </c>
       <c r="N9" t="n">
         <v>215</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6051</v>
+        <v>2.76</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9915</v>
+        <v>1.0505</v>
       </c>
       <c r="D10" t="n">
-        <v>0.594</v>
+        <v>0.608</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6051</v>
+        <v>2.76</v>
       </c>
       <c r="F10" t="n">
-        <v>1.338</v>
+        <v>1.575</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2671</v>
+        <v>1.185</v>
       </c>
       <c r="H10" t="n">
-        <v>1.338</v>
+        <v>1.575</v>
       </c>
       <c r="I10" t="n">
-        <v>1.338</v>
+        <v>1.575</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2671</v>
+        <v>1.185</v>
       </c>
       <c r="K10" t="n">
         <v>104</v>
@@ -897,7 +897,7 @@
         <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6051</v>
+        <v>2.76</v>
       </c>
       <c r="N10" t="n">
         <v>164</v>
@@ -906,136 +906,136 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5654</v>
+        <v>2.7028</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9764</v>
+        <v>1.0287</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5654</v>
+        <v>2.7028</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9701</v>
+        <v>1.4109</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5355</v>
+        <v>1.2919</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9701</v>
+        <v>1.4109</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9701</v>
+        <v>1.4689</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5355</v>
+        <v>1.2919</v>
       </c>
       <c r="K11" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="L11" t="n">
-        <v>216</v>
+        <v>144</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5654</v>
+        <v>2.7608</v>
       </c>
       <c r="N11" t="n">
-        <v>330</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3441</v>
+        <v>2.5961</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8922</v>
+        <v>0.9881</v>
       </c>
       <c r="D12" t="n">
-        <v>0.49</v>
+        <v>0.534</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3441</v>
+        <v>2.5961</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2779</v>
+        <v>2.5961</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0662</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2779</v>
+        <v>2.5961</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2887</v>
+        <v>2.5961</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0662</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3549</v>
+        <v>2.5961</v>
       </c>
       <c r="N12" t="n">
-        <v>274</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2734</v>
+        <v>2.2661</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8653</v>
+        <v>0.8625</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4618</v>
+        <v>0.385</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2734</v>
+        <v>2.2661</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6001</v>
+        <v>1.4648</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6733</v>
+        <v>0.8013</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6001</v>
+        <v>1.4648</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2969</v>
+        <v>1.525</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6733</v>
+        <v>0.8013</v>
       </c>
       <c r="K13" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L13" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9702</v>
+        <v>2.3263</v>
       </c>
       <c r="N13" t="n">
         <v>274</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1138</v>
+        <v>2.1531</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8045</v>
+        <v>0.8195</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3982</v>
+        <v>0.334</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1138</v>
+        <v>2.1531</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3475</v>
+        <v>0.6219</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7663</v>
+        <v>1.5312</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3475</v>
+        <v>0.6219</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3475</v>
+        <v>0.6219</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7663</v>
+        <v>1.5312</v>
       </c>
       <c r="K14" t="n">
         <v>114</v>
@@ -1081,7 +1081,7 @@
         <v>216</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1138</v>
+        <v>2.1531</v>
       </c>
       <c r="N14" t="n">
         <v>330</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9756</v>
+        <v>2.1451</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7519</v>
+        <v>0.8164</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3432</v>
+        <v>0.3304</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9756</v>
+        <v>2.1451</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9756</v>
+        <v>-0.649</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.7941</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9756</v>
+        <v>-0.649</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9756</v>
+        <v>-0.649</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.7941</v>
       </c>
       <c r="K15" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9756</v>
+        <v>2.1451</v>
       </c>
       <c r="N15" t="n">
-        <v>133</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8091</v>
+        <v>2.0371</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6886</v>
+        <v>0.7753</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2768</v>
+        <v>0.2816</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8091</v>
+        <v>2.0371</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5938</v>
+        <v>1.783</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2153</v>
+        <v>0.2541</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5938</v>
+        <v>1.783</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5938</v>
+        <v>1.783</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2153</v>
+        <v>0.2541</v>
       </c>
       <c r="K16" t="n">
         <v>135</v>
@@ -1173,7 +1173,7 @@
         <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8091</v>
+        <v>2.0371</v>
       </c>
       <c r="N16" t="n">
         <v>187</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6444</v>
+        <v>1.9127</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6259</v>
+        <v>0.728</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2112</v>
+        <v>0.2255</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6444</v>
+        <v>1.9127</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6444</v>
+        <v>1.9127</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6444</v>
+        <v>1.9127</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6444</v>
+        <v>1.9127</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6444</v>
+        <v>1.9127</v>
       </c>
       <c r="N17" t="n">
         <v>119</v>
@@ -1228,173 +1228,173 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4792</v>
+        <v>1.8914</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.7199</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1454</v>
+        <v>0.2159</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4792</v>
+        <v>1.8914</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1441</v>
+        <v>1.8034</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3351</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1441</v>
+        <v>1.8034</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1441</v>
+        <v>0.9377</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3351</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L18" t="n">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4792</v>
+        <v>1.0257</v>
       </c>
       <c r="N18" t="n">
-        <v>164</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3115</v>
+        <v>1.787</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4992</v>
+        <v>0.6802</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0786</v>
+        <v>0.1687</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3115</v>
+        <v>1.787</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4862</v>
+        <v>1.375</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7977</v>
+        <v>0.412</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4862</v>
+        <v>1.375</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4903</v>
+        <v>1.375</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7977</v>
+        <v>0.412</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L19" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3074</v>
+        <v>1.787</v>
       </c>
       <c r="N19" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2037</v>
+        <v>1.7456</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4581</v>
+        <v>0.6644</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0356</v>
+        <v>0.15</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2037</v>
+        <v>1.7456</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2037</v>
+        <v>1.891</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.1454</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2037</v>
+        <v>1.891</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2037</v>
+        <v>1.9688</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.1454</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2037</v>
+        <v>1.8234</v>
       </c>
       <c r="N20" t="n">
-        <v>119</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1176</v>
+        <v>1.6818</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4254</v>
+        <v>0.6401</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0013</v>
+        <v>0.1212</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1176</v>
+        <v>1.6818</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3168</v>
+        <v>2.4285</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1992</v>
+        <v>-0.7467</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3168</v>
+        <v>2.4285</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3168</v>
+        <v>2.4285</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1992</v>
+        <v>-0.7467</v>
       </c>
       <c r="K21" t="n">
         <v>104</v>
@@ -1403,7 +1403,7 @@
         <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1176</v>
+        <v>1.6818</v>
       </c>
       <c r="N21" t="n">
         <v>164</v>
@@ -1412,35 +1412,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0639</v>
+        <v>1.6094</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4049</v>
+        <v>0.6126</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0201</v>
+        <v>0.0885</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0639</v>
+        <v>1.6094</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4495</v>
+        <v>-0.0209</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3856</v>
+        <v>1.6303</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4495</v>
+        <v>-0.0209</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4617</v>
+        <v>-0.0218</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3856</v>
+        <v>1.6303</v>
       </c>
       <c r="K22" t="n">
         <v>130</v>
@@ -1449,7 +1449,7 @@
         <v>144</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0761</v>
+        <v>1.6085</v>
       </c>
       <c r="N22" t="n">
         <v>274</v>
@@ -1458,173 +1458,173 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8567</v>
+        <v>1.4137</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3261</v>
+        <v>0.5381</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1026</v>
+        <v>0.0002</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8567</v>
+        <v>1.4137</v>
       </c>
       <c r="F23" t="n">
-        <v>0.837</v>
+        <v>1.5502</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0197</v>
+        <v>-0.1365</v>
       </c>
       <c r="H23" t="n">
-        <v>0.837</v>
+        <v>1.5502</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6784</v>
+        <v>1.5502</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0197</v>
+        <v>-0.1365</v>
       </c>
       <c r="K23" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L23" t="n">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6981000000000001</v>
+        <v>1.4137</v>
       </c>
       <c r="N23" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7435</v>
+        <v>1.4026</v>
       </c>
       <c r="C24" t="n">
-        <v>0.283</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1477</v>
+        <v>-0.0048</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7435</v>
+        <v>1.4026</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7435</v>
+        <v>1.4026</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7435</v>
+        <v>1.4026</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7435</v>
+        <v>1.4026</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7435</v>
+        <v>1.4026</v>
       </c>
       <c r="N24" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2477</v>
+        <v>0.6007</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.2286</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3452</v>
+        <v>-0.3668</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2477</v>
+        <v>0.6007</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0248</v>
+        <v>0.4654</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2725</v>
+        <v>0.1353</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0248</v>
+        <v>0.4654</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0248</v>
+        <v>0.4845</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2725</v>
+        <v>0.1353</v>
       </c>
       <c r="K25" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2477</v>
+        <v>0.6198</v>
       </c>
       <c r="N25" t="n">
-        <v>187</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0693</v>
+        <v>0.4781</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0264</v>
+        <v>0.182</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4163</v>
+        <v>-0.4222</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0693</v>
+        <v>0.4781</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2747</v>
+        <v>0.1548</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2054</v>
+        <v>0.3233</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2747</v>
+        <v>0.1548</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2747</v>
+        <v>0.1548</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2054</v>
+        <v>0.3233</v>
       </c>
       <c r="K26" t="n">
         <v>135</v>
@@ -1633,7 +1633,7 @@
         <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0693</v>
+        <v>0.4781</v>
       </c>
       <c r="N26" t="n">
         <v>187</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1634</v>
+        <v>0.4144</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0622</v>
+        <v>0.1577</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.509</v>
+        <v>-0.4509</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1634</v>
+        <v>0.4144</v>
       </c>
       <c r="F27" t="n">
-        <v>0.119</v>
+        <v>0.4028</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2824</v>
+        <v>0.0116</v>
       </c>
       <c r="H27" t="n">
-        <v>0.119</v>
+        <v>0.4028</v>
       </c>
       <c r="I27" t="n">
-        <v>0.12</v>
+        <v>0.4028</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2824</v>
+        <v>0.0116</v>
       </c>
       <c r="K27" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L27" t="n">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1624</v>
+        <v>0.4144</v>
       </c>
       <c r="N27" t="n">
-        <v>274</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2823</v>
+        <v>0.09</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1074</v>
+        <v>0.0343</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5564</v>
+        <v>-0.5974</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2823</v>
+        <v>0.09</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2823</v>
+        <v>0.09</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2823</v>
+        <v>0.09</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2823</v>
+        <v>0.09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2823</v>
+        <v>0.09</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5817</v>
+        <v>-0.2212</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2214</v>
+        <v>-0.0842</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6757</v>
+        <v>-0.7379</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5817</v>
+        <v>-0.2212</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.0443</v>
+        <v>0.3644</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4626</v>
+        <v>-0.5856</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.0443</v>
+        <v>0.3644</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8464</v>
+        <v>0.3644</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4626</v>
+        <v>-0.5856</v>
       </c>
       <c r="K29" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L29" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3838</v>
+        <v>-0.2212</v>
       </c>
       <c r="N29" t="n">
-        <v>215</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2312</v>
+        <v>-0.1199</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6859</v>
+        <v>-0.7803</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="N30" t="n">
         <v>119</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.242</v>
+        <v>-0.1315</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6972</v>
+        <v>-0.794</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6357</v>
+        <v>-0.3456</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7286</v>
+        <v>-0.4507</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2773</v>
+        <v>-0.1715</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7342</v>
+        <v>-0.8415</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7286</v>
+        <v>-0.4507</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7286</v>
+        <v>-0.4507</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7286</v>
+        <v>-0.4507</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7286</v>
+        <v>-0.4507</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7286</v>
+        <v>-0.4507</v>
       </c>
       <c r="N32" t="n">
         <v>133</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.7435</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3704</v>
+        <v>-0.283</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8317</v>
+        <v>-0.9737</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.7435</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-1.1815</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.9023</v>
+        <v>0.438</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-1.1815</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.6143</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9023</v>
+        <v>0.438</v>
       </c>
       <c r="K33" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9732999999999999</v>
+        <v>-0.1763</v>
       </c>
       <c r="N33" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.204</v>
+        <v>-0.8026</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4583</v>
+        <v>-0.3055</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9236</v>
+        <v>-1.0003</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.204</v>
+        <v>-0.8026</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.204</v>
+        <v>-0.8026</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.204</v>
+        <v>-0.8026</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.204</v>
+        <v>-0.8026</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.204</v>
+        <v>-0.8026</v>
       </c>
       <c r="N34" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.233</v>
+        <v>-0.9337</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4693</v>
+        <v>-0.3554</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9351</v>
+        <v>-1.0595</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.233</v>
+        <v>-0.9337</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.233</v>
+        <v>-0.9337</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.233</v>
+        <v>-0.9337</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.233</v>
+        <v>-0.9337</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.233</v>
+        <v>-0.9337</v>
       </c>
       <c r="N35" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6041</v>
+        <v>-0.9576</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6105</v>
+        <v>-0.3645</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.083</v>
+        <v>-1.0703</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6041</v>
+        <v>-0.9576</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6041</v>
+        <v>-0.2973</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>-0.6603</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6041</v>
+        <v>-0.2973</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6041</v>
+        <v>-0.2973</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>-0.6603</v>
       </c>
       <c r="K36" t="n">
         <v>135</v>
@@ -2093,7 +2093,7 @@
         <v>52</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6041</v>
+        <v>-0.9576</v>
       </c>
       <c r="N36" t="n">
         <v>187</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Altekz</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7327</v>
+        <v>-1.386</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6595</v>
+        <v>-0.5275</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1342</v>
+        <v>-1.2637</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7327</v>
+        <v>-1.386</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.7327</v>
+        <v>-1.2153</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.7327</v>
+        <v>-1.2153</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.7327</v>
+        <v>-1.2153</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="K37" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.7327</v>
+        <v>-1.386</v>
       </c>
       <c r="N37" t="n">
-        <v>133</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Altekz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.0705</v>
+        <v>-1.5302</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7881</v>
+        <v>-0.5824</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2688</v>
+        <v>-1.3288</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.0705</v>
+        <v>-1.5302</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8282</v>
+        <v>-1.5302</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2423</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8282</v>
+        <v>-1.5302</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8282</v>
+        <v>-1.5302</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2423</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L38" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.0705</v>
+        <v>-1.5302</v>
       </c>
       <c r="N38" t="n">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.123</v>
+        <v>-1.6376</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.6233</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2897</v>
+        <v>-1.3773</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.123</v>
+        <v>-1.6376</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3253</v>
+        <v>-0.9677</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7977</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3253</v>
+        <v>-0.9677</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3253</v>
+        <v>-0.9677</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7977</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>114</v>
@@ -2231,7 +2231,7 @@
         <v>216</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.123</v>
+        <v>-1.6376</v>
       </c>
       <c r="N39" t="n">
         <v>330</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.9518</v>
+        <v>-3.55</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.1235</v>
+        <v>-1.3512</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6199</v>
+        <v>-2.2407</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.9518</v>
+        <v>-3.55</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9518</v>
+        <v>-2.5887</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.9613</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9518</v>
+        <v>-2.5887</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.582</v>
+        <v>-1.346</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.9613</v>
       </c>
       <c r="K40" t="n">
         <v>135</v>
@@ -2277,7 +2277,7 @@
         <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.582</v>
+        <v>-2.3073</v>
       </c>
       <c r="N40" t="n">
         <v>215</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.7605</v>
+        <v>-3.8682</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.8119</v>
+        <v>-1.4723</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3405</v>
+        <v>-2.3843</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.7605</v>
+        <v>-3.8682</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2999</v>
+        <v>-1.9174</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.4606</v>
+        <v>-1.9508</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2999</v>
+        <v>-1.9174</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2999</v>
+        <v>-1.9174</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.4606</v>
+        <v>-1.9508</v>
       </c>
       <c r="K41" t="n">
         <v>114</v>
@@ -2323,7 +2323,7 @@
         <v>216</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.7605</v>
+        <v>-3.8682</v>
       </c>
       <c r="N41" t="n">
         <v>330</v>
@@ -2429,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0031</v>
+        <v>0.999</v>
       </c>
       <c r="J2" t="n">
-        <v>25.0775</v>
+        <v>24.975</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6249</v>
+        <v>0.6495</v>
       </c>
       <c r="J3" t="n">
-        <v>15.6225</v>
+        <v>16.2375</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5592</v>
+        <v>0.6039</v>
       </c>
       <c r="J4" t="n">
-        <v>13.98</v>
+        <v>15.0975</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.19</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4727</v>
+        <v>0.5326</v>
       </c>
       <c r="J5" t="n">
-        <v>11.8175</v>
+        <v>13.315</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1365</v>
+        <v>0.2091</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4125</v>
+        <v>5.2275</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.99</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0629</v>
+        <v>0.0192</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5725</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1184</v>
+        <v>-0.1101</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.96</v>
+        <v>-2.7525</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.32</v>
+        <v>-0.2243</v>
       </c>
       <c r="J9" t="n">
-        <v>-8</v>
+        <v>-5.6075</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3475</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.1175</v>
+        <v>-8.6875</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.3758</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.15</v>
+        <v>-9.395</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2989</v>
+        <v>0.2479</v>
       </c>
       <c r="J12" t="n">
-        <v>7.7714</v>
+        <v>6.4454</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2155</v>
+        <v>0.1686</v>
       </c>
       <c r="J13" t="n">
-        <v>5.603</v>
+        <v>4.3836</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0009</v>
+        <v>-0.0157</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0234</v>
+        <v>-0.4082</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1876</v>
+        <v>-0.1169</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.8776</v>
+        <v>-3.0394</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6369</v>
+        <v>-0.4229</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.5594</v>
+        <v>-10.9954</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5083</v>
+        <v>0.4405</v>
       </c>
       <c r="J17" t="n">
-        <v>13.2158</v>
+        <v>11.453</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4822</v>
+        <v>0.4171</v>
       </c>
       <c r="J18" t="n">
-        <v>12.5372</v>
+        <v>10.8446</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4689</v>
+        <v>0.4054</v>
       </c>
       <c r="J19" t="n">
-        <v>12.1914</v>
+        <v>10.5404</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0275</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.715</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.84</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3571</v>
+        <v>-0.2153</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.284599999999999</v>
+        <v>-5.5978</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>24.3825</v>
+        <v>24.4575</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.28</v>
       </c>
       <c r="I23" t="n">
-        <v>0.721</v>
+        <v>0.7389</v>
       </c>
       <c r="J23" t="n">
-        <v>18.025</v>
+        <v>18.4725</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6478</v>
       </c>
       <c r="J24" t="n">
-        <v>15.31</v>
+        <v>16.195</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4648</v>
+        <v>0.5303</v>
       </c>
       <c r="J25" t="n">
-        <v>11.62</v>
+        <v>13.2575</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1616</v>
+        <v>0.2362</v>
       </c>
       <c r="J26" t="n">
-        <v>4.04</v>
+        <v>5.905</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7187</v>
+        <v>0.8953</v>
       </c>
       <c r="J27" t="n">
-        <v>17.9675</v>
+        <v>22.3825</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2623</v>
+        <v>0.2691</v>
       </c>
       <c r="J28" t="n">
-        <v>6.5575</v>
+        <v>6.7275</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4483</v>
+        <v>-0.2909</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.2075</v>
+        <v>-7.2725</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.61</v>
+        <v>-0.4044</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.25</v>
+        <v>-10.11</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.48</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7698</v>
+        <v>-0.5238</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.245</v>
+        <v>-13.095</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5658</v>
+        <v>0.4265</v>
       </c>
       <c r="J32" t="n">
-        <v>15.2766</v>
+        <v>11.5155</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5152</v>
+        <v>0.3991</v>
       </c>
       <c r="J33" t="n">
-        <v>13.9104</v>
+        <v>10.7757</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4219</v>
+        <v>0.35</v>
       </c>
       <c r="J34" t="n">
-        <v>11.3913</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0249</v>
+        <v>0.0506</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6723</v>
+        <v>1.3662</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5538</v>
+        <v>-0.3595</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.9526</v>
+        <v>-9.7065</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.4639</v>
       </c>
       <c r="J37" t="n">
-        <v>16.2</v>
+        <v>12.5253</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2317</v>
+        <v>0.1905</v>
       </c>
       <c r="J38" t="n">
-        <v>6.2559</v>
+        <v>5.1435</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1398</v>
+        <v>0.1082</v>
       </c>
       <c r="J39" t="n">
-        <v>3.7746</v>
+        <v>2.9214</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.83</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3369</v>
+        <v>-0.2075</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.096299999999999</v>
+        <v>-5.6025</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6322</v>
+        <v>-0.419</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.0694</v>
+        <v>-11.313</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4441</v>
+        <v>0.4378</v>
       </c>
       <c r="J42" t="n">
-        <v>11.1025</v>
+        <v>10.945</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1916</v>
+        <v>0.186</v>
       </c>
       <c r="J43" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3282</v>
+        <v>-0.208</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.205</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4324</v>
+        <v>-0.2773</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.81</v>
+        <v>-6.9325</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5017</v>
+        <v>-0.3255</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.5425</v>
+        <v>-8.137499999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1727</v>
+        <v>0.8415</v>
       </c>
       <c r="J47" t="n">
-        <v>29.3175</v>
+        <v>21.0375</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1113</v>
+        <v>0.8035</v>
       </c>
       <c r="J48" t="n">
-        <v>27.7825</v>
+        <v>20.0875</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.5699</v>
       </c>
       <c r="J49" t="n">
-        <v>17.5775</v>
+        <v>14.2475</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1522</v>
+        <v>0.2305</v>
       </c>
       <c r="J50" t="n">
-        <v>3.805</v>
+        <v>5.7625</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2018</v>
+        <v>-0.1183</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.045</v>
+        <v>-2.9575</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.73</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9923</v>
+        <v>0.8921</v>
       </c>
       <c r="J52" t="n">
-        <v>27.7844</v>
+        <v>24.9788</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2679</v>
+        <v>0.3089</v>
       </c>
       <c r="J53" t="n">
-        <v>7.5012</v>
+        <v>8.6492</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2948</v>
+        <v>-0.1745</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.2544</v>
+        <v>-4.886</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.355</v>
+        <v>-0.2163</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.94</v>
+        <v>-6.0564</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.77</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4394</v>
+        <v>-0.2763</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.3032</v>
+        <v>-7.7364</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2543</v>
+        <v>0.8832</v>
       </c>
       <c r="J57" t="n">
-        <v>35.1204</v>
+        <v>24.7296</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.33</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9171</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>25.6788</v>
+        <v>18.6704</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1011</v>
+        <v>0.1444</v>
       </c>
       <c r="J59" t="n">
-        <v>2.8308</v>
+        <v>4.0432</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.87</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5242</v>
+        <v>-0.4618</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.6776</v>
+        <v>-12.9304</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.7516</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.3132</v>
+        <v>-21.0448</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9727</v>
+        <v>0.6973</v>
       </c>
       <c r="J62" t="n">
-        <v>28.2083</v>
+        <v>20.2217</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6445</v>
+        <v>0.4937</v>
       </c>
       <c r="J63" t="n">
-        <v>18.6905</v>
+        <v>14.3173</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.06</v>
       </c>
       <c r="I64" t="n">
-        <v>0.239</v>
+        <v>0.2191</v>
       </c>
       <c r="J64" t="n">
-        <v>6.931</v>
+        <v>6.3539</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6324</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.778</v>
+        <v>-18.3396</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7065</v>
+        <v>-0.6583</v>
       </c>
       <c r="J66" t="n">
-        <v>-20.4885</v>
+        <v>-19.0907</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.43</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6833</v>
+        <v>0.632</v>
       </c>
       <c r="J67" t="n">
-        <v>19.8157</v>
+        <v>18.328</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3993</v>
+        <v>0.4073</v>
       </c>
       <c r="J68" t="n">
-        <v>11.5797</v>
+        <v>11.8117</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3233</v>
+        <v>-0.1979</v>
       </c>
       <c r="J69" t="n">
-        <v>-9.3757</v>
+        <v>-5.7391</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4112</v>
+        <v>-0.2584</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.9248</v>
+        <v>-7.4936</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4932</v>
+        <v>-0.3167</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.3028</v>
+        <v>-9.1843</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3831</v>
+        <v>0.3266</v>
       </c>
       <c r="J72" t="n">
-        <v>10.3437</v>
+        <v>8.818199999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1274</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.4398</v>
+        <v>2.2815</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.347</v>
+        <v>-0.2193</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.369</v>
+        <v>-5.9211</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3622</v>
+        <v>-0.2294</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.779400000000001</v>
+        <v>-6.1938</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3919</v>
+        <v>-0.2492</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.5813</v>
+        <v>-6.7284</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.6528</v>
       </c>
       <c r="J77" t="n">
-        <v>25.8714</v>
+        <v>17.6256</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.407</v>
+        <v>0.3504</v>
       </c>
       <c r="J78" t="n">
-        <v>10.989</v>
+        <v>9.460800000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2742</v>
+        <v>0.2684</v>
       </c>
       <c r="J79" t="n">
-        <v>7.4034</v>
+        <v>7.2468</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1209</v>
       </c>
       <c r="J80" t="n">
-        <v>2.6244</v>
+        <v>3.2643</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4083</v>
+        <v>-0.2515</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.0241</v>
+        <v>-6.7905</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.41</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0998</v>
+        <v>0.7815</v>
       </c>
       <c r="J82" t="n">
-        <v>39.5928</v>
+        <v>28.134</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7664</v>
+        <v>0.5723</v>
       </c>
       <c r="J83" t="n">
-        <v>27.5904</v>
+        <v>20.6028</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2218</v>
+        <v>0.242</v>
       </c>
       <c r="J84" t="n">
-        <v>7.9848</v>
+        <v>8.712</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.5387</v>
       </c>
       <c r="J85" t="n">
-        <v>-21.4668</v>
+        <v>-19.3932</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.647</v>
+        <v>-0.592</v>
       </c>
       <c r="J86" t="n">
-        <v>-23.292</v>
+        <v>-21.312</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4699</v>
+        <v>0.4612</v>
       </c>
       <c r="J87" t="n">
-        <v>16.9164</v>
+        <v>16.6032</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J88" t="n">
-        <v>2.6064</v>
+        <v>2.4264</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2078</v>
+        <v>-0.1222</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.4808</v>
+        <v>-4.3992</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.89</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2423</v>
+        <v>-0.1444</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.722799999999999</v>
+        <v>-5.1984</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2589</v>
+        <v>-0.1552</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.320399999999999</v>
+        <v>-5.5872</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0029</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>36.1044</v>
+        <v>25.8552</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3199</v>
+        <v>0.302</v>
       </c>
       <c r="J93" t="n">
-        <v>11.5164</v>
+        <v>10.872</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2864</v>
+        <v>0.2735</v>
       </c>
       <c r="J94" t="n">
-        <v>10.3104</v>
+        <v>9.846</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1186</v>
+        <v>-0.0678</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.2696</v>
+        <v>-2.4408</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7147</v>
+        <v>-0.6652</v>
       </c>
       <c r="J96" t="n">
-        <v>-25.7292</v>
+        <v>-23.9472</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7587</v>
+        <v>0.6954</v>
       </c>
       <c r="J97" t="n">
-        <v>27.3132</v>
+        <v>25.0344</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.51</v>
       </c>
       <c r="I98" t="n">
-        <v>0.736</v>
+        <v>0.677</v>
       </c>
       <c r="J98" t="n">
-        <v>26.496</v>
+        <v>24.372</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0527</v>
+        <v>-0.0112</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.8972</v>
+        <v>-0.4032</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3365</v>
+        <v>-0.2015</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.114</v>
+        <v>-7.254</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.73</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5014</v>
+        <v>-0.3206</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.0504</v>
+        <v>-11.5416</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.44</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1264</v>
+        <v>0.8028</v>
       </c>
       <c r="J102" t="n">
-        <v>27.0336</v>
+        <v>19.2672</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6016</v>
+        <v>0.4874</v>
       </c>
       <c r="J103" t="n">
-        <v>14.4384</v>
+        <v>11.6976</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3572</v>
+        <v>0.3702</v>
       </c>
       <c r="J104" t="n">
-        <v>8.572800000000001</v>
+        <v>8.8848</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0008</v>
+        <v>0.0605</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.0192</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.342</v>
+        <v>-0.2693</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.208</v>
+        <v>-6.4632</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5084</v>
+        <v>0.4896</v>
       </c>
       <c r="J107" t="n">
-        <v>12.2016</v>
+        <v>11.7504</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.89</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1465</v>
+        <v>-0.1253</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.516</v>
+        <v>-3.0072</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4009</v>
+        <v>-0.265</v>
       </c>
       <c r="J109" t="n">
-        <v>-9.621600000000001</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4009</v>
+        <v>-0.265</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.621600000000001</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7977</v>
+        <v>-0.5452</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.1448</v>
+        <v>-13.0848</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9659</v>
+        <v>0.6938</v>
       </c>
       <c r="J112" t="n">
-        <v>28.977</v>
+        <v>20.814</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1112</v>
+        <v>-0.0648</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.336</v>
+        <v>-1.944</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.98</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1554</v>
+        <v>-0.1056</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.662</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1948</v>
+        <v>-0.1426</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.844</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1948</v>
+        <v>-0.1426</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.844</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4927</v>
       </c>
       <c r="J117" t="n">
-        <v>15.228</v>
+        <v>14.781</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.326</v>
+        <v>0.3566</v>
       </c>
       <c r="J118" t="n">
-        <v>9.779999999999999</v>
+        <v>10.698</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0593</v>
+        <v>-0.0238</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.779</v>
+        <v>-0.714</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1684</v>
+        <v>-0.0921</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.052</v>
+        <v>-2.763</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4061</v>
+        <v>-0.2533</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.183</v>
+        <v>-7.599</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0968</v>
+        <v>0.789</v>
       </c>
       <c r="J122" t="n">
-        <v>24.1296</v>
+        <v>17.358</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.42</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0549</v>
+        <v>0.763</v>
       </c>
       <c r="J123" t="n">
-        <v>23.2078</v>
+        <v>16.786</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.262</v>
+        <v>0.3266</v>
       </c>
       <c r="J124" t="n">
-        <v>5.764</v>
+        <v>7.1852</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2333</v>
+        <v>0.301</v>
       </c>
       <c r="J125" t="n">
-        <v>5.1326</v>
+        <v>6.622</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2977</v>
+        <v>-0.2185</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.5494</v>
+        <v>-4.807</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3318</v>
+        <v>0.3471</v>
       </c>
       <c r="J127" t="n">
-        <v>7.2996</v>
+        <v>7.6362</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0786</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.6258</v>
+        <v>-1.7292</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1107</v>
+        <v>-0.1025</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.4354</v>
+        <v>-2.255</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.6116</v>
+        <v>-0.407</v>
       </c>
       <c r="J130" t="n">
-        <v>-13.4552</v>
+        <v>-8.954000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.713</v>
+        <v>-0.4811</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.686</v>
+        <v>-10.5842</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6076</v>
+        <v>0.6283</v>
       </c>
       <c r="J132" t="n">
-        <v>21.266</v>
+        <v>21.9905</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6076</v>
+        <v>0.6283</v>
       </c>
       <c r="J133" t="n">
-        <v>21.266</v>
+        <v>21.9905</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6076</v>
+        <v>0.6283</v>
       </c>
       <c r="J134" t="n">
-        <v>21.266</v>
+        <v>21.9905</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5423</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>18.9805</v>
+        <v>20.377</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3982</v>
+        <v>0.4602</v>
       </c>
       <c r="J136" t="n">
-        <v>13.937</v>
+        <v>16.107</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.98</v>
       </c>
       <c r="I137" t="n">
-        <v>0.0046</v>
+        <v>-0.0217</v>
       </c>
       <c r="J137" t="n">
-        <v>0.161</v>
+        <v>-0.7595</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.91</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.138</v>
+        <v>-0.1108</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.83</v>
+        <v>-3.878</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1765</v>
+        <v>-0.1327</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.1775</v>
+        <v>-4.6445</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2616</v>
+        <v>-0.1733</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.156000000000001</v>
+        <v>-6.0655</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4501</v>
+        <v>-0.2917</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.7535</v>
+        <v>-10.2095</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9696</v>
       </c>
       <c r="J142" t="n">
-        <v>25.5684</v>
+        <v>25.2096</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6339</v>
+        <v>0.6214</v>
       </c>
       <c r="J143" t="n">
-        <v>16.4814</v>
+        <v>16.1564</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4999</v>
+        <v>0.4977</v>
       </c>
       <c r="J144" t="n">
-        <v>12.9974</v>
+        <v>12.9402</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0328</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.5506</v>
+        <v>-0.8528</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.369</v>
+        <v>-0.2979</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.593999999999999</v>
+        <v>-7.7454</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3906</v>
+        <v>0.4453</v>
       </c>
       <c r="J147" t="n">
-        <v>10.1556</v>
+        <v>11.5778</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1637</v>
+        <v>0.1663</v>
       </c>
       <c r="J148" t="n">
-        <v>4.2562</v>
+        <v>4.3238</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.147</v>
+        <v>-0.0861</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.822</v>
+        <v>-2.2386</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2716</v>
+        <v>-0.1646</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.0616</v>
+        <v>-4.2796</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3343</v>
+        <v>-0.2063</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.691800000000001</v>
+        <v>-5.3638</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5819</v>
+        <v>0.5585</v>
       </c>
       <c r="J152" t="n">
-        <v>17.457</v>
+        <v>16.755</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5555</v>
+        <v>0.5332</v>
       </c>
       <c r="J153" t="n">
-        <v>16.665</v>
+        <v>15.996</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3842</v>
+        <v>0.3769</v>
       </c>
       <c r="J154" t="n">
-        <v>11.526</v>
+        <v>11.307</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.05</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1366</v>
+        <v>0.1771</v>
       </c>
       <c r="J155" t="n">
-        <v>4.098</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2896</v>
+        <v>-0.2237</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.688000000000001</v>
+        <v>-6.711</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4672</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>14.016</v>
+        <v>16.407</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3836</v>
+        <v>0.4387</v>
       </c>
       <c r="J158" t="n">
-        <v>11.508</v>
+        <v>13.161</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1553</v>
+        <v>0.1618</v>
       </c>
       <c r="J159" t="n">
-        <v>4.659</v>
+        <v>4.854</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1927</v>
+        <v>-0.1117</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.781</v>
+        <v>-3.351</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6938</v>
+        <v>-0.4656</v>
       </c>
       <c r="J161" t="n">
-        <v>-20.814</v>
+        <v>-13.968</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4831</v>
+        <v>0.4321</v>
       </c>
       <c r="J162" t="n">
-        <v>14.493</v>
+        <v>12.963</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2284</v>
+        <v>0.1822</v>
       </c>
       <c r="J163" t="n">
-        <v>6.852</v>
+        <v>5.466</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0067</v>
+        <v>-0.017</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.201</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.263</v>
+        <v>-0.1616</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.89</v>
+        <v>-4.848</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6874</v>
+        <v>-0.4609</v>
       </c>
       <c r="J166" t="n">
-        <v>-20.622</v>
+        <v>-13.827</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6271</v>
       </c>
       <c r="J167" t="n">
-        <v>21.336</v>
+        <v>18.813</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3061</v>
+        <v>0.2561</v>
       </c>
       <c r="J168" t="n">
-        <v>9.183</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2581</v>
+        <v>0.2169</v>
       </c>
       <c r="J169" t="n">
-        <v>7.743</v>
+        <v>6.507</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1835</v>
+        <v>-0.0978</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.505</v>
+        <v>-2.934</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4966</v>
+        <v>-0.3175</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.898</v>
+        <v>-9.525</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6741</v>
+        <v>0.6427</v>
       </c>
       <c r="J172" t="n">
-        <v>20.223</v>
+        <v>19.281</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5457</v>
+        <v>0.5154</v>
       </c>
       <c r="J173" t="n">
-        <v>16.371</v>
+        <v>15.462</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1933</v>
+        <v>0.2136</v>
       </c>
       <c r="J174" t="n">
-        <v>5.799</v>
+        <v>6.408</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2432</v>
+        <v>-0.1833</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.296</v>
+        <v>-5.499</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.95</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2774</v>
+        <v>-0.2166</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.321999999999999</v>
+        <v>-6.498</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7277</v>
+        <v>0.9019</v>
       </c>
       <c r="J177" t="n">
-        <v>21.831</v>
+        <v>27.057</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1162</v>
+        <v>-0.0636</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.486</v>
+        <v>-1.908</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1758</v>
+        <v>-0.1005</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.274</v>
+        <v>-3.015</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.84</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3254</v>
+        <v>-0.1988</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.762</v>
+        <v>-5.964</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3554</v>
+        <v>-0.2193</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.662</v>
+        <v>-6.579</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.93</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>-1.4536</v>
+        <v>-1.6997</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1697</v>
+        <v>-0.1434</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.9031</v>
+        <v>-3.2982</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2213</v>
+        <v>-0.1752</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.0899</v>
+        <v>-4.0296</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4369</v>
+        <v>-0.2904</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.0487</v>
+        <v>-6.6792</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6056</v>
+        <v>-0.4036</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.9288</v>
+        <v>-9.2828</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.33</v>
       </c>
       <c r="I187" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J187" t="n">
-        <v>47.3639</v>
+        <v>42.1774</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.33</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8006</v>
+        <v>0.8379</v>
       </c>
       <c r="J188" t="n">
-        <v>18.4138</v>
+        <v>19.2717</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.26</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6065</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>13.9495</v>
+        <v>15.732</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5296</v>
+        <v>-0.4558</v>
       </c>
       <c r="J190" t="n">
-        <v>-12.1808</v>
+        <v>-10.4834</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9948</v>
+        <v>-0.969</v>
       </c>
       <c r="J191" t="n">
-        <v>-22.8804</v>
+        <v>-22.287</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4462</v>
+        <v>0.3714</v>
       </c>
       <c r="J192" t="n">
-        <v>12.9398</v>
+        <v>10.7706</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3466</v>
+        <v>0.2814</v>
       </c>
       <c r="J193" t="n">
-        <v>10.0514</v>
+        <v>8.160600000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.95</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1437</v>
+        <v>-0.0781</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.1673</v>
+        <v>-2.2649</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1437</v>
+        <v>-0.0781</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.1673</v>
+        <v>-2.2649</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4168</v>
+        <v>-0.2614</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.0872</v>
+        <v>-7.5806</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.23</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3831</v>
+        <v>0.3509</v>
       </c>
       <c r="J197" t="n">
-        <v>11.1099</v>
+        <v>10.1761</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3239</v>
+        <v>0.2976</v>
       </c>
       <c r="J198" t="n">
-        <v>9.3931</v>
+        <v>8.6304</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.19</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3239</v>
+        <v>0.2976</v>
       </c>
       <c r="J199" t="n">
-        <v>9.3931</v>
+        <v>8.6304</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1802</v>
+        <v>0.1871</v>
       </c>
       <c r="J200" t="n">
-        <v>5.2258</v>
+        <v>5.4259</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2435</v>
+        <v>-0.1366</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.0615</v>
+        <v>-3.9614</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2162</v>
+        <v>0.2141</v>
       </c>
       <c r="J202" t="n">
-        <v>6.2698</v>
+        <v>6.2089</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>0.138</v>
+        <v>0.1184</v>
       </c>
       <c r="J203" t="n">
-        <v>4.002</v>
+        <v>3.4336</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.0445</v>
+        <v>-1.9169</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2897</v>
+        <v>-0.1859</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.401300000000001</v>
+        <v>-5.3911</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6533</v>
+        <v>-0.4357</v>
       </c>
       <c r="J206" t="n">
-        <v>-18.9457</v>
+        <v>-12.6353</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2967</v>
+        <v>1.1877</v>
       </c>
       <c r="J207" t="n">
-        <v>37.6043</v>
+        <v>34.4433</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.23</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6387</v>
+        <v>0.6372</v>
       </c>
       <c r="J208" t="n">
-        <v>18.5223</v>
+        <v>18.4788</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.13</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3403</v>
+        <v>0.3911</v>
       </c>
       <c r="J209" t="n">
-        <v>9.8687</v>
+        <v>11.3419</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0529</v>
+        <v>0.0139</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.5341</v>
+        <v>0.4031</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.95</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3182</v>
+        <v>-0.2428</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.2278</v>
+        <v>-7.0412</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1753</v>
+        <v>1.105</v>
       </c>
       <c r="J212" t="n">
-        <v>34.0837</v>
+        <v>32.045</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.08</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2431</v>
+        <v>0.2686</v>
       </c>
       <c r="J213" t="n">
-        <v>7.0499</v>
+        <v>7.7894</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2086</v>
+        <v>0.2395</v>
       </c>
       <c r="J214" t="n">
-        <v>6.0494</v>
+        <v>6.9455</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2181</v>
+        <v>-0.1543</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.3249</v>
+        <v>-4.4747</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4401</v>
+        <v>-0.3756</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.7629</v>
+        <v>-10.8924</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5085</v>
+        <v>0.6012</v>
       </c>
       <c r="J217" t="n">
-        <v>14.7465</v>
+        <v>17.4348</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3409</v>
+        <v>0.3841</v>
       </c>
       <c r="J218" t="n">
-        <v>9.886100000000001</v>
+        <v>11.1389</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1537</v>
+        <v>-0.0877</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.4573</v>
+        <v>-2.5433</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2266</v>
+        <v>-0.1338</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.5714</v>
+        <v>-3.8802</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.68</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5454</v>
+        <v>-0.3547</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.8166</v>
+        <v>-10.2863</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9549</v>
+        <v>0.9263</v>
       </c>
       <c r="J222" t="n">
-        <v>34.3764</v>
+        <v>33.3468</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9099</v>
+        <v>0.8782</v>
       </c>
       <c r="J223" t="n">
-        <v>32.7564</v>
+        <v>31.6152</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.85</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5339</v>
+        <v>-0.486</v>
       </c>
       <c r="J224" t="n">
-        <v>-19.2204</v>
+        <v>-17.496</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.78</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.7139</v>
+        <v>-0.6704</v>
       </c>
       <c r="J225" t="n">
-        <v>-25.7004</v>
+        <v>-24.1344</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8798</v>
+        <v>-0.8467</v>
       </c>
       <c r="J226" t="n">
-        <v>-31.6728</v>
+        <v>-30.4812</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.621</v>
+        <v>0.7602</v>
       </c>
       <c r="J227" t="n">
-        <v>22.356</v>
+        <v>27.3672</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5967</v>
+        <v>0.7279</v>
       </c>
       <c r="J228" t="n">
-        <v>21.4812</v>
+        <v>26.2044</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.18</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3124</v>
+        <v>0.373</v>
       </c>
       <c r="J229" t="n">
-        <v>11.2464</v>
+        <v>13.428</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.335</v>
+        <v>-0.2007</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.06</v>
+        <v>-7.2252</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4741</v>
+        <v>-0.3007</v>
       </c>
       <c r="J231" t="n">
-        <v>-17.0676</v>
+        <v>-10.8252</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2866</v>
+        <v>1.2006</v>
       </c>
       <c r="J232" t="n">
-        <v>27.0186</v>
+        <v>25.2126</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1869</v>
+        <v>1.1406</v>
       </c>
       <c r="J233" t="n">
-        <v>24.9249</v>
+        <v>23.9526</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0177</v>
+        <v>1.0427</v>
       </c>
       <c r="J234" t="n">
-        <v>21.3717</v>
+        <v>21.8967</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.8643</v>
+        <v>0.9484</v>
       </c>
       <c r="J235" t="n">
-        <v>18.1503</v>
+        <v>19.9164</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.04</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.0129</v>
+        <v>0.0732</v>
       </c>
       <c r="J236" t="n">
-        <v>-0.2709</v>
+        <v>1.5372</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.91</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0645</v>
+        <v>-0.0801</v>
       </c>
       <c r="J237" t="n">
-        <v>-1.3545</v>
+        <v>-1.6821</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.87</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1331</v>
+        <v>-0.1274</v>
       </c>
       <c r="J238" t="n">
-        <v>-2.7951</v>
+        <v>-2.6754</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.74</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3473</v>
+        <v>-0.2629</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.2933</v>
+        <v>-5.5209</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.63</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5393</v>
+        <v>-0.3638</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.3253</v>
+        <v>-7.6398</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.43</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8041</v>
+        <v>-0.5505</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.8861</v>
+        <v>-11.5605</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2928</v>
+        <v>1.1943</v>
       </c>
       <c r="J242" t="n">
-        <v>28.4416</v>
+        <v>26.2746</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>1.028</v>
+        <v>1.0298</v>
       </c>
       <c r="J243" t="n">
-        <v>22.616</v>
+        <v>22.6556</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.28</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6582</v>
+        <v>0.7292</v>
       </c>
       <c r="J244" t="n">
-        <v>14.4804</v>
+        <v>16.0424</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.24</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5562</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>12.2364</v>
+        <v>14.0272</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2136</v>
+        <v>-0.1277</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.6992</v>
+        <v>-2.8094</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6293</v>
+        <v>0.7831</v>
       </c>
       <c r="J247" t="n">
-        <v>13.8446</v>
+        <v>17.2282</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.71</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4181</v>
+        <v>-0.2911</v>
       </c>
       <c r="J248" t="n">
-        <v>-9.1982</v>
+        <v>-6.4042</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.5996</v>
+        <v>-0.4028</v>
       </c>
       <c r="J249" t="n">
-        <v>-13.1912</v>
+        <v>-8.861599999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.58</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6133</v>
+        <v>-0.4122</v>
       </c>
       <c r="J250" t="n">
-        <v>-13.4926</v>
+        <v>-9.0684</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7815</v>
+        <v>-0.5334</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.193</v>
+        <v>-11.7348</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>1.8231</v>
+        <v>1.5464</v>
       </c>
       <c r="J252" t="n">
-        <v>41.9313</v>
+        <v>35.5672</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.58</v>
       </c>
       <c r="I253" t="n">
-        <v>1.2764</v>
+        <v>1.1971</v>
       </c>
       <c r="J253" t="n">
-        <v>29.3572</v>
+        <v>27.5333</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.49</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0924</v>
+        <v>1.0895</v>
       </c>
       <c r="J254" t="n">
-        <v>25.1252</v>
+        <v>25.0585</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2111</v>
+        <v>0.3081</v>
       </c>
       <c r="J255" t="n">
-        <v>4.8553</v>
+        <v>7.0863</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.03</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.052</v>
+        <v>0.0338</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.196</v>
+        <v>0.7774</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.79</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2428</v>
+        <v>-0.2051</v>
       </c>
       <c r="J257" t="n">
-        <v>-5.5844</v>
+        <v>-4.7173</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.68</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.4264</v>
+        <v>-0.3128</v>
       </c>
       <c r="J258" t="n">
-        <v>-9.8072</v>
+        <v>-7.1944</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.4706</v>
+        <v>-0.3302</v>
       </c>
       <c r="J259" t="n">
-        <v>-10.8238</v>
+        <v>-7.5946</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.488</v>
+        <v>-0.3392</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.224</v>
+        <v>-7.8016</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5662</v>
+        <v>-0.3852</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.0226</v>
+        <v>-8.8596</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1756</v>
+        <v>1.1165</v>
       </c>
       <c r="J262" t="n">
-        <v>25.8632</v>
+        <v>24.563</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0304</v>
+        <v>1.0242</v>
       </c>
       <c r="J263" t="n">
-        <v>22.6688</v>
+        <v>22.5324</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7336</v>
+        <v>0.7579</v>
       </c>
       <c r="J264" t="n">
-        <v>16.1392</v>
+        <v>16.6738</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.05</v>
       </c>
       <c r="I265" t="n">
-        <v>0.0625</v>
+        <v>0.1391</v>
       </c>
       <c r="J265" t="n">
-        <v>1.375</v>
+        <v>3.0602</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.0422</v>
+        <v>0.0341</v>
       </c>
       <c r="J266" t="n">
-        <v>-0.9284</v>
+        <v>0.7502</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.23</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4457</v>
+        <v>0.5142</v>
       </c>
       <c r="J267" t="n">
-        <v>9.805400000000001</v>
+        <v>11.3124</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1782</v>
+        <v>0.1756</v>
       </c>
       <c r="J268" t="n">
-        <v>3.9204</v>
+        <v>3.8632</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1692</v>
+        <v>-0.1059</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.7224</v>
+        <v>-2.3298</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3544</v>
+        <v>-0.2223</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.7968</v>
+        <v>-4.8906</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.7</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5093</v>
+        <v>-0.3297</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.2046</v>
+        <v>-7.2534</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.25</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7368</v>
+        <v>0.7103</v>
       </c>
       <c r="J272" t="n">
-        <v>19.8936</v>
+        <v>19.1781</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6634</v>
+        <v>0.6363</v>
       </c>
       <c r="J273" t="n">
-        <v>17.9118</v>
+        <v>17.1801</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2872</v>
+        <v>0.2971</v>
       </c>
       <c r="J274" t="n">
-        <v>7.7544</v>
+        <v>8.021699999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1422</v>
+        <v>0.1789</v>
       </c>
       <c r="J275" t="n">
-        <v>3.8394</v>
+        <v>4.8303</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5998</v>
+        <v>-0.5415</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.1946</v>
+        <v>-14.6205</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4564</v>
+        <v>0.532</v>
       </c>
       <c r="J277" t="n">
-        <v>12.3228</v>
+        <v>14.364</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4564</v>
+        <v>0.532</v>
       </c>
       <c r="J278" t="n">
-        <v>12.3228</v>
+        <v>14.364</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J279" t="n">
-        <v>1.9548</v>
+        <v>1.8198</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.564</v>
+        <v>-2.0277</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.49</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7743</v>
+        <v>-0.5276</v>
       </c>
       <c r="J281" t="n">
-        <v>-20.9061</v>
+        <v>-14.2452</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.41</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0998</v>
+        <v>1.055</v>
       </c>
       <c r="J282" t="n">
-        <v>29.6946</v>
+        <v>28.485</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4859</v>
+        <v>0.4608</v>
       </c>
       <c r="J283" t="n">
-        <v>13.1193</v>
+        <v>12.4416</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3026</v>
+        <v>0.2985</v>
       </c>
       <c r="J284" t="n">
-        <v>8.170199999999999</v>
+        <v>8.0595</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.88</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4904</v>
+        <v>-0.4288</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.2408</v>
+        <v>-11.5776</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5175</v>
+        <v>-0.4568</v>
       </c>
       <c r="J286" t="n">
-        <v>-13.9725</v>
+        <v>-12.3336</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.09</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2261</v>
+        <v>0.2364</v>
       </c>
       <c r="J287" t="n">
-        <v>6.1047</v>
+        <v>6.3828</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1524</v>
+        <v>0.1484</v>
       </c>
       <c r="J288" t="n">
-        <v>4.1148</v>
+        <v>4.0068</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0261</v>
+        <v>0.0061</v>
       </c>
       <c r="J289" t="n">
-        <v>0.7047</v>
+        <v>0.1647</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1771</v>
+        <v>-0.1075</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.7817</v>
+        <v>-2.9025</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.74</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4587</v>
+        <v>-0.2933</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.3849</v>
+        <v>-7.9191</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.78</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1758</v>
+        <v>-0.1645</v>
       </c>
       <c r="J292" t="n">
-        <v>-3.3402</v>
+        <v>-3.1255</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.5017</v>
+        <v>-0.3889</v>
       </c>
       <c r="J293" t="n">
-        <v>-9.532299999999999</v>
+        <v>-7.3891</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.48</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.673</v>
+        <v>-0.4696</v>
       </c>
       <c r="J294" t="n">
-        <v>-12.787</v>
+        <v>-8.9224</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.43</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.7487</v>
+        <v>-0.517</v>
       </c>
       <c r="J295" t="n">
-        <v>-14.2253</v>
+        <v>-9.823</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.8054</v>
+        <v>-0.5557</v>
       </c>
       <c r="J296" t="n">
-        <v>-15.3026</v>
+        <v>-10.5583</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.26</v>
       </c>
       <c r="I297" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J297" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.8</v>
       </c>
       <c r="I298" t="n">
-        <v>1.6177</v>
+        <v>1.4254</v>
       </c>
       <c r="J298" t="n">
-        <v>30.7363</v>
+        <v>27.0826</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.34</v>
       </c>
       <c r="I299" t="n">
-        <v>0.672</v>
+        <v>0.8096</v>
       </c>
       <c r="J299" t="n">
-        <v>12.768</v>
+        <v>15.3824</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.3</v>
       </c>
       <c r="I300" t="n">
-        <v>0.587</v>
+        <v>0.7197</v>
       </c>
       <c r="J300" t="n">
-        <v>11.153</v>
+        <v>13.6743</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.22</v>
       </c>
       <c r="I301" t="n">
-        <v>0.4111</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>7.8109</v>
+        <v>10.1042</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.16</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3287</v>
+        <v>0.3676</v>
       </c>
       <c r="J302" t="n">
-        <v>9.861000000000001</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2494</v>
+        <v>0.2698</v>
       </c>
       <c r="J303" t="n">
-        <v>7.482</v>
+        <v>8.093999999999999</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1793</v>
+        <v>0.1864</v>
       </c>
       <c r="J304" t="n">
-        <v>5.379</v>
+        <v>5.592</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.274</v>
+        <v>-0.1655</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.220000000000001</v>
+        <v>-4.965</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4783</v>
+        <v>-0.3062</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.349</v>
+        <v>-9.186</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.33</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9204</v>
+        <v>0.9013</v>
       </c>
       <c r="J307" t="n">
-        <v>27.612</v>
+        <v>27.039</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.07</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2103</v>
+        <v>0.2399</v>
       </c>
       <c r="J308" t="n">
-        <v>6.309</v>
+        <v>7.197</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1408</v>
+        <v>0.1784</v>
       </c>
       <c r="J309" t="n">
-        <v>4.224</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.04</v>
       </c>
       <c r="I310" t="n">
-        <v>0.105</v>
+        <v>0.1458</v>
       </c>
       <c r="J310" t="n">
-        <v>3.15</v>
+        <v>4.374</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.97</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2171</v>
+        <v>-0.1538</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.513</v>
+        <v>-4.614</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6972/event_6972_evp_summary.xlsx
+++ b/database/event/6972/event_6972_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4569</v>
+        <v>5.3536</v>
       </c>
       <c r="C2" t="n">
-        <v>2.077</v>
+        <v>2.0376</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8255</v>
+        <v>1.8129</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4569</v>
+        <v>5.3536</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0884</v>
+        <v>3.0106</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3685</v>
+        <v>2.343</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3953</v>
+        <v>5.0388</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8053</v>
+        <v>2.7209</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3685</v>
+        <v>2.343</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1738</v>
+        <v>5.0639</v>
       </c>
       <c r="N2" t="n">
         <v>274</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2681</v>
+        <v>5.2892</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0051</v>
+        <v>2.0131</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7403</v>
+        <v>1.7835</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2681</v>
+        <v>5.2892</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0532</v>
+        <v>1.909</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2149</v>
+        <v>3.3802</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0532</v>
+        <v>1.909</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0532</v>
+        <v>1.909</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2149</v>
+        <v>3.3802</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>216</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2681</v>
+        <v>5.2892</v>
       </c>
       <c r="N3" t="n">
         <v>330</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1581</v>
+        <v>5.1422</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9632</v>
+        <v>1.9572</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6906</v>
+        <v>1.7166</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1581</v>
+        <v>5.1422</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1593</v>
+        <v>3.1155</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9988</v>
+        <v>2.0267</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6451</v>
+        <v>5.3849</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9352</v>
+        <v>2.9078</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9988</v>
+        <v>2.0267</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -621,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>4.934</v>
+        <v>4.9345</v>
       </c>
       <c r="N4" t="n">
         <v>274</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1216</v>
+        <v>5.1087</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9493</v>
+        <v>1.9444</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6741</v>
+        <v>1.7014</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1216</v>
+        <v>5.1087</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6418</v>
+        <v>3.5377</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4798</v>
+        <v>1.571</v>
       </c>
       <c r="H5" t="n">
-        <v>7.3453</v>
+        <v>6.7779</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8192</v>
+        <v>3.66</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4798</v>
+        <v>1.571</v>
       </c>
       <c r="K5" t="n">
         <v>106</v>
@@ -667,7 +667,7 @@
         <v>168</v>
       </c>
       <c r="M5" t="n">
-        <v>5.298999999999999</v>
+        <v>5.231</v>
       </c>
       <c r="N5" t="n">
         <v>274</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3087</v>
+        <v>4.2913</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6399</v>
+        <v>1.6333</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3071</v>
+        <v>1.3293</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3087</v>
+        <v>4.2913</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6881</v>
+        <v>3.5915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6206</v>
+        <v>0.6998</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5084</v>
+        <v>6.9557</v>
       </c>
       <c r="I6" t="n">
-        <v>3.904</v>
+        <v>3.756</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6206</v>
+        <v>0.6998</v>
       </c>
       <c r="K6" t="n">
         <v>135</v>
@@ -713,7 +713,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5246</v>
+        <v>4.4558</v>
       </c>
       <c r="N6" t="n">
         <v>215</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1218</v>
+        <v>4.2569</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5688</v>
+        <v>1.6202</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2228</v>
+        <v>1.3136</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1218</v>
+        <v>4.2569</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0877</v>
+        <v>3.1105</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0341</v>
+        <v>1.1464</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3928</v>
+        <v>5.3684</v>
       </c>
       <c r="I7" t="n">
-        <v>2.804</v>
+        <v>2.8989</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0341</v>
+        <v>1.1464</v>
       </c>
       <c r="K7" t="n">
         <v>135</v>
@@ -759,7 +759,7 @@
         <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8381</v>
+        <v>4.0453</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1889</v>
+        <v>3.1225</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2137</v>
+        <v>1.1885</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8016</v>
+        <v>0.7972</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1889</v>
+        <v>3.1225</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3402</v>
+        <v>2.2848</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8487</v>
+        <v>0.8377</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7591</v>
+        <v>2.6443</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4346</v>
+        <v>1.4279</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8487</v>
+        <v>0.8377</v>
       </c>
       <c r="K8" t="n">
         <v>106</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2833</v>
+        <v>2.2656</v>
       </c>
       <c r="N8" t="n">
         <v>274</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9366</v>
+        <v>2.8786</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1177</v>
+        <v>1.0956</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6877</v>
+        <v>0.6862</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9366</v>
+        <v>2.8786</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8544</v>
+        <v>2.7916</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0822</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>4.571</v>
+        <v>4.3162</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3767</v>
+        <v>2.3307</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0822</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>135</v>
@@ -851,7 +851,7 @@
         <v>80</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4589</v>
+        <v>2.4177</v>
       </c>
       <c r="N9" t="n">
         <v>215</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.76</v>
+        <v>2.8594</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0505</v>
+        <v>1.0883</v>
       </c>
       <c r="D10" t="n">
-        <v>0.608</v>
+        <v>0.6775</v>
       </c>
       <c r="E10" t="n">
-        <v>2.76</v>
+        <v>2.8594</v>
       </c>
       <c r="F10" t="n">
-        <v>1.575</v>
+        <v>1.4091</v>
       </c>
       <c r="G10" t="n">
-        <v>1.185</v>
+        <v>1.4503</v>
       </c>
       <c r="H10" t="n">
-        <v>1.575</v>
+        <v>1.4091</v>
       </c>
       <c r="I10" t="n">
-        <v>1.575</v>
+        <v>1.4454</v>
       </c>
       <c r="J10" t="n">
-        <v>1.185</v>
+        <v>1.4503</v>
       </c>
       <c r="K10" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L10" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="M10" t="n">
-        <v>2.76</v>
+        <v>2.8957</v>
       </c>
       <c r="N10" t="n">
-        <v>164</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7028</v>
+        <v>2.7888</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0287</v>
+        <v>1.0614</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6453</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7028</v>
+        <v>2.7888</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4109</v>
+        <v>1.4762</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2919</v>
+        <v>1.3126</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4109</v>
+        <v>1.4762</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4689</v>
+        <v>1.4762</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2919</v>
+        <v>1.3126</v>
       </c>
       <c r="K11" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L11" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7608</v>
+        <v>2.7888</v>
       </c>
       <c r="N11" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5961</v>
+        <v>2.3851</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9881</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.534</v>
+        <v>0.4615</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5961</v>
+        <v>2.3851</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5961</v>
+        <v>-0.6149</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5961</v>
+        <v>-0.6149</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5961</v>
+        <v>-0.6149</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5961</v>
+        <v>2.3851</v>
       </c>
       <c r="N12" t="n">
-        <v>133</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2661</v>
+        <v>2.3806</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8625</v>
+        <v>0.9061</v>
       </c>
       <c r="D13" t="n">
-        <v>0.385</v>
+        <v>0.4595</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2661</v>
+        <v>2.3806</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4648</v>
+        <v>1.4292</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8013</v>
+        <v>0.9514</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4648</v>
+        <v>1.4292</v>
       </c>
       <c r="I13" t="n">
-        <v>1.525</v>
+        <v>1.466</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8013</v>
+        <v>0.9514</v>
       </c>
       <c r="K13" t="n">
         <v>130</v>
@@ -1035,7 +1035,7 @@
         <v>144</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3263</v>
+        <v>2.4174</v>
       </c>
       <c r="N13" t="n">
         <v>274</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1531</v>
+        <v>2.3636</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8195</v>
+        <v>0.8996</v>
       </c>
       <c r="D14" t="n">
-        <v>0.334</v>
+        <v>0.4518</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1531</v>
+        <v>2.3636</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6219</v>
+        <v>2.3636</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5312</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6219</v>
+        <v>2.4483</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6219</v>
+        <v>2.4483</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5312</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="L14" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1531</v>
+        <v>2.4483</v>
       </c>
       <c r="N14" t="n">
-        <v>330</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1451</v>
+        <v>2.2357</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8164</v>
+        <v>0.8509</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3304</v>
+        <v>0.3935</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1451</v>
+        <v>2.2357</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.649</v>
+        <v>0.5401</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7941</v>
+        <v>1.6956</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.649</v>
+        <v>0.5401</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.649</v>
+        <v>0.5401</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7941</v>
+        <v>1.6956</v>
       </c>
       <c r="K15" t="n">
         <v>114</v>
@@ -1127,7 +1127,7 @@
         <v>216</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1451</v>
+        <v>2.2357</v>
       </c>
       <c r="N15" t="n">
         <v>330</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0371</v>
+        <v>1.9513</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7753</v>
+        <v>0.7427</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2816</v>
+        <v>0.2641</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0371</v>
+        <v>1.9513</v>
       </c>
       <c r="F16" t="n">
-        <v>1.783</v>
+        <v>1.697</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2541</v>
+        <v>0.2543</v>
       </c>
       <c r="H16" t="n">
-        <v>1.783</v>
+        <v>1.697</v>
       </c>
       <c r="I16" t="n">
-        <v>1.783</v>
+        <v>1.697</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2541</v>
+        <v>0.2543</v>
       </c>
       <c r="K16" t="n">
         <v>135</v>
@@ -1173,7 +1173,7 @@
         <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0371</v>
+        <v>1.9513</v>
       </c>
       <c r="N16" t="n">
         <v>187</v>
@@ -1182,90 +1182,90 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9127</v>
+        <v>1.8843</v>
       </c>
       <c r="C17" t="n">
-        <v>0.728</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2255</v>
+        <v>0.2336</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9127</v>
+        <v>1.8843</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9127</v>
+        <v>1.7956</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9127</v>
+        <v>1.7956</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9127</v>
+        <v>0.9696</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="K17" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9127</v>
+        <v>1.0583</v>
       </c>
       <c r="N17" t="n">
-        <v>119</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8914</v>
+        <v>1.8773</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7199</v>
+        <v>0.7145</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2159</v>
+        <v>0.2304</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8914</v>
+        <v>1.8773</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8034</v>
+        <v>2.0011</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08799999999999999</v>
+        <v>-0.1238</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8034</v>
+        <v>2.0011</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9377</v>
+        <v>2.0527</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08799999999999999</v>
+        <v>-0.1238</v>
       </c>
       <c r="K18" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L18" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0257</v>
+        <v>1.9289</v>
       </c>
       <c r="N18" t="n">
         <v>274</v>
@@ -1274,277 +1274,277 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.787</v>
+        <v>1.8757</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6802</v>
+        <v>0.7139</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1687</v>
+        <v>0.2297</v>
       </c>
       <c r="E19" t="n">
-        <v>1.787</v>
+        <v>1.8757</v>
       </c>
       <c r="F19" t="n">
-        <v>1.375</v>
+        <v>1.8757</v>
       </c>
       <c r="G19" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.375</v>
+        <v>1.8757</v>
       </c>
       <c r="I19" t="n">
-        <v>1.375</v>
+        <v>1.8757</v>
       </c>
       <c r="J19" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="L19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.787</v>
+        <v>1.8757</v>
       </c>
       <c r="N19" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7456</v>
+        <v>1.8127</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6644</v>
+        <v>0.6899</v>
       </c>
       <c r="D20" t="n">
-        <v>0.15</v>
+        <v>0.201</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7456</v>
+        <v>1.8127</v>
       </c>
       <c r="F20" t="n">
-        <v>1.891</v>
+        <v>1.3353</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1454</v>
+        <v>0.4774</v>
       </c>
       <c r="H20" t="n">
-        <v>1.891</v>
+        <v>1.3353</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9688</v>
+        <v>1.3353</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1454</v>
+        <v>0.4774</v>
       </c>
       <c r="K20" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L20" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8234</v>
+        <v>1.8127</v>
       </c>
       <c r="N20" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6818</v>
+        <v>1.6882</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6401</v>
+        <v>0.6425</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1212</v>
+        <v>0.1443</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6818</v>
+        <v>1.6882</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4285</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7467</v>
+        <v>1.7606</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4285</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4285</v>
+        <v>-0.0743</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7467</v>
+        <v>1.7606</v>
       </c>
       <c r="K21" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="L21" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6818</v>
+        <v>1.6863</v>
       </c>
       <c r="N21" t="n">
-        <v>164</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6094</v>
+        <v>1.5636</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6126</v>
+        <v>0.5951</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0885</v>
+        <v>0.0876</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6094</v>
+        <v>1.5636</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0209</v>
+        <v>2.3258</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6303</v>
+        <v>-0.7622</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0209</v>
+        <v>2.3655</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0218</v>
+        <v>2.3655</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6303</v>
+        <v>-0.7622</v>
       </c>
       <c r="K22" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L22" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6085</v>
+        <v>1.6033</v>
       </c>
       <c r="N22" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4137</v>
+        <v>1.3657</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5381</v>
+        <v>0.5198</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002</v>
+        <v>-0.0025</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4137</v>
+        <v>1.3657</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5502</v>
+        <v>1.3657</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1365</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5502</v>
+        <v>1.3657</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5502</v>
+        <v>1.3657</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1365</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4137</v>
+        <v>1.3657</v>
       </c>
       <c r="N23" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4026</v>
+        <v>1.3255</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0048</v>
+        <v>-0.0208</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4026</v>
+        <v>1.3255</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4026</v>
+        <v>1.4771</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.1516</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4026</v>
+        <v>1.4771</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4026</v>
+        <v>1.4771</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.1516</v>
       </c>
       <c r="K24" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4026</v>
+        <v>1.3255</v>
       </c>
       <c r="N24" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6007</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2286</v>
+        <v>0.2212</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3668</v>
+        <v>-0.3597</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6007</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4654</v>
+        <v>0.4118</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1353</v>
+        <v>0.1693</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4654</v>
+        <v>0.4118</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4845</v>
+        <v>0.4224</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1353</v>
+        <v>0.1693</v>
       </c>
       <c r="K25" t="n">
         <v>130</v>
@@ -1587,7 +1587,7 @@
         <v>144</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6198</v>
+        <v>0.5917</v>
       </c>
       <c r="N25" t="n">
         <v>274</v>
@@ -1596,35 +1596,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4781</v>
+        <v>0.435</v>
       </c>
       <c r="C26" t="n">
-        <v>0.182</v>
+        <v>0.1656</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4222</v>
+        <v>-0.4262</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4781</v>
+        <v>0.435</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1548</v>
+        <v>0.3764</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3233</v>
+        <v>0.0586</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1548</v>
+        <v>0.3764</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1548</v>
+        <v>0.3764</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3233</v>
+        <v>0.0586</v>
       </c>
       <c r="K26" t="n">
         <v>135</v>
@@ -1633,7 +1633,7 @@
         <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4781</v>
+        <v>0.435</v>
       </c>
       <c r="N26" t="n">
         <v>187</v>
@@ -1642,35 +1642,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4144</v>
+        <v>0.4341</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1577</v>
+        <v>0.1652</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4509</v>
+        <v>-0.4266</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4144</v>
+        <v>0.4341</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4028</v>
+        <v>0.1193</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0116</v>
+        <v>0.3148</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4028</v>
+        <v>0.1193</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4028</v>
+        <v>0.1193</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0116</v>
+        <v>0.3148</v>
       </c>
       <c r="K27" t="n">
         <v>135</v>
@@ -1679,7 +1679,7 @@
         <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4144</v>
+        <v>0.4341</v>
       </c>
       <c r="N27" t="n">
         <v>187</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09</v>
+        <v>0.0408</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0343</v>
+        <v>0.0155</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5974</v>
+        <v>-0.6056</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09</v>
+        <v>0.0408</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09</v>
+        <v>0.0408</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09</v>
+        <v>0.0408</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09</v>
+        <v>0.0408</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.09</v>
+        <v>0.0408</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2212</v>
+        <v>-0.31</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0842</v>
+        <v>-0.118</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7379</v>
+        <v>-0.7653</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2212</v>
+        <v>-0.31</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3644</v>
+        <v>0.3029</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5856</v>
+        <v>-0.6129</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3644</v>
+        <v>0.3029</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3644</v>
+        <v>0.3029</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5856</v>
+        <v>-0.6129</v>
       </c>
       <c r="K29" t="n">
         <v>104</v>
@@ -1771,7 +1771,7 @@
         <v>60</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2212</v>
+        <v>-0.31</v>
       </c>
       <c r="N29" t="n">
         <v>164</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3151</v>
+        <v>-0.3405</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1199</v>
+        <v>-0.1296</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7803</v>
+        <v>-0.7792</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3151</v>
+        <v>-0.3405</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3151</v>
+        <v>-0.3405</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3151</v>
+        <v>-0.3405</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3151</v>
+        <v>-0.3405</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3151</v>
+        <v>-0.3405</v>
       </c>
       <c r="N30" t="n">
         <v>119</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3456</v>
+        <v>-0.375</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1315</v>
+        <v>-0.1427</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.794</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3456</v>
+        <v>-0.375</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3456</v>
+        <v>-0.375</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3456</v>
+        <v>-0.375</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3456</v>
+        <v>-0.375</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3456</v>
+        <v>-0.375</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4507</v>
+        <v>-0.4534</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1715</v>
+        <v>-0.1726</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8415</v>
+        <v>-0.8306</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4507</v>
+        <v>-0.4534</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4507</v>
+        <v>-0.9378</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.4844</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4507</v>
+        <v>-0.9378</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4507</v>
+        <v>-0.5064</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.4844</v>
       </c>
       <c r="K32" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4507</v>
+        <v>-0.02199999999999996</v>
       </c>
       <c r="N32" t="n">
-        <v>133</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7435</v>
+        <v>-0.4931</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.283</v>
+        <v>-0.1877</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9737</v>
+        <v>-0.8487</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7435</v>
+        <v>-0.4931</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.1815</v>
+        <v>-0.4931</v>
       </c>
       <c r="G33" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.1815</v>
+        <v>-0.4931</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6143</v>
+        <v>-0.4931</v>
       </c>
       <c r="J33" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1763</v>
+        <v>-0.4931</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8026</v>
+        <v>-0.8246</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3055</v>
+        <v>-0.3139</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0003</v>
+        <v>-0.9996</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8026</v>
+        <v>-0.8246</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8026</v>
+        <v>-0.8246</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8026</v>
+        <v>-0.8246</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8026</v>
+        <v>-0.8246</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8026</v>
+        <v>-0.8246</v>
       </c>
       <c r="N34" t="n">
         <v>119</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9337</v>
+        <v>-0.97</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3554</v>
+        <v>-0.3692</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0595</v>
+        <v>-1.0658</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9337</v>
+        <v>-0.97</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9337</v>
+        <v>-0.97</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9337</v>
+        <v>-0.97</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9337</v>
+        <v>-0.97</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9337</v>
+        <v>-0.97</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9576</v>
+        <v>-1.0472</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3645</v>
+        <v>-0.3986</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0703</v>
+        <v>-1.1009</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9576</v>
+        <v>-1.0472</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2973</v>
+        <v>-0.3618</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6603</v>
+        <v>-0.6854</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2973</v>
+        <v>-0.3618</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2973</v>
+        <v>-0.3618</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6603</v>
+        <v>-0.6854</v>
       </c>
       <c r="K36" t="n">
         <v>135</v>
@@ -2093,7 +2093,7 @@
         <v>52</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9576</v>
+        <v>-1.0472</v>
       </c>
       <c r="N36" t="n">
         <v>187</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.386</v>
+        <v>-1.4377</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5275</v>
+        <v>-0.5472</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2637</v>
+        <v>-1.2787</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.386</v>
+        <v>-1.4377</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2153</v>
+        <v>-1.2405</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1707</v>
+        <v>-0.1972</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2153</v>
+        <v>-1.2405</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2153</v>
+        <v>-1.2405</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1707</v>
+        <v>-0.1972</v>
       </c>
       <c r="K37" t="n">
         <v>135</v>
@@ -2139,7 +2139,7 @@
         <v>52</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.386</v>
+        <v>-1.4377</v>
       </c>
       <c r="N37" t="n">
         <v>187</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Altekz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5302</v>
+        <v>-1.4704</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5824</v>
+        <v>-0.5597</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.3288</v>
+        <v>-1.2936</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5302</v>
+        <v>-1.4704</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5302</v>
+        <v>-0.9669</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5302</v>
+        <v>-0.9669</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5302</v>
+        <v>-0.9669</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5302</v>
+        <v>-1.4704</v>
       </c>
       <c r="N38" t="n">
-        <v>133</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Altekz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6376</v>
+        <v>-1.5678</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6233</v>
+        <v>-0.5967</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3773</v>
+        <v>-1.3379</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6376</v>
+        <v>-1.5678</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9677</v>
+        <v>-1.5678</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6699000000000001</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9677</v>
+        <v>-1.5678</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9677</v>
+        <v>-1.5678</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6699000000000001</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="L39" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6376</v>
+        <v>-1.5678</v>
       </c>
       <c r="N39" t="n">
-        <v>330</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.55</v>
+        <v>-3.2954</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.3512</v>
+        <v>-1.2543</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.2407</v>
+        <v>-2.1243</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.55</v>
+        <v>-3.2954</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.5887</v>
+        <v>-2.3008</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9613</v>
+        <v>-0.9946</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.5887</v>
+        <v>-2.3008</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.346</v>
+        <v>-1.2424</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9613</v>
+        <v>-0.9946</v>
       </c>
       <c r="K40" t="n">
         <v>135</v>
@@ -2277,7 +2277,7 @@
         <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3073</v>
+        <v>-2.237</v>
       </c>
       <c r="N40" t="n">
         <v>215</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8682</v>
+        <v>-3.8202</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4723</v>
+        <v>-1.454</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3843</v>
+        <v>-2.3632</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8682</v>
+        <v>-3.8202</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9174</v>
+        <v>-1.8758</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.9508</v>
+        <v>-1.9444</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9174</v>
+        <v>-1.8758</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9174</v>
+        <v>-1.8758</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9508</v>
+        <v>-1.9444</v>
       </c>
       <c r="K41" t="n">
         <v>114</v>
@@ -2323,7 +2323,7 @@
         <v>216</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.8682</v>
+        <v>-3.8202</v>
       </c>
       <c r="N41" t="n">
         <v>330</v>
@@ -2429,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.999</v>
+        <v>0.9446</v>
       </c>
       <c r="J2" t="n">
-        <v>24.975</v>
+        <v>23.615</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6495</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>16.2375</v>
+        <v>15.6625</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6039</v>
+        <v>0.5854</v>
       </c>
       <c r="J4" t="n">
-        <v>15.0975</v>
+        <v>14.635</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.19</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5326</v>
+        <v>0.5211</v>
       </c>
       <c r="J5" t="n">
-        <v>13.315</v>
+        <v>13.0275</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2091</v>
+        <v>0.2246</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2275</v>
+        <v>5.615</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.99</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0192</v>
+        <v>-0.0012</v>
       </c>
       <c r="J7" t="n">
-        <v>0.48</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1101</v>
+        <v>-0.1284</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7525</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2243</v>
+        <v>-0.2432</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.6075</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3475</v>
+        <v>-0.3634</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.6875</v>
+        <v>-9.085000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3758</v>
+        <v>-0.3904</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.395</v>
+        <v>-9.76</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2479</v>
+        <v>0.2526</v>
       </c>
       <c r="J12" t="n">
-        <v>6.4454</v>
+        <v>6.5676</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1686</v>
+        <v>0.1752</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3836</v>
+        <v>4.5552</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0157</v>
+        <v>-0.0215</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4082</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.0394</v>
+        <v>-3.3982</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4229</v>
+        <v>-0.4323</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.9954</v>
+        <v>-11.2398</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4405</v>
+        <v>0.4513</v>
       </c>
       <c r="J17" t="n">
-        <v>11.453</v>
+        <v>11.7338</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4171</v>
+        <v>0.4291</v>
       </c>
       <c r="J18" t="n">
-        <v>10.8446</v>
+        <v>11.1566</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4054</v>
+        <v>0.4179</v>
       </c>
       <c r="J19" t="n">
-        <v>10.5404</v>
+        <v>10.8654</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0185</v>
       </c>
       <c r="J20" t="n">
-        <v>0.221</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.84</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2153</v>
+        <v>-0.2252</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.5978</v>
+        <v>-5.8552</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9228</v>
       </c>
       <c r="J22" t="n">
-        <v>24.4575</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.28</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7389</v>
+        <v>0.7065</v>
       </c>
       <c r="J23" t="n">
-        <v>18.4725</v>
+        <v>17.6625</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6478</v>
+        <v>0.6253</v>
       </c>
       <c r="J24" t="n">
-        <v>16.195</v>
+        <v>15.6325</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5303</v>
+        <v>0.5196</v>
       </c>
       <c r="J25" t="n">
-        <v>13.2575</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2362</v>
+        <v>0.2507</v>
       </c>
       <c r="J26" t="n">
-        <v>5.905</v>
+        <v>6.2675</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8953</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>22.3825</v>
+        <v>20.905</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2691</v>
+        <v>0.2643</v>
       </c>
       <c r="J28" t="n">
-        <v>6.7275</v>
+        <v>6.6075</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2909</v>
+        <v>-0.3068</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.2725</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4044</v>
+        <v>-0.4161</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.11</v>
+        <v>-10.4025</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.48</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5238</v>
+        <v>-0.5291</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.095</v>
+        <v>-13.2275</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4265</v>
+        <v>0.4828</v>
       </c>
       <c r="J32" t="n">
-        <v>11.5155</v>
+        <v>13.0356</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3991</v>
+        <v>0.4491</v>
       </c>
       <c r="J33" t="n">
-        <v>10.7757</v>
+        <v>12.1257</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.35</v>
+        <v>0.375</v>
       </c>
       <c r="J34" t="n">
-        <v>9.449999999999999</v>
+        <v>10.125</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0506</v>
+        <v>0.0633</v>
       </c>
       <c r="J35" t="n">
-        <v>1.3662</v>
+        <v>1.7091</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3595</v>
+        <v>-0.3677</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.7065</v>
+        <v>-9.927899999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4639</v>
+        <v>0.5161</v>
       </c>
       <c r="J37" t="n">
-        <v>12.5253</v>
+        <v>13.9347</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1905</v>
+        <v>0.1992</v>
       </c>
       <c r="J38" t="n">
-        <v>5.1435</v>
+        <v>5.3784</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1082</v>
+        <v>0.117</v>
       </c>
       <c r="J39" t="n">
-        <v>2.9214</v>
+        <v>3.159</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.83</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2075</v>
+        <v>-0.2213</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.6025</v>
+        <v>-5.9751</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.419</v>
+        <v>-0.4276</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.313</v>
+        <v>-11.5452</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4378</v>
+        <v>0.4789</v>
       </c>
       <c r="J42" t="n">
-        <v>10.945</v>
+        <v>11.9725</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.186</v>
+        <v>0.1877</v>
       </c>
       <c r="J43" t="n">
-        <v>4.65</v>
+        <v>4.6925</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.208</v>
+        <v>-0.224</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.2</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2773</v>
+        <v>-0.2924</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.9325</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3255</v>
+        <v>-0.3392</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.137499999999999</v>
+        <v>-8.48</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8415</v>
+        <v>0.9314</v>
       </c>
       <c r="J47" t="n">
-        <v>21.0375</v>
+        <v>23.285</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8035</v>
+        <v>0.8904</v>
       </c>
       <c r="J48" t="n">
-        <v>20.0875</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5699</v>
+        <v>0.6344</v>
       </c>
       <c r="J49" t="n">
-        <v>14.2475</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2305</v>
+        <v>0.2467</v>
       </c>
       <c r="J50" t="n">
-        <v>5.7625</v>
+        <v>6.1675</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1183</v>
+        <v>-0.1037</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.9575</v>
+        <v>-2.5925</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.73</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8921</v>
+        <v>0.9954</v>
       </c>
       <c r="J52" t="n">
-        <v>24.9788</v>
+        <v>27.8712</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3089</v>
+        <v>0.3161</v>
       </c>
       <c r="J53" t="n">
-        <v>8.6492</v>
+        <v>8.8508</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1745</v>
+        <v>-0.1861</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.886</v>
+        <v>-5.2108</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2163</v>
+        <v>-0.2282</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.0564</v>
+        <v>-6.3896</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.77</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2763</v>
+        <v>-0.2877</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.7364</v>
+        <v>-8.0556</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8832</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>24.7296</v>
+        <v>27.1096</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.33</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.7346</v>
       </c>
       <c r="J58" t="n">
-        <v>18.6704</v>
+        <v>20.5688</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1444</v>
+        <v>0.1552</v>
       </c>
       <c r="J59" t="n">
-        <v>4.0432</v>
+        <v>4.3456</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.87</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4618</v>
+        <v>-0.439</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.9304</v>
+        <v>-12.292</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7516</v>
+        <v>-0.6976</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.0448</v>
+        <v>-19.5328</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6973</v>
+        <v>0.7644</v>
       </c>
       <c r="J62" t="n">
-        <v>20.2217</v>
+        <v>22.1676</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4937</v>
+        <v>0.5403</v>
       </c>
       <c r="J63" t="n">
-        <v>14.3173</v>
+        <v>15.6687</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.06</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2191</v>
+        <v>0.2236</v>
       </c>
       <c r="J64" t="n">
-        <v>6.3539</v>
+        <v>6.4844</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6324</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>-18.3396</v>
+        <v>-17.2637</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6583</v>
+        <v>-0.6183</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.0907</v>
+        <v>-17.9307</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.43</v>
       </c>
       <c r="I67" t="n">
-        <v>0.632</v>
+        <v>0.7039</v>
       </c>
       <c r="J67" t="n">
-        <v>18.328</v>
+        <v>20.4131</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4073</v>
+        <v>0.4469</v>
       </c>
       <c r="J68" t="n">
-        <v>11.8117</v>
+        <v>12.9601</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1979</v>
+        <v>-0.2115</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.7391</v>
+        <v>-6.1335</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2584</v>
+        <v>-0.2717</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.4936</v>
+        <v>-7.8793</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3167</v>
+        <v>-0.3288</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.1843</v>
+        <v>-9.5352</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3266</v>
+        <v>0.329</v>
       </c>
       <c r="J72" t="n">
-        <v>8.818199999999999</v>
+        <v>8.882999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0888</v>
       </c>
       <c r="J73" t="n">
-        <v>2.2815</v>
+        <v>2.3976</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2193</v>
+        <v>-0.235</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.9211</v>
+        <v>-6.345</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2294</v>
+        <v>-0.2449</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.1938</v>
+        <v>-6.6123</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2492</v>
+        <v>-0.2645</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.7284</v>
+        <v>-7.1415</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6528</v>
+        <v>0.7486</v>
       </c>
       <c r="J77" t="n">
-        <v>17.6256</v>
+        <v>20.2122</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3504</v>
+        <v>0.3779</v>
       </c>
       <c r="J78" t="n">
-        <v>9.460800000000001</v>
+        <v>10.2033</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2684</v>
+        <v>0.2863</v>
       </c>
       <c r="J79" t="n">
-        <v>7.2468</v>
+        <v>7.7301</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1209</v>
+        <v>0.1392</v>
       </c>
       <c r="J80" t="n">
-        <v>3.2643</v>
+        <v>3.7584</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2515</v>
+        <v>-0.2601</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.7905</v>
+        <v>-7.0227</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.41</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7815</v>
+        <v>0.858</v>
       </c>
       <c r="J82" t="n">
-        <v>28.134</v>
+        <v>30.888</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5723</v>
+        <v>0.6299</v>
       </c>
       <c r="J83" t="n">
-        <v>20.6028</v>
+        <v>22.6764</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.242</v>
+        <v>0.2473</v>
       </c>
       <c r="J84" t="n">
-        <v>8.712</v>
+        <v>8.902799999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5387</v>
+        <v>-0.5094</v>
       </c>
       <c r="J85" t="n">
-        <v>-19.3932</v>
+        <v>-18.3384</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.592</v>
+        <v>-0.5571</v>
       </c>
       <c r="J86" t="n">
-        <v>-21.312</v>
+        <v>-20.0556</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4612</v>
+        <v>0.5102</v>
       </c>
       <c r="J87" t="n">
-        <v>16.6032</v>
+        <v>18.3672</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0674</v>
+        <v>0.0743</v>
       </c>
       <c r="J88" t="n">
-        <v>2.4264</v>
+        <v>2.6748</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1222</v>
+        <v>-0.1347</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.3992</v>
+        <v>-4.8492</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.89</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1444</v>
+        <v>-0.1575</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.1984</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1552</v>
+        <v>-0.1686</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.5872</v>
+        <v>-6.0696</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7884</v>
       </c>
       <c r="J92" t="n">
-        <v>25.8552</v>
+        <v>28.3824</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="J93" t="n">
-        <v>10.872</v>
+        <v>10.908</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2735</v>
+        <v>0.2762</v>
       </c>
       <c r="J94" t="n">
-        <v>9.846</v>
+        <v>9.943199999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0678</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.4408</v>
+        <v>-2.4696</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6652</v>
+        <v>-0.6231</v>
       </c>
       <c r="J96" t="n">
-        <v>-23.9472</v>
+        <v>-22.4316</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6954</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>25.0344</v>
+        <v>28.1052</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.51</v>
       </c>
       <c r="I98" t="n">
-        <v>0.677</v>
+        <v>0.7602</v>
       </c>
       <c r="J98" t="n">
-        <v>24.372</v>
+        <v>27.3672</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0112</v>
+        <v>-0.0086</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.4032</v>
+        <v>-0.3096</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2015</v>
+        <v>-0.2121</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.254</v>
+        <v>-7.6356</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.73</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3206</v>
+        <v>-0.3301</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.5416</v>
+        <v>-11.8836</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.44</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8028</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>19.2672</v>
+        <v>21.2304</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4874</v>
+        <v>0.5385</v>
       </c>
       <c r="J103" t="n">
-        <v>11.6976</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3702</v>
+        <v>0.393</v>
       </c>
       <c r="J104" t="n">
-        <v>8.8848</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0605</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>1.452</v>
+        <v>1.8432</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2693</v>
+        <v>-0.2584</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.4632</v>
+        <v>-6.2016</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4896</v>
+        <v>0.5319</v>
       </c>
       <c r="J107" t="n">
-        <v>11.7504</v>
+        <v>12.7656</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.89</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1253</v>
+        <v>-0.143</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.0072</v>
+        <v>-3.432</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.265</v>
+        <v>-0.2828</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.36</v>
+        <v>-6.7872</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.265</v>
+        <v>-0.2828</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.36</v>
+        <v>-6.7872</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5452</v>
+        <v>-0.5501</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.0848</v>
+        <v>-13.2024</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6938</v>
+        <v>0.7612</v>
       </c>
       <c r="J112" t="n">
-        <v>20.814</v>
+        <v>22.836</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0648</v>
+        <v>-0.0665</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.944</v>
+        <v>-1.995</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.98</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1056</v>
+        <v>-0.1077</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.168</v>
+        <v>-3.231</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1426</v>
+        <v>-0.1441</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.278</v>
+        <v>-4.323</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1426</v>
+        <v>-0.1441</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.278</v>
+        <v>-4.323</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4927</v>
+        <v>0.5485</v>
       </c>
       <c r="J117" t="n">
-        <v>14.781</v>
+        <v>16.455</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3566</v>
+        <v>0.374</v>
       </c>
       <c r="J118" t="n">
-        <v>10.698</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0238</v>
+        <v>-0.0277</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.714</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0921</v>
+        <v>-0.1021</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.763</v>
+        <v>-3.063</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2533</v>
+        <v>-0.2657</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.599</v>
+        <v>-7.971</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.789</v>
+        <v>0.8724</v>
       </c>
       <c r="J122" t="n">
-        <v>17.358</v>
+        <v>19.1928</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.42</v>
       </c>
       <c r="I123" t="n">
-        <v>0.763</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>16.786</v>
+        <v>18.5746</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3266</v>
+        <v>0.335</v>
       </c>
       <c r="J124" t="n">
-        <v>7.1852</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I125" t="n">
-        <v>0.301</v>
+        <v>0.3093</v>
       </c>
       <c r="J125" t="n">
-        <v>6.622</v>
+        <v>6.8046</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2185</v>
+        <v>-0.2064</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.807</v>
+        <v>-4.5408</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3471</v>
+        <v>0.3425</v>
       </c>
       <c r="J127" t="n">
-        <v>7.6362</v>
+        <v>7.535</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0786</v>
+        <v>-0.0951</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.7292</v>
+        <v>-2.0922</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1025</v>
+        <v>-0.1197</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.255</v>
+        <v>-2.6334</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.407</v>
+        <v>-0.4197</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.954000000000001</v>
+        <v>-9.2334</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4811</v>
+        <v>-0.4899</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.5842</v>
+        <v>-10.7778</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6283</v>
+        <v>0.6071</v>
       </c>
       <c r="J132" t="n">
-        <v>21.9905</v>
+        <v>21.2485</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6283</v>
+        <v>0.6071</v>
       </c>
       <c r="J133" t="n">
-        <v>21.9905</v>
+        <v>21.2485</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6283</v>
+        <v>0.6071</v>
       </c>
       <c r="J134" t="n">
-        <v>21.9905</v>
+        <v>21.2485</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5654</v>
       </c>
       <c r="J135" t="n">
-        <v>20.377</v>
+        <v>19.789</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I136" t="n">
-        <v>0.4602</v>
+        <v>0.4551</v>
       </c>
       <c r="J136" t="n">
-        <v>16.107</v>
+        <v>15.9285</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.98</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0217</v>
+        <v>-0.0318</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.7595</v>
+        <v>-1.113</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.91</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1108</v>
+        <v>-0.1261</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.878</v>
+        <v>-4.4135</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1327</v>
+        <v>-0.1486</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.6445</v>
+        <v>-5.201</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1733</v>
+        <v>-0.1902</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.0655</v>
+        <v>-6.657</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2917</v>
+        <v>-0.3074</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.2095</v>
+        <v>-10.759</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9696</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>25.2096</v>
+        <v>23.6028</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6214</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>16.1564</v>
+        <v>15.5298</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4977</v>
+        <v>0.4863</v>
       </c>
       <c r="J144" t="n">
-        <v>12.9402</v>
+        <v>12.6438</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0328</v>
+        <v>-0.0225</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.8528</v>
+        <v>-0.585</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2979</v>
+        <v>-0.2859</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.7454</v>
+        <v>-7.4334</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4453</v>
+        <v>0.4386</v>
       </c>
       <c r="J147" t="n">
-        <v>11.5778</v>
+        <v>11.4036</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1663</v>
+        <v>0.1734</v>
       </c>
       <c r="J148" t="n">
-        <v>4.3238</v>
+        <v>4.5084</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0861</v>
+        <v>-0.0975</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.2386</v>
+        <v>-2.535</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1646</v>
+        <v>-0.1784</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.2796</v>
+        <v>-4.6384</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2063</v>
+        <v>-0.2204</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.3638</v>
+        <v>-5.7304</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5585</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>16.755</v>
+        <v>16.164</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5332</v>
+        <v>0.5161</v>
       </c>
       <c r="J153" t="n">
-        <v>15.996</v>
+        <v>15.483</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3769</v>
+        <v>0.3741</v>
       </c>
       <c r="J154" t="n">
-        <v>11.307</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.05</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1771</v>
+        <v>0.1866</v>
       </c>
       <c r="J155" t="n">
-        <v>5.313</v>
+        <v>5.598</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2237</v>
+        <v>-0.2186</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.711</v>
+        <v>-6.558</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5334</v>
       </c>
       <c r="J157" t="n">
-        <v>16.407</v>
+        <v>16.002</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4387</v>
+        <v>0.4337</v>
       </c>
       <c r="J158" t="n">
-        <v>13.161</v>
+        <v>13.011</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1618</v>
+        <v>0.1701</v>
       </c>
       <c r="J159" t="n">
-        <v>4.854</v>
+        <v>5.103</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1117</v>
+        <v>-0.1236</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.351</v>
+        <v>-3.708</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4656</v>
+        <v>-0.4719</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.968</v>
+        <v>-14.157</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4321</v>
+        <v>0.428</v>
       </c>
       <c r="J162" t="n">
-        <v>12.963</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1822</v>
+        <v>0.1892</v>
       </c>
       <c r="J163" t="n">
-        <v>5.466</v>
+        <v>5.676</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.017</v>
+        <v>-0.0226</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.51</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1616</v>
+        <v>-0.1761</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.848</v>
+        <v>-5.283</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4609</v>
+        <v>-0.4682</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.827</v>
+        <v>-14.046</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6271</v>
+        <v>0.6242</v>
       </c>
       <c r="J167" t="n">
-        <v>18.813</v>
+        <v>18.726</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2561</v>
+        <v>0.2712</v>
       </c>
       <c r="J168" t="n">
-        <v>7.683</v>
+        <v>8.135999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2169</v>
+        <v>0.2324</v>
       </c>
       <c r="J169" t="n">
-        <v>6.507</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0978</v>
+        <v>-0.1065</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.934</v>
+        <v>-3.195</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3175</v>
+        <v>-0.3276</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.525</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6427</v>
+        <v>0.6121</v>
       </c>
       <c r="J172" t="n">
-        <v>19.281</v>
+        <v>18.363</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5154</v>
+        <v>0.4985</v>
       </c>
       <c r="J173" t="n">
-        <v>15.462</v>
+        <v>14.955</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2136</v>
+        <v>0.22</v>
       </c>
       <c r="J174" t="n">
-        <v>6.408</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1833</v>
+        <v>-0.1818</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.499</v>
+        <v>-5.454</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.95</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2166</v>
+        <v>-0.2137</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.498</v>
+        <v>-6.411</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9019</v>
+        <v>0.8535</v>
       </c>
       <c r="J177" t="n">
-        <v>27.057</v>
+        <v>25.605</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0636</v>
+        <v>-0.0728</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.908</v>
+        <v>-2.184</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1005</v>
+        <v>-0.1118</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.015</v>
+        <v>-3.354</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.84</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1988</v>
+        <v>-0.2123</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.964</v>
+        <v>-6.369</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2193</v>
+        <v>-0.2327</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.579</v>
+        <v>-6.981</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.93</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0914</v>
       </c>
       <c r="J182" t="n">
-        <v>-1.6997</v>
+        <v>-2.1022</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1434</v>
+        <v>-0.1622</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.2982</v>
+        <v>-3.7306</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1752</v>
+        <v>-0.1942</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.0296</v>
+        <v>-4.4666</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2904</v>
+        <v>-0.3082</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.6792</v>
+        <v>-7.0886</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4036</v>
+        <v>-0.417</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.2828</v>
+        <v>-9.590999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.33</v>
       </c>
       <c r="I187" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J187" t="n">
-        <v>42.1774</v>
+        <v>44.5556</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.33</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8379</v>
+        <v>0.7964</v>
       </c>
       <c r="J188" t="n">
-        <v>19.2717</v>
+        <v>18.3172</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.26</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6597</v>
       </c>
       <c r="J189" t="n">
-        <v>15.732</v>
+        <v>15.1731</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4558</v>
+        <v>-0.423</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.4834</v>
+        <v>-9.728999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.969</v>
+        <v>-0.8804</v>
       </c>
       <c r="J191" t="n">
-        <v>-22.287</v>
+        <v>-20.2492</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3714</v>
+        <v>0.3801</v>
       </c>
       <c r="J192" t="n">
-        <v>10.7706</v>
+        <v>11.0229</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2814</v>
+        <v>0.2932</v>
       </c>
       <c r="J193" t="n">
-        <v>8.160600000000001</v>
+        <v>8.502800000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.95</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0781</v>
+        <v>-0.0878</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.2649</v>
+        <v>-2.5462</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0781</v>
+        <v>-0.0878</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.2649</v>
+        <v>-2.5462</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2614</v>
+        <v>-0.2741</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.5806</v>
+        <v>-7.9489</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.23</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3509</v>
+        <v>0.3594</v>
       </c>
       <c r="J197" t="n">
-        <v>10.1761</v>
+        <v>10.4226</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2976</v>
+        <v>0.3085</v>
       </c>
       <c r="J198" t="n">
-        <v>8.6304</v>
+        <v>8.9465</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.19</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2976</v>
+        <v>0.3085</v>
       </c>
       <c r="J199" t="n">
-        <v>8.6304</v>
+        <v>8.9465</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1871</v>
+        <v>0.2005</v>
       </c>
       <c r="J200" t="n">
-        <v>5.4259</v>
+        <v>5.8145</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1366</v>
+        <v>-0.146</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.9614</v>
+        <v>-4.234</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2141</v>
+        <v>0.2138</v>
       </c>
       <c r="J202" t="n">
-        <v>6.2089</v>
+        <v>6.2002</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1184</v>
+        <v>0.1192</v>
       </c>
       <c r="J203" t="n">
-        <v>3.4336</v>
+        <v>3.4568</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.9169</v>
+        <v>-2.2823</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1859</v>
+        <v>-0.2022</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.3911</v>
+        <v>-5.8638</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4357</v>
+        <v>-0.4454</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.6353</v>
+        <v>-12.9166</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1877</v>
+        <v>1.1523</v>
       </c>
       <c r="J207" t="n">
-        <v>34.4433</v>
+        <v>33.4167</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.23</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6372</v>
+        <v>0.6131</v>
       </c>
       <c r="J208" t="n">
-        <v>18.4788</v>
+        <v>17.7799</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.13</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3911</v>
+        <v>0.3902</v>
       </c>
       <c r="J209" t="n">
-        <v>11.3419</v>
+        <v>11.3158</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0139</v>
+        <v>0.0315</v>
       </c>
       <c r="J210" t="n">
-        <v>0.4031</v>
+        <v>0.9135</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.95</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2428</v>
+        <v>-0.2319</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.0412</v>
+        <v>-6.7251</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.105</v>
+        <v>1.059</v>
       </c>
       <c r="J212" t="n">
-        <v>32.045</v>
+        <v>30.711</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.08</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2686</v>
+        <v>0.273</v>
       </c>
       <c r="J213" t="n">
-        <v>7.7894</v>
+        <v>7.917</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2395</v>
+        <v>0.2456</v>
       </c>
       <c r="J214" t="n">
-        <v>6.9455</v>
+        <v>7.1224</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1543</v>
+        <v>-0.1522</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.4747</v>
+        <v>-4.4138</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3756</v>
+        <v>-0.3606</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.8924</v>
+        <v>-10.4574</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6012</v>
+        <v>0.5827</v>
       </c>
       <c r="J217" t="n">
-        <v>17.4348</v>
+        <v>16.8983</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3841</v>
+        <v>0.3827</v>
       </c>
       <c r="J218" t="n">
-        <v>11.1389</v>
+        <v>11.0983</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0877</v>
+        <v>-0.0987</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.5433</v>
+        <v>-2.8623</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1338</v>
+        <v>-0.1466</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.8802</v>
+        <v>-4.2514</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.68</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3547</v>
+        <v>-0.3656</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.2863</v>
+        <v>-10.6024</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9263</v>
+        <v>0.8548</v>
       </c>
       <c r="J222" t="n">
-        <v>33.3468</v>
+        <v>30.7728</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8782</v>
+        <v>0.8122</v>
       </c>
       <c r="J223" t="n">
-        <v>31.6152</v>
+        <v>29.2392</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.85</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.486</v>
+        <v>-0.4672</v>
       </c>
       <c r="J224" t="n">
-        <v>-17.496</v>
+        <v>-16.8192</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.78</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6704</v>
+        <v>-0.6315</v>
       </c>
       <c r="J225" t="n">
-        <v>-24.1344</v>
+        <v>-22.734</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8467</v>
+        <v>-0.786</v>
       </c>
       <c r="J226" t="n">
-        <v>-30.4812</v>
+        <v>-28.296</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7602</v>
+        <v>0.7335</v>
       </c>
       <c r="J227" t="n">
-        <v>27.3672</v>
+        <v>26.406</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7279</v>
+        <v>0.7044</v>
       </c>
       <c r="J228" t="n">
-        <v>26.2044</v>
+        <v>25.3584</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.18</v>
       </c>
       <c r="I229" t="n">
-        <v>0.373</v>
+        <v>0.3785</v>
       </c>
       <c r="J229" t="n">
-        <v>13.428</v>
+        <v>13.626</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2007</v>
+        <v>-0.2114</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2252</v>
+        <v>-7.6104</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3007</v>
+        <v>-0.3107</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.8252</v>
+        <v>-11.1852</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2006</v>
+        <v>1.1755</v>
       </c>
       <c r="J232" t="n">
-        <v>25.2126</v>
+        <v>24.6855</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1406</v>
+        <v>1.1109</v>
       </c>
       <c r="J233" t="n">
-        <v>23.9526</v>
+        <v>23.3289</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0427</v>
+        <v>0.9998</v>
       </c>
       <c r="J234" t="n">
-        <v>21.8967</v>
+        <v>20.9958</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.9484</v>
+        <v>0.899</v>
       </c>
       <c r="J235" t="n">
-        <v>19.9164</v>
+        <v>18.879</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.04</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0732</v>
+        <v>0.1056</v>
       </c>
       <c r="J236" t="n">
-        <v>1.5372</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.91</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0801</v>
+        <v>-0.1022</v>
       </c>
       <c r="J237" t="n">
-        <v>-1.6821</v>
+        <v>-2.1462</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.87</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1274</v>
+        <v>-0.1498</v>
       </c>
       <c r="J238" t="n">
-        <v>-2.6754</v>
+        <v>-3.1458</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.74</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2629</v>
+        <v>-0.2833</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.5209</v>
+        <v>-5.9493</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.63</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3638</v>
+        <v>-0.3811</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.6398</v>
+        <v>-8.0031</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.43</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5505</v>
+        <v>-0.5569</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.5605</v>
+        <v>-11.6949</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1943</v>
+        <v>1.1652</v>
       </c>
       <c r="J242" t="n">
-        <v>26.2746</v>
+        <v>25.6344</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0298</v>
+        <v>0.9813</v>
       </c>
       <c r="J243" t="n">
-        <v>22.6556</v>
+        <v>21.5886</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.28</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7292</v>
+        <v>0.7</v>
       </c>
       <c r="J244" t="n">
-        <v>16.0424</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.24</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J245" t="n">
-        <v>14.0272</v>
+        <v>13.6048</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1277</v>
+        <v>-0.1103</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.8094</v>
+        <v>-2.4266</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7831</v>
+        <v>0.7205</v>
       </c>
       <c r="J247" t="n">
-        <v>17.2282</v>
+        <v>15.851</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.71</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2911</v>
+        <v>-0.3107</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.4042</v>
+        <v>-6.8354</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4028</v>
+        <v>-0.418</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.861599999999999</v>
+        <v>-9.196</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.58</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4122</v>
+        <v>-0.4269</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.0684</v>
+        <v>-9.3918</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5334</v>
+        <v>-0.5407</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.7348</v>
+        <v>-11.8954</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5464</v>
+        <v>1.5431</v>
       </c>
       <c r="J252" t="n">
-        <v>35.5672</v>
+        <v>35.4913</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.58</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1971</v>
+        <v>1.1724</v>
       </c>
       <c r="J253" t="n">
-        <v>27.5333</v>
+        <v>26.9652</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.49</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0895</v>
+        <v>1.0555</v>
       </c>
       <c r="J254" t="n">
-        <v>25.0585</v>
+        <v>24.2765</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3081</v>
+        <v>0.3266</v>
       </c>
       <c r="J255" t="n">
-        <v>7.0863</v>
+        <v>7.5118</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.03</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0338</v>
+        <v>0.0687</v>
       </c>
       <c r="J256" t="n">
-        <v>0.7774</v>
+        <v>1.5801</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.79</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2051</v>
+        <v>-0.2284</v>
       </c>
       <c r="J257" t="n">
-        <v>-4.7173</v>
+        <v>-5.2532</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.68</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.3128</v>
+        <v>-0.333</v>
       </c>
       <c r="J258" t="n">
-        <v>-7.1944</v>
+        <v>-7.659</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3302</v>
+        <v>-0.35</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.5946</v>
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3392</v>
+        <v>-0.3587</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.8016</v>
+        <v>-8.2501</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3852</v>
+        <v>-0.4027</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.8596</v>
+        <v>-9.2621</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1165</v>
+        <v>1.0797</v>
       </c>
       <c r="J262" t="n">
-        <v>24.563</v>
+        <v>23.7534</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0242</v>
+        <v>0.9727</v>
       </c>
       <c r="J263" t="n">
-        <v>22.5324</v>
+        <v>21.3994</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7579</v>
+        <v>0.724</v>
       </c>
       <c r="J264" t="n">
-        <v>16.6738</v>
+        <v>15.928</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.05</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1391</v>
+        <v>0.1603</v>
       </c>
       <c r="J265" t="n">
-        <v>3.0602</v>
+        <v>3.5266</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0341</v>
+        <v>0.0584</v>
       </c>
       <c r="J266" t="n">
-        <v>0.7502</v>
+        <v>1.2848</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.23</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5142</v>
+        <v>0.4995</v>
       </c>
       <c r="J267" t="n">
-        <v>11.3124</v>
+        <v>10.989</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1756</v>
+        <v>0.1802</v>
       </c>
       <c r="J268" t="n">
-        <v>3.8632</v>
+        <v>3.9644</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1059</v>
+        <v>-0.1192</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.3298</v>
+        <v>-2.6224</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2223</v>
+        <v>-0.2372</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.8906</v>
+        <v>-5.2184</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.7</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3297</v>
+        <v>-0.3425</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.2534</v>
+        <v>-7.535</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.25</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7103</v>
+        <v>0.6731</v>
       </c>
       <c r="J272" t="n">
-        <v>19.1781</v>
+        <v>18.1737</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6363</v>
+        <v>0.6077</v>
       </c>
       <c r="J273" t="n">
-        <v>17.1801</v>
+        <v>16.4079</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2971</v>
+        <v>0.2997</v>
       </c>
       <c r="J274" t="n">
-        <v>8.021699999999999</v>
+        <v>8.091900000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1789</v>
+        <v>0.1879</v>
       </c>
       <c r="J275" t="n">
-        <v>4.8303</v>
+        <v>5.0733</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5415</v>
+        <v>-0.5114</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.6205</v>
+        <v>-13.8078</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.532</v>
+        <v>0.5192</v>
       </c>
       <c r="J277" t="n">
-        <v>14.364</v>
+        <v>14.0184</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.532</v>
+        <v>0.5192</v>
       </c>
       <c r="J278" t="n">
-        <v>14.364</v>
+        <v>14.0184</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0674</v>
+        <v>0.0743</v>
       </c>
       <c r="J279" t="n">
-        <v>1.8198</v>
+        <v>2.0061</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.0277</v>
+        <v>-2.3085</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.49</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5276</v>
+        <v>-0.5308</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.2452</v>
+        <v>-14.3316</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.41</v>
       </c>
       <c r="I282" t="n">
-        <v>1.055</v>
+        <v>0.9991</v>
       </c>
       <c r="J282" t="n">
-        <v>28.485</v>
+        <v>26.9757</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4608</v>
+        <v>0.4497</v>
       </c>
       <c r="J283" t="n">
-        <v>12.4416</v>
+        <v>12.1419</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2985</v>
+        <v>0.3006</v>
       </c>
       <c r="J284" t="n">
-        <v>8.0595</v>
+        <v>8.116199999999999</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.88</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4288</v>
+        <v>-0.4101</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.5776</v>
+        <v>-11.0727</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4568</v>
+        <v>-0.4355</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.3336</v>
+        <v>-11.7585</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.09</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2364</v>
+        <v>0.2403</v>
       </c>
       <c r="J287" t="n">
-        <v>6.3828</v>
+        <v>6.4881</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1484</v>
+        <v>0.1544</v>
       </c>
       <c r="J288" t="n">
-        <v>4.0068</v>
+        <v>4.1688</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0061</v>
+        <v>0.0043</v>
       </c>
       <c r="J289" t="n">
-        <v>0.1647</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1075</v>
+        <v>-0.1204</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.9025</v>
+        <v>-3.2508</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.74</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2933</v>
+        <v>-0.3067</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.9191</v>
+        <v>-8.280900000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.78</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1645</v>
+        <v>-0.1984</v>
       </c>
       <c r="J292" t="n">
-        <v>-3.1255</v>
+        <v>-3.7696</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.3889</v>
+        <v>-0.4105</v>
       </c>
       <c r="J293" t="n">
-        <v>-7.3891</v>
+        <v>-7.7995</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.48</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4696</v>
+        <v>-0.4866</v>
       </c>
       <c r="J294" t="n">
-        <v>-8.9224</v>
+        <v>-9.2454</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.43</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.517</v>
+        <v>-0.5306</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.823</v>
+        <v>-10.0814</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5557</v>
+        <v>-0.5662</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.5583</v>
+        <v>-10.7578</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.26</v>
       </c>
       <c r="I297" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J297" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.8</v>
       </c>
       <c r="I298" t="n">
-        <v>1.4254</v>
+        <v>1.4207</v>
       </c>
       <c r="J298" t="n">
-        <v>27.0826</v>
+        <v>26.9933</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.34</v>
       </c>
       <c r="I299" t="n">
-        <v>0.8096</v>
+        <v>0.7812</v>
       </c>
       <c r="J299" t="n">
-        <v>15.3824</v>
+        <v>14.8428</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.3</v>
       </c>
       <c r="I300" t="n">
-        <v>0.7197</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>13.6743</v>
+        <v>13.3399</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.22</v>
       </c>
       <c r="I301" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5354</v>
       </c>
       <c r="J301" t="n">
-        <v>10.1042</v>
+        <v>10.1726</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.16</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3676</v>
+        <v>0.3667</v>
       </c>
       <c r="J302" t="n">
-        <v>11.028</v>
+        <v>11.001</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2698</v>
+        <v>0.2742</v>
       </c>
       <c r="J303" t="n">
-        <v>8.093999999999999</v>
+        <v>8.226000000000001</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1864</v>
+        <v>0.1936</v>
       </c>
       <c r="J304" t="n">
-        <v>5.592</v>
+        <v>5.808</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1655</v>
+        <v>-0.1791</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.965</v>
+        <v>-5.373</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3062</v>
+        <v>-0.3187</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.186</v>
+        <v>-9.561</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.33</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9013</v>
+        <v>0.8406</v>
       </c>
       <c r="J307" t="n">
-        <v>27.039</v>
+        <v>25.218</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.07</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2399</v>
+        <v>0.2458</v>
       </c>
       <c r="J308" t="n">
-        <v>7.197</v>
+        <v>7.374</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1784</v>
+        <v>0.1875</v>
       </c>
       <c r="J309" t="n">
-        <v>5.352</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.04</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1458</v>
+        <v>0.1562</v>
       </c>
       <c r="J310" t="n">
-        <v>4.374</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.97</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1538</v>
+        <v>-0.1518</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.614</v>
+        <v>-4.554</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6972/event_6972_evp_summary.xlsx
+++ b/database/event/6972/event_6972_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3536</v>
+        <v>5.2176</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0376</v>
+        <v>1.9859</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8129</v>
+        <v>1.7711</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3536</v>
+        <v>5.2176</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0106</v>
+        <v>2.9658</v>
       </c>
       <c r="G2" t="n">
-        <v>2.343</v>
+        <v>2.2518</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0388</v>
+        <v>4.6923</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7209</v>
+        <v>2.6346</v>
       </c>
       <c r="J2" t="n">
-        <v>2.343</v>
+        <v>2.2518</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>5.0639</v>
+        <v>4.8864</v>
       </c>
       <c r="N2" t="n">
         <v>274</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2892</v>
+        <v>5.0841</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0131</v>
+        <v>1.9351</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7835</v>
+        <v>1.7103</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2892</v>
+        <v>5.0841</v>
       </c>
       <c r="F3" t="n">
-        <v>1.909</v>
+        <v>1.878</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3802</v>
+        <v>3.2061</v>
       </c>
       <c r="H3" t="n">
-        <v>1.909</v>
+        <v>1.878</v>
       </c>
       <c r="I3" t="n">
-        <v>1.909</v>
+        <v>1.878</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3802</v>
+        <v>3.2061</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>216</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2892</v>
+        <v>5.0841</v>
       </c>
       <c r="N3" t="n">
         <v>330</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1422</v>
+        <v>5.0711</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9572</v>
+        <v>1.9301</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7166</v>
+        <v>1.7043</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1422</v>
+        <v>5.0711</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1155</v>
+        <v>3.067</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0267</v>
+        <v>2.0041</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3849</v>
+        <v>5.0724</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9078</v>
+        <v>2.848</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0267</v>
+        <v>2.0041</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -621,7 +621,7 @@
         <v>168</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9345</v>
+        <v>4.8521</v>
       </c>
       <c r="N4" t="n">
         <v>274</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1087</v>
+        <v>4.945</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9444</v>
+        <v>1.8821</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7014</v>
+        <v>1.6469</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1087</v>
+        <v>4.945</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5377</v>
+        <v>3.4334</v>
       </c>
       <c r="G5" t="n">
-        <v>1.571</v>
+        <v>1.5116</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7779</v>
+        <v>6.4477</v>
       </c>
       <c r="I5" t="n">
-        <v>3.66</v>
+        <v>3.6202</v>
       </c>
       <c r="J5" t="n">
-        <v>1.571</v>
+        <v>1.5116</v>
       </c>
       <c r="K5" t="n">
         <v>106</v>
@@ -667,7 +667,7 @@
         <v>168</v>
       </c>
       <c r="M5" t="n">
-        <v>5.231</v>
+        <v>5.1318</v>
       </c>
       <c r="N5" t="n">
         <v>274</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2913</v>
+        <v>4.1644</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6333</v>
+        <v>1.585</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3293</v>
+        <v>1.2913</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2913</v>
+        <v>4.1644</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5915</v>
+        <v>3.0948</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6998</v>
+        <v>1.0696</v>
       </c>
       <c r="H6" t="n">
-        <v>6.9557</v>
+        <v>5.1768</v>
       </c>
       <c r="I6" t="n">
-        <v>3.756</v>
+        <v>2.9066</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6998</v>
+        <v>1.0696</v>
       </c>
       <c r="K6" t="n">
         <v>135</v>
@@ -713,7 +713,7 @@
         <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4558</v>
+        <v>3.9762</v>
       </c>
       <c r="N6" t="n">
         <v>215</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2569</v>
+        <v>4.0864</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6202</v>
+        <v>1.5553</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3136</v>
+        <v>1.2558</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2569</v>
+        <v>4.0864</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1105</v>
+        <v>3.4694</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1464</v>
+        <v>0.617</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3684</v>
+        <v>6.5831</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8989</v>
+        <v>3.6962</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1464</v>
+        <v>0.617</v>
       </c>
       <c r="K7" t="n">
         <v>135</v>
@@ -759,7 +759,7 @@
         <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0453</v>
+        <v>4.3132</v>
       </c>
       <c r="N7" t="n">
         <v>215</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1225</v>
+        <v>3.1749</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1885</v>
+        <v>1.2084</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7972</v>
+        <v>0.8405</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1225</v>
+        <v>3.1749</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2848</v>
+        <v>2.3904</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8377</v>
+        <v>0.7845</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6443</v>
+        <v>2.5321</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4279</v>
+        <v>1.4217</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8377</v>
+        <v>0.7845</v>
       </c>
       <c r="K8" t="n">
         <v>106</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2656</v>
+        <v>2.2062</v>
       </c>
       <c r="N8" t="n">
         <v>274</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8786</v>
+        <v>2.8219</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0956</v>
+        <v>1.074</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6862</v>
+        <v>0.6797</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8786</v>
+        <v>2.8219</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7916</v>
+        <v>1.4098</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.4121</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3162</v>
+        <v>1.4098</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3307</v>
+        <v>1.4475</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.4121</v>
       </c>
       <c r="K9" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="L9" t="n">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4177</v>
+        <v>2.8596</v>
       </c>
       <c r="N9" t="n">
-        <v>215</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8594</v>
+        <v>2.7886</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0883</v>
+        <v>1.0614</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6775</v>
+        <v>0.6646</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8594</v>
+        <v>2.7886</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4091</v>
+        <v>2.7517</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4503</v>
+        <v>0.0369</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4091</v>
+        <v>3.8886</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4454</v>
+        <v>2.1833</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4503</v>
+        <v>0.0369</v>
       </c>
       <c r="K10" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L10" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8957</v>
+        <v>2.2202</v>
       </c>
       <c r="N10" t="n">
-        <v>274</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7888</v>
+        <v>2.7341</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0614</v>
+        <v>1.0406</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6453</v>
+        <v>0.6397</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7888</v>
+        <v>2.7341</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4762</v>
+        <v>1.4873</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3126</v>
+        <v>1.2468</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4762</v>
+        <v>1.4873</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4762</v>
+        <v>1.4873</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3126</v>
+        <v>1.2468</v>
       </c>
       <c r="K11" t="n">
         <v>104</v>
@@ -943,7 +943,7 @@
         <v>60</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7888</v>
+        <v>2.7341</v>
       </c>
       <c r="N11" t="n">
         <v>164</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3851</v>
+        <v>2.2458</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.8548</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4615</v>
+        <v>0.4173</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3851</v>
+        <v>2.2458</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6149</v>
+        <v>2.2458</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6149</v>
+        <v>2.2458</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6149</v>
+        <v>2.2458</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="L12" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3851</v>
+        <v>2.2458</v>
       </c>
       <c r="N12" t="n">
-        <v>330</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3806</v>
+        <v>2.2457</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9061</v>
+        <v>0.8547</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4595</v>
+        <v>0.4172</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3806</v>
+        <v>2.2457</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4292</v>
+        <v>1.2926</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9514</v>
+        <v>0.953</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4292</v>
+        <v>1.2926</v>
       </c>
       <c r="I13" t="n">
-        <v>1.466</v>
+        <v>1.3272</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9514</v>
+        <v>0.953</v>
       </c>
       <c r="K13" t="n">
         <v>130</v>
@@ -1035,7 +1035,7 @@
         <v>144</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4174</v>
+        <v>2.2802</v>
       </c>
       <c r="N13" t="n">
         <v>274</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3636</v>
+        <v>2.2114</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8996</v>
+        <v>0.8417</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4518</v>
+        <v>0.4016</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3636</v>
+        <v>2.2114</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3636</v>
+        <v>-0.6629</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.8743</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4483</v>
+        <v>-0.6629</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4483</v>
+        <v>-0.6629</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.8743</v>
       </c>
       <c r="K14" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4483</v>
+        <v>2.2114</v>
       </c>
       <c r="N14" t="n">
-        <v>133</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2357</v>
+        <v>2.1319</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8509</v>
+        <v>0.8114</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3935</v>
+        <v>0.3654</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2357</v>
+        <v>2.1319</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5401</v>
+        <v>0.494</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6956</v>
+        <v>1.6379</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5401</v>
+        <v>0.494</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5401</v>
+        <v>0.494</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6956</v>
+        <v>1.6379</v>
       </c>
       <c r="K15" t="n">
         <v>114</v>
@@ -1127,7 +1127,7 @@
         <v>216</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2357</v>
+        <v>2.1319</v>
       </c>
       <c r="N15" t="n">
         <v>330</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9513</v>
+        <v>1.8621</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7427</v>
+        <v>0.7087</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2641</v>
+        <v>0.2425</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9513</v>
+        <v>1.8621</v>
       </c>
       <c r="F16" t="n">
-        <v>1.697</v>
+        <v>1.9849</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2543</v>
+        <v>-0.1228</v>
       </c>
       <c r="H16" t="n">
-        <v>1.697</v>
+        <v>1.9849</v>
       </c>
       <c r="I16" t="n">
-        <v>1.697</v>
+        <v>2.0379</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2543</v>
+        <v>-0.1228</v>
       </c>
       <c r="K16" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9513</v>
+        <v>1.9151</v>
       </c>
       <c r="N16" t="n">
-        <v>187</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8843</v>
+        <v>1.7876</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6804</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2336</v>
+        <v>0.2085</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8843</v>
+        <v>1.7876</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7956</v>
+        <v>1.5747</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0887</v>
+        <v>0.2128</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7956</v>
+        <v>1.5747</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9696</v>
+        <v>1.5747</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0887</v>
+        <v>0.2128</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="L17" t="n">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0583</v>
+        <v>1.7875</v>
       </c>
       <c r="N17" t="n">
-        <v>274</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8773</v>
+        <v>1.721</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7145</v>
+        <v>0.655</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2304</v>
+        <v>0.1782</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8773</v>
+        <v>1.721</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0011</v>
+        <v>1.2661</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1238</v>
+        <v>0.4549</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0011</v>
+        <v>1.2661</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0527</v>
+        <v>1.2661</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1238</v>
+        <v>0.4549</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L18" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9289</v>
+        <v>1.721</v>
       </c>
       <c r="N18" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8757</v>
+        <v>1.6462</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7139</v>
+        <v>0.6266</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2297</v>
+        <v>0.1441</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8757</v>
+        <v>1.6462</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8757</v>
+        <v>1.6462</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8757</v>
+        <v>1.6462</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8757</v>
+        <v>1.6462</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8757</v>
+        <v>1.6462</v>
       </c>
       <c r="N19" t="n">
         <v>119</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8127</v>
+        <v>1.6031</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6899</v>
+        <v>0.6102</v>
       </c>
       <c r="D20" t="n">
-        <v>0.201</v>
+        <v>0.1245</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8127</v>
+        <v>1.6031</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3353</v>
+        <v>1.5919</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4774</v>
+        <v>0.0112</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3353</v>
+        <v>1.5919</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3353</v>
+        <v>0.8938</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4774</v>
+        <v>0.0112</v>
       </c>
       <c r="K20" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L20" t="n">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8127</v>
+        <v>0.905</v>
       </c>
       <c r="N20" t="n">
-        <v>164</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6882</v>
+        <v>1.5904</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6425</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1443</v>
+        <v>0.1187</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6882</v>
+        <v>1.5904</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0238</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7606</v>
+        <v>1.6142</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0238</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0743</v>
+        <v>-0.0244</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7606</v>
+        <v>1.6142</v>
       </c>
       <c r="K21" t="n">
         <v>130</v>
@@ -1403,7 +1403,7 @@
         <v>144</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6863</v>
+        <v>1.5898</v>
       </c>
       <c r="N21" t="n">
         <v>274</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5636</v>
+        <v>1.5749</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5951</v>
+        <v>0.5994</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0876</v>
+        <v>0.1117</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5636</v>
+        <v>1.5749</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3258</v>
+        <v>2.3233</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7622</v>
+        <v>-0.7484</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3655</v>
+        <v>2.3743</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3655</v>
+        <v>2.3743</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7622</v>
+        <v>-0.7484</v>
       </c>
       <c r="K22" t="n">
         <v>104</v>
@@ -1449,7 +1449,7 @@
         <v>60</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6033</v>
+        <v>1.6259</v>
       </c>
       <c r="N22" t="n">
         <v>164</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3657</v>
+        <v>1.3585</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5198</v>
+        <v>0.5171</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0025</v>
+        <v>0.0131</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3657</v>
+        <v>1.3585</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3657</v>
+        <v>1.492</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.1335</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3657</v>
+        <v>1.492</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3657</v>
+        <v>1.492</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.1335</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3657</v>
+        <v>1.3585</v>
       </c>
       <c r="N23" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3255</v>
+        <v>1.2164</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.463</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0208</v>
+        <v>-0.0517</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3255</v>
+        <v>1.2164</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4771</v>
+        <v>1.2164</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1516</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4771</v>
+        <v>1.2164</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4771</v>
+        <v>1.2164</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1516</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3255</v>
+        <v>1.2164</v>
       </c>
       <c r="N24" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5906</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2212</v>
+        <v>0.2248</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3597</v>
+        <v>-0.3367</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5906</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4118</v>
+        <v>0.4214</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1693</v>
+        <v>0.1692</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4118</v>
+        <v>0.4214</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4224</v>
+        <v>0.4327</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1693</v>
+        <v>0.1692</v>
       </c>
       <c r="K25" t="n">
         <v>130</v>
@@ -1587,7 +1587,7 @@
         <v>144</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5917</v>
+        <v>0.6019</v>
       </c>
       <c r="N25" t="n">
         <v>274</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.435</v>
+        <v>0.3605</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1656</v>
+        <v>0.1372</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4262</v>
+        <v>-0.4416</v>
       </c>
       <c r="E26" t="n">
-        <v>0.435</v>
+        <v>0.3605</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3764</v>
+        <v>0.3272</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0586</v>
+        <v>0.0333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3764</v>
+        <v>0.3272</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3764</v>
+        <v>0.3272</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0586</v>
+        <v>0.0333</v>
       </c>
       <c r="K26" t="n">
         <v>135</v>
@@ -1633,7 +1633,7 @@
         <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>0.435</v>
+        <v>0.3605</v>
       </c>
       <c r="N26" t="n">
         <v>187</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4341</v>
+        <v>0.3569</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1652</v>
+        <v>0.1358</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4266</v>
+        <v>-0.4432</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4341</v>
+        <v>0.3569</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1193</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3148</v>
+        <v>0.2733</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1193</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1193</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3148</v>
+        <v>0.2733</v>
       </c>
       <c r="K27" t="n">
         <v>135</v>
@@ -1679,7 +1679,7 @@
         <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4341</v>
+        <v>0.3569</v>
       </c>
       <c r="N27" t="n">
         <v>187</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0408</v>
+        <v>0.0368</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0155</v>
+        <v>0.014</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6056</v>
+        <v>-0.589</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0408</v>
+        <v>0.0368</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0408</v>
+        <v>0.0368</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0408</v>
+        <v>0.0368</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0408</v>
+        <v>0.0368</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0408</v>
+        <v>0.0368</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.31</v>
+        <v>-0.2282</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.118</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7653</v>
+        <v>-0.7097</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.31</v>
+        <v>-0.2282</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3029</v>
+        <v>0.352</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6129</v>
+        <v>-0.5802</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3029</v>
+        <v>0.352</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3029</v>
+        <v>0.352</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6129</v>
+        <v>-0.5802</v>
       </c>
       <c r="K29" t="n">
         <v>104</v>
@@ -1771,7 +1771,7 @@
         <v>60</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.31</v>
+        <v>-0.2282000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>164</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3405</v>
+        <v>-0.3278</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1296</v>
+        <v>-0.1248</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7792</v>
+        <v>-0.7551</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3405</v>
+        <v>-0.3278</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3405</v>
+        <v>-0.3278</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3405</v>
+        <v>-0.3278</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3405</v>
+        <v>-0.3278</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3405</v>
+        <v>-0.3278</v>
       </c>
       <c r="N30" t="n">
         <v>119</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.375</v>
+        <v>-0.4579</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1427</v>
+        <v>-0.1743</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.8144</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.375</v>
+        <v>-0.4579</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.375</v>
+        <v>-0.4579</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.375</v>
+        <v>-0.4579</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.375</v>
+        <v>-0.4579</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.375</v>
+        <v>-0.4579</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4534</v>
+        <v>-0.4829</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1726</v>
+        <v>-0.1838</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8306</v>
+        <v>-0.8258</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4534</v>
+        <v>-0.4829</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9378</v>
+        <v>-0.4829</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4844</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9378</v>
+        <v>-0.4829</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5064</v>
+        <v>-0.4829</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4844</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.02199999999999996</v>
+        <v>-0.4829</v>
       </c>
       <c r="N32" t="n">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4931</v>
+        <v>-0.5739</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1877</v>
+        <v>-0.2184</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8487</v>
+        <v>-0.8672</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4931</v>
+        <v>-0.5739</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4931</v>
+        <v>-0.9863</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.4124</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4931</v>
+        <v>-0.9863</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4931</v>
+        <v>-0.5538</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.4124</v>
       </c>
       <c r="K33" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4931</v>
+        <v>-0.1414</v>
       </c>
       <c r="N33" t="n">
-        <v>133</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8246</v>
+        <v>-0.8527</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3139</v>
+        <v>-0.3245</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9996</v>
+        <v>-0.9942</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8246</v>
+        <v>-0.8527</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8246</v>
+        <v>-0.8527</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8246</v>
+        <v>-0.8527</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8246</v>
+        <v>-0.8527</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8246</v>
+        <v>-0.8527</v>
       </c>
       <c r="N34" t="n">
         <v>119</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.97</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3692</v>
+        <v>-0.3666</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0658</v>
+        <v>-1.0446</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.97</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.97</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.97</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.97</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.97</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0472</v>
+        <v>-0.9671</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3986</v>
+        <v>-0.3681</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1009</v>
+        <v>-1.0463</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0472</v>
+        <v>-0.9671</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3618</v>
+        <v>-0.3108</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6854</v>
+        <v>-0.6563</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3618</v>
+        <v>-0.3108</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3618</v>
+        <v>-0.3108</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6854</v>
+        <v>-0.6563</v>
       </c>
       <c r="K36" t="n">
         <v>135</v>
@@ -2093,7 +2093,7 @@
         <v>52</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0472</v>
+        <v>-0.9671000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>187</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4377</v>
+        <v>-1.3699</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5472</v>
+        <v>-0.5214</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2787</v>
+        <v>-1.2298</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4377</v>
+        <v>-1.3699</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2405</v>
+        <v>-1.2037</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1972</v>
+        <v>-0.1662</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2405</v>
+        <v>-1.2037</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2405</v>
+        <v>-1.2037</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1972</v>
+        <v>-0.1662</v>
       </c>
       <c r="K37" t="n">
         <v>135</v>
@@ -2139,7 +2139,7 @@
         <v>52</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4377</v>
+        <v>-1.3699</v>
       </c>
       <c r="N37" t="n">
         <v>187</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4704</v>
+        <v>-1.462</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5597</v>
+        <v>-0.5565</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2936</v>
+        <v>-1.2718</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4704</v>
+        <v>-1.462</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9669</v>
+        <v>-0.9432</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.5188</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9669</v>
+        <v>-0.9432</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9669</v>
+        <v>-0.9432</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.5188</v>
       </c>
       <c r="K38" t="n">
         <v>114</v>
@@ -2185,7 +2185,7 @@
         <v>216</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4704</v>
+        <v>-1.462</v>
       </c>
       <c r="N38" t="n">
         <v>330</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5678</v>
+        <v>-1.5366</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5967</v>
+        <v>-0.5848</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3379</v>
+        <v>-1.3058</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5678</v>
+        <v>-1.5366</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5678</v>
+        <v>-1.5366</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5678</v>
+        <v>-1.5366</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5678</v>
+        <v>-1.5366</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5678</v>
+        <v>-1.5366</v>
       </c>
       <c r="N39" t="n">
         <v>133</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.2954</v>
+        <v>-2.8888</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.2543</v>
+        <v>-1.0995</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.1243</v>
+        <v>-1.9218</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.2954</v>
+        <v>-2.8888</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3008</v>
+        <v>-1.9399</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9946</v>
+        <v>-0.9489</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3008</v>
+        <v>-1.9399</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2424</v>
+        <v>-1.0892</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9946</v>
+        <v>-0.9489</v>
       </c>
       <c r="K40" t="n">
         <v>135</v>
@@ -2277,7 +2277,7 @@
         <v>80</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.237</v>
+        <v>-2.0381</v>
       </c>
       <c r="N40" t="n">
         <v>215</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8202</v>
+        <v>-3.6191</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.454</v>
+        <v>-1.3775</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3632</v>
+        <v>-2.2545</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8202</v>
+        <v>-3.6191</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8758</v>
+        <v>-1.7855</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.9444</v>
+        <v>-1.8336</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8758</v>
+        <v>-1.7855</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8758</v>
+        <v>-1.7855</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9444</v>
+        <v>-1.8336</v>
       </c>
       <c r="K41" t="n">
         <v>114</v>
@@ -2323,7 +2323,7 @@
         <v>216</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.8202</v>
+        <v>-3.6191</v>
       </c>
       <c r="N41" t="n">
         <v>330</v>
@@ -2429,10 +2429,10 @@
         <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9446</v>
+        <v>0.9319</v>
       </c>
       <c r="J2" t="n">
-        <v>23.615</v>
+        <v>23.2975</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.5954</v>
       </c>
       <c r="J3" t="n">
-        <v>15.6625</v>
+        <v>14.885</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5854</v>
+        <v>0.5532</v>
       </c>
       <c r="J4" t="n">
-        <v>14.635</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.19</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5211</v>
+        <v>0.4879</v>
       </c>
       <c r="J5" t="n">
-        <v>13.0275</v>
+        <v>12.1975</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2246</v>
+        <v>0.1953</v>
       </c>
       <c r="J6" t="n">
-        <v>5.615</v>
+        <v>4.8825</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.99</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0012</v>
+        <v>0.0059</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03</v>
+        <v>0.1475</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1284</v>
+        <v>-0.1134</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.21</v>
+        <v>-2.835</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.79</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2432</v>
+        <v>-0.2259</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.08</v>
+        <v>-5.6475</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.66</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3634</v>
+        <v>-0.3492</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.085000000000001</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3904</v>
+        <v>-0.3782</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.76</v>
+        <v>-9.455</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2526</v>
+        <v>0.2378</v>
       </c>
       <c r="J12" t="n">
-        <v>6.5676</v>
+        <v>6.1828</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1752</v>
+        <v>0.1578</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5552</v>
+        <v>4.1028</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0215</v>
+        <v>-0.016</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.416</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1307</v>
+        <v>-0.1127</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.3982</v>
+        <v>-2.9302</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4323</v>
+        <v>-0.4248</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.2398</v>
+        <v>-11.0448</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4513</v>
+        <v>0.3854</v>
       </c>
       <c r="J17" t="n">
-        <v>11.7338</v>
+        <v>10.0204</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.31</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4291</v>
+        <v>0.3645</v>
       </c>
       <c r="J18" t="n">
-        <v>11.1566</v>
+        <v>9.477</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4179</v>
+        <v>0.354</v>
       </c>
       <c r="J19" t="n">
-        <v>10.8654</v>
+        <v>9.204000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0185</v>
+        <v>0.0114</v>
       </c>
       <c r="J20" t="n">
-        <v>0.481</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.84</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2252</v>
+        <v>-0.2055</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.8552</v>
+        <v>-5.343</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.39</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9228</v>
+        <v>0.9086</v>
       </c>
       <c r="J22" t="n">
-        <v>23.07</v>
+        <v>22.715</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.28</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7065</v>
+        <v>0.6788</v>
       </c>
       <c r="J23" t="n">
-        <v>17.6625</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6253</v>
+        <v>0.5949</v>
       </c>
       <c r="J24" t="n">
-        <v>15.6325</v>
+        <v>14.8725</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5196</v>
+        <v>0.4869</v>
       </c>
       <c r="J25" t="n">
-        <v>12.99</v>
+        <v>12.1725</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2507</v>
+        <v>0.2202</v>
       </c>
       <c r="J26" t="n">
-        <v>6.2675</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.42</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7991</v>
       </c>
       <c r="J27" t="n">
-        <v>20.905</v>
+        <v>19.9775</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2643</v>
+        <v>0.2181</v>
       </c>
       <c r="J28" t="n">
-        <v>6.6075</v>
+        <v>5.4525</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3068</v>
+        <v>-0.2892</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.67</v>
+        <v>-7.23</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4161</v>
+        <v>-0.4063</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.4025</v>
+        <v>-10.1575</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.48</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5291</v>
+        <v>-0.5331</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.2275</v>
+        <v>-13.3275</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4828</v>
+        <v>0.4301</v>
       </c>
       <c r="J32" t="n">
-        <v>13.0356</v>
+        <v>11.6127</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4491</v>
+        <v>0.3881</v>
       </c>
       <c r="J33" t="n">
-        <v>12.1257</v>
+        <v>10.4787</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.375</v>
+        <v>0.3139</v>
       </c>
       <c r="J34" t="n">
-        <v>10.125</v>
+        <v>8.475300000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0633</v>
+        <v>0.0453</v>
       </c>
       <c r="J35" t="n">
-        <v>1.7091</v>
+        <v>1.2231</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3677</v>
+        <v>-0.356</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.927899999999999</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5161</v>
+        <v>0.546</v>
       </c>
       <c r="J37" t="n">
-        <v>13.9347</v>
+        <v>14.742</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.1</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1992</v>
+        <v>0.1824</v>
       </c>
       <c r="J38" t="n">
-        <v>5.3784</v>
+        <v>4.9248</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.05</v>
       </c>
       <c r="I39" t="n">
-        <v>0.117</v>
+        <v>0.101</v>
       </c>
       <c r="J39" t="n">
-        <v>3.159</v>
+        <v>2.727</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.83</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2213</v>
+        <v>-0.2008</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.9751</v>
+        <v>-5.4216</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4276</v>
+        <v>-0.4202</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.5452</v>
+        <v>-11.3454</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4789</v>
+        <v>0.4368</v>
       </c>
       <c r="J42" t="n">
-        <v>11.9725</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1877</v>
+        <v>0.1478</v>
       </c>
       <c r="J43" t="n">
-        <v>4.6925</v>
+        <v>3.695</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.224</v>
+        <v>-0.204</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.6</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2924</v>
+        <v>-0.274</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.31</v>
+        <v>-6.85</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.7</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3392</v>
+        <v>-0.3233</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.48</v>
+        <v>-8.0825</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9314</v>
+        <v>0.9174</v>
       </c>
       <c r="J47" t="n">
-        <v>23.285</v>
+        <v>22.935</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8904</v>
+        <v>0.8759</v>
       </c>
       <c r="J48" t="n">
-        <v>22.26</v>
+        <v>21.8975</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6344</v>
+        <v>0.625</v>
       </c>
       <c r="J49" t="n">
-        <v>15.86</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2467</v>
+        <v>0.2164</v>
       </c>
       <c r="J50" t="n">
-        <v>6.1675</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1037</v>
+        <v>-0.0834</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.5925</v>
+        <v>-2.085</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.73</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9954</v>
+        <v>0.9597</v>
       </c>
       <c r="J52" t="n">
-        <v>27.8712</v>
+        <v>26.8716</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3161</v>
+        <v>0.2656</v>
       </c>
       <c r="J53" t="n">
-        <v>8.8508</v>
+        <v>7.4368</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1861</v>
+        <v>-0.1655</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.2108</v>
+        <v>-4.634</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.83</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2282</v>
+        <v>-0.2079</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.3896</v>
+        <v>-5.8212</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.77</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2877</v>
+        <v>-0.2696</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.0556</v>
+        <v>-7.5488</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.49</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.956</v>
       </c>
       <c r="J57" t="n">
-        <v>27.1096</v>
+        <v>26.768</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.33</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7346</v>
+        <v>0.7186</v>
       </c>
       <c r="J58" t="n">
-        <v>20.5688</v>
+        <v>20.1208</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1552</v>
+        <v>0.1292</v>
       </c>
       <c r="J59" t="n">
-        <v>4.3456</v>
+        <v>3.6176</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.87</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.439</v>
+        <v>-0.3963</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.292</v>
+        <v>-11.0964</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6976</v>
+        <v>-0.666</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.5328</v>
+        <v>-18.648</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7644</v>
+        <v>0.7489</v>
       </c>
       <c r="J62" t="n">
-        <v>22.1676</v>
+        <v>21.7181</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5403</v>
+        <v>0.5283</v>
       </c>
       <c r="J63" t="n">
-        <v>15.6687</v>
+        <v>15.3207</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.06</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2236</v>
+        <v>0.189</v>
       </c>
       <c r="J64" t="n">
-        <v>6.4844</v>
+        <v>5.481</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5566</v>
       </c>
       <c r="J65" t="n">
-        <v>-17.2637</v>
+        <v>-16.1414</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6183</v>
+        <v>-0.5807</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.9307</v>
+        <v>-16.8403</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.43</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7039</v>
+        <v>0.6717</v>
       </c>
       <c r="J67" t="n">
-        <v>20.4131</v>
+        <v>19.4793</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.21</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4469</v>
+        <v>0.3936</v>
       </c>
       <c r="J68" t="n">
-        <v>12.9601</v>
+        <v>11.4144</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2115</v>
+        <v>-0.1909</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.1335</v>
+        <v>-5.5361</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2717</v>
+        <v>-0.2525</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.8793</v>
+        <v>-7.3225</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.72</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3288</v>
+        <v>-0.3126</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.5352</v>
+        <v>-9.0654</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.329</v>
+        <v>0.3203</v>
       </c>
       <c r="J72" t="n">
-        <v>8.882999999999999</v>
+        <v>8.648099999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.03</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0888</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>2.3976</v>
+        <v>1.9953</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.235</v>
+        <v>-0.215</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.345</v>
+        <v>-5.805</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2449</v>
+        <v>-0.225</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.6123</v>
+        <v>-6.075</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2645</v>
+        <v>-0.2451</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.1415</v>
+        <v>-6.6177</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7486</v>
+        <v>0.7009</v>
       </c>
       <c r="J77" t="n">
-        <v>20.2122</v>
+        <v>18.9243</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.27</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3779</v>
+        <v>0.3183</v>
       </c>
       <c r="J78" t="n">
-        <v>10.2033</v>
+        <v>8.594099999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2863</v>
+        <v>0.2357</v>
       </c>
       <c r="J79" t="n">
-        <v>7.7301</v>
+        <v>6.3639</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1392</v>
+        <v>0.1076</v>
       </c>
       <c r="J80" t="n">
-        <v>3.7584</v>
+        <v>2.9052</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2601</v>
+        <v>-0.2422</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.0227</v>
+        <v>-6.5394</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.41</v>
       </c>
       <c r="I82" t="n">
-        <v>0.858</v>
+        <v>0.8429</v>
       </c>
       <c r="J82" t="n">
-        <v>30.888</v>
+        <v>30.3444</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.26</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6299</v>
+        <v>0.616</v>
       </c>
       <c r="J83" t="n">
-        <v>22.6764</v>
+        <v>22.176</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2473</v>
+        <v>0.2132</v>
       </c>
       <c r="J84" t="n">
-        <v>8.902799999999999</v>
+        <v>7.6752</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.84</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5094</v>
+        <v>-0.4679</v>
       </c>
       <c r="J85" t="n">
-        <v>-18.3384</v>
+        <v>-16.8444</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5571</v>
+        <v>-0.5172</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.0556</v>
+        <v>-18.6192</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.26</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5102</v>
+        <v>0.4761</v>
       </c>
       <c r="J87" t="n">
-        <v>18.3672</v>
+        <v>17.1396</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.02</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0743</v>
+        <v>0.053</v>
       </c>
       <c r="J88" t="n">
-        <v>2.6748</v>
+        <v>1.908</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1347</v>
+        <v>-0.1157</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.8492</v>
+        <v>-4.1652</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.89</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1575</v>
+        <v>-0.1376</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.67</v>
+        <v>-4.9536</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.88</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1686</v>
+        <v>-0.1484</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.0696</v>
+        <v>-5.3424</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7884</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>28.3824</v>
+        <v>27.8172</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.303</v>
+        <v>0.2648</v>
       </c>
       <c r="J93" t="n">
-        <v>10.908</v>
+        <v>9.5328</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.08</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2762</v>
+        <v>0.2394</v>
       </c>
       <c r="J94" t="n">
-        <v>9.943199999999999</v>
+        <v>8.618399999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.99</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0494</v>
       </c>
       <c r="J95" t="n">
-        <v>-2.4696</v>
+        <v>-1.7784</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6231</v>
+        <v>-0.5861</v>
       </c>
       <c r="J96" t="n">
-        <v>-22.4316</v>
+        <v>-21.0996</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.53</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="J97" t="n">
-        <v>28.1052</v>
+        <v>26.748</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.51</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7602</v>
+        <v>0.7231</v>
       </c>
       <c r="J98" t="n">
-        <v>27.3672</v>
+        <v>26.0316</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0086</v>
+        <v>-0.0063</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.3096</v>
+        <v>-0.2268</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.85</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2121</v>
+        <v>-0.1919</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.6356</v>
+        <v>-6.9084</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.73</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3301</v>
+        <v>-0.3152</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.8836</v>
+        <v>-11.3472</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.44</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8693</v>
       </c>
       <c r="J102" t="n">
-        <v>21.2304</v>
+        <v>20.8632</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.21</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5385</v>
+        <v>0.529</v>
       </c>
       <c r="J103" t="n">
-        <v>12.924</v>
+        <v>12.696</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.393</v>
+        <v>0.3565</v>
       </c>
       <c r="J104" t="n">
-        <v>9.432</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0602</v>
       </c>
       <c r="J105" t="n">
-        <v>1.8432</v>
+        <v>1.4448</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2584</v>
+        <v>-0.2196</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.2016</v>
+        <v>-5.2704</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.24</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5319</v>
+        <v>0.5125</v>
       </c>
       <c r="J107" t="n">
-        <v>12.7656</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.89</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.143</v>
+        <v>-0.1272</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.432</v>
+        <v>-3.0528</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2828</v>
+        <v>-0.265</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.7872</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2828</v>
+        <v>-0.265</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.7872</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5501</v>
+        <v>-0.5565</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.2024</v>
+        <v>-13.356</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.34</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7612</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>22.836</v>
+        <v>22.365</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0665</v>
+        <v>-0.0478</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.995</v>
+        <v>-1.434</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.98</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1077</v>
+        <v>-0.0823</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.231</v>
+        <v>-2.469</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1441</v>
+        <v>-0.114</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.323</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.97</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1441</v>
+        <v>-0.114</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.323</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.3</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5485</v>
+        <v>0.5214</v>
       </c>
       <c r="J117" t="n">
-        <v>16.455</v>
+        <v>15.642</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.374</v>
+        <v>0.3192</v>
       </c>
       <c r="J118" t="n">
-        <v>11.22</v>
+        <v>9.576000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0277</v>
+        <v>-0.0196</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.831</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1021</v>
+        <v>-0.0847</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.063</v>
+        <v>-2.541</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2657</v>
+        <v>-0.2464</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.971</v>
+        <v>-7.392</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8724</v>
+        <v>0.8571</v>
       </c>
       <c r="J122" t="n">
-        <v>19.1928</v>
+        <v>18.8562</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.42</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8288</v>
       </c>
       <c r="J123" t="n">
-        <v>18.5746</v>
+        <v>18.2336</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.335</v>
+        <v>0.3018</v>
       </c>
       <c r="J124" t="n">
-        <v>7.37</v>
+        <v>6.6396</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.1</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3093</v>
+        <v>0.2766</v>
       </c>
       <c r="J125" t="n">
-        <v>6.8046</v>
+        <v>6.0852</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2064</v>
+        <v>-0.1721</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.5408</v>
+        <v>-3.7862</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.12</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3425</v>
+        <v>0.2948</v>
       </c>
       <c r="J127" t="n">
-        <v>7.535</v>
+        <v>6.4856</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0951</v>
+        <v>-0.0815</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.0922</v>
+        <v>-1.793</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1197</v>
+        <v>-0.1049</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.6334</v>
+        <v>-2.3078</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4197</v>
+        <v>-0.4099</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.2334</v>
+        <v>-9.017799999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4899</v>
+        <v>-0.4879</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.7778</v>
+        <v>-10.7338</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6071</v>
+        <v>0.5748</v>
       </c>
       <c r="J132" t="n">
-        <v>21.2485</v>
+        <v>20.118</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6071</v>
+        <v>0.5748</v>
       </c>
       <c r="J133" t="n">
-        <v>21.2485</v>
+        <v>20.118</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.23</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6071</v>
+        <v>0.5748</v>
       </c>
       <c r="J134" t="n">
-        <v>21.2485</v>
+        <v>20.118</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.21</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5654</v>
+        <v>0.5323</v>
       </c>
       <c r="J135" t="n">
-        <v>19.789</v>
+        <v>18.6305</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.16</v>
       </c>
       <c r="I136" t="n">
-        <v>0.4551</v>
+        <v>0.421</v>
       </c>
       <c r="J136" t="n">
-        <v>15.9285</v>
+        <v>14.735</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.98</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0318</v>
+        <v>-0.0244</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.113</v>
+        <v>-0.854</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.91</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1261</v>
+        <v>-0.1101</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.4135</v>
+        <v>-3.8535</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1486</v>
+        <v>-0.1314</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.201</v>
+        <v>-4.599</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1902</v>
+        <v>-0.1714</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.657</v>
+        <v>-5.999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3074</v>
+        <v>-0.2898</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.759</v>
+        <v>-10.143</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.8905</v>
       </c>
       <c r="J142" t="n">
-        <v>23.6028</v>
+        <v>23.153</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5611</v>
       </c>
       <c r="J143" t="n">
-        <v>15.5298</v>
+        <v>14.5886</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.17</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4863</v>
+        <v>0.4484</v>
       </c>
       <c r="J144" t="n">
-        <v>12.6438</v>
+        <v>11.6584</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0225</v>
+        <v>-0.0172</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.585</v>
+        <v>-0.4472</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2859</v>
+        <v>-0.2457</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.4334</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4386</v>
+        <v>0.381</v>
       </c>
       <c r="J147" t="n">
-        <v>11.4036</v>
+        <v>9.906000000000001</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1734</v>
+        <v>0.1354</v>
       </c>
       <c r="J148" t="n">
-        <v>4.5084</v>
+        <v>3.5204</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0975</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.535</v>
+        <v>-2.1086</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.87</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1784</v>
+        <v>-0.1581</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.6384</v>
+        <v>-4.1106</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.83</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2204</v>
+        <v>-0.1999</v>
       </c>
       <c r="J151" t="n">
-        <v>-5.7304</v>
+        <v>-5.1974</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4996</v>
       </c>
       <c r="J152" t="n">
-        <v>16.164</v>
+        <v>14.988</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5161</v>
+        <v>0.4765</v>
       </c>
       <c r="J153" t="n">
-        <v>15.483</v>
+        <v>14.295</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3741</v>
+        <v>0.3353</v>
       </c>
       <c r="J154" t="n">
-        <v>11.223</v>
+        <v>10.059</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.05</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1866</v>
+        <v>0.1577</v>
       </c>
       <c r="J155" t="n">
-        <v>5.598</v>
+        <v>4.731</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2186</v>
+        <v>-0.1816</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.558</v>
+        <v>-5.448</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5334</v>
+        <v>0.4741</v>
       </c>
       <c r="J157" t="n">
-        <v>16.002</v>
+        <v>14.223</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.2</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4337</v>
+        <v>0.3762</v>
       </c>
       <c r="J158" t="n">
-        <v>13.011</v>
+        <v>11.286</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1701</v>
+        <v>0.133</v>
       </c>
       <c r="J159" t="n">
-        <v>5.103</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1236</v>
+        <v>-0.1051</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.708</v>
+        <v>-3.153</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4719</v>
+        <v>-0.4698</v>
       </c>
       <c r="J161" t="n">
-        <v>-14.157</v>
+        <v>-14.094</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.428</v>
+        <v>0.4294</v>
       </c>
       <c r="J162" t="n">
-        <v>12.84</v>
+        <v>12.882</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1892</v>
+        <v>0.1721</v>
       </c>
       <c r="J163" t="n">
-        <v>5.676</v>
+        <v>5.163</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0226</v>
+        <v>-0.0167</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.678</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1761</v>
+        <v>-0.1561</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.283</v>
+        <v>-4.683</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4682</v>
+        <v>-0.465</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.046</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.48</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6242</v>
+        <v>0.5536</v>
       </c>
       <c r="J167" t="n">
-        <v>18.726</v>
+        <v>16.608</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.17</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2712</v>
+        <v>0.2192</v>
       </c>
       <c r="J168" t="n">
-        <v>8.135999999999999</v>
+        <v>6.576</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.14</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2324</v>
+        <v>0.1851</v>
       </c>
       <c r="J169" t="n">
-        <v>6.972</v>
+        <v>5.553</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1065</v>
+        <v>-0.0887</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.195</v>
+        <v>-2.661</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3276</v>
+        <v>-0.3122</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.827999999999999</v>
+        <v>-9.366</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.22</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6121</v>
+        <v>0.5743</v>
       </c>
       <c r="J172" t="n">
-        <v>18.363</v>
+        <v>17.229</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.17</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4985</v>
+        <v>0.4577</v>
       </c>
       <c r="J173" t="n">
-        <v>14.955</v>
+        <v>13.731</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.22</v>
+        <v>0.1874</v>
       </c>
       <c r="J174" t="n">
-        <v>6.6</v>
+        <v>5.622</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1818</v>
+        <v>-0.1478</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.454</v>
+        <v>-4.434</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.95</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2137</v>
+        <v>-0.177</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.411</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.47</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8535</v>
+        <v>0.8053</v>
       </c>
       <c r="J177" t="n">
-        <v>25.605</v>
+        <v>24.159</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0728</v>
+        <v>-0.0584</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.184</v>
+        <v>-1.752</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1118</v>
+        <v>-0.094</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.354</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.84</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2123</v>
+        <v>-0.1916</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.369</v>
+        <v>-5.748</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.82</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2327</v>
+        <v>-0.2124</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.981</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.93</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.0914</v>
+        <v>-0.0779</v>
       </c>
       <c r="J182" t="n">
-        <v>-2.1022</v>
+        <v>-1.7917</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.87</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1622</v>
+        <v>-0.1462</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.7306</v>
+        <v>-3.3626</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.84</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1942</v>
+        <v>-0.1776</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.4666</v>
+        <v>-4.0848</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.72</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3082</v>
+        <v>-0.2916</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.0886</v>
+        <v>-6.7068</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.6</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.417</v>
+        <v>-0.4069</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.590999999999999</v>
+        <v>-9.358700000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>2.33</v>
       </c>
       <c r="I187" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J187" t="n">
-        <v>44.5556</v>
+        <v>45.5814</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.33</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7964</v>
+        <v>0.7765</v>
       </c>
       <c r="J188" t="n">
-        <v>18.3172</v>
+        <v>17.8595</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.26</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6597</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>15.1731</v>
+        <v>14.5728</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.423</v>
+        <v>-0.3848</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.728999999999999</v>
+        <v>-8.8504</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8804</v>
+        <v>-0.8712</v>
       </c>
       <c r="J191" t="n">
-        <v>-20.2492</v>
+        <v>-20.0376</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.25</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3801</v>
+        <v>0.318</v>
       </c>
       <c r="J192" t="n">
-        <v>11.0229</v>
+        <v>9.222</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2932</v>
+        <v>0.238</v>
       </c>
       <c r="J193" t="n">
-        <v>8.502800000000001</v>
+        <v>6.902</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.95</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0878</v>
+        <v>-0.0717</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.5462</v>
+        <v>-2.0793</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0878</v>
+        <v>-0.0717</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.5462</v>
+        <v>-2.0793</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2741</v>
+        <v>-0.255</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.9489</v>
+        <v>-7.395</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.23</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3594</v>
+        <v>0.3533</v>
       </c>
       <c r="J197" t="n">
-        <v>10.4226</v>
+        <v>10.2457</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3085</v>
+        <v>0.2988</v>
       </c>
       <c r="J198" t="n">
-        <v>8.9465</v>
+        <v>8.6652</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.19</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3085</v>
+        <v>0.2988</v>
       </c>
       <c r="J199" t="n">
-        <v>8.9465</v>
+        <v>8.6652</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.11</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2005</v>
+        <v>0.1872</v>
       </c>
       <c r="J200" t="n">
-        <v>5.8145</v>
+        <v>5.4288</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.91</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.146</v>
+        <v>-0.1263</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.234</v>
+        <v>-3.6627</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2138</v>
+        <v>0.1713</v>
       </c>
       <c r="J202" t="n">
-        <v>6.2002</v>
+        <v>4.9677</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.03</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1192</v>
+        <v>0.0892</v>
       </c>
       <c r="J203" t="n">
-        <v>3.4568</v>
+        <v>2.5868</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.95</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0658</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.2823</v>
+        <v>-1.9082</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2022</v>
+        <v>-0.1827</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.8638</v>
+        <v>-5.2983</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4454</v>
+        <v>-0.4388</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.9166</v>
+        <v>-12.7252</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.53</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1523</v>
+        <v>1.1658</v>
       </c>
       <c r="J207" t="n">
-        <v>33.4167</v>
+        <v>33.8082</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.23</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6131</v>
+        <v>0.5788</v>
       </c>
       <c r="J208" t="n">
-        <v>17.7799</v>
+        <v>16.7852</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.13</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3902</v>
+        <v>0.3547</v>
       </c>
       <c r="J209" t="n">
-        <v>11.3158</v>
+        <v>10.2863</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0315</v>
+        <v>0.0216</v>
       </c>
       <c r="J210" t="n">
-        <v>0.9135</v>
+        <v>0.6264</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.95</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2319</v>
+        <v>-0.195</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.7251</v>
+        <v>-5.655</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.059</v>
+        <v>1.0667</v>
       </c>
       <c r="J212" t="n">
-        <v>30.711</v>
+        <v>30.9343</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.08</v>
       </c>
       <c r="I213" t="n">
-        <v>0.273</v>
+        <v>0.238</v>
       </c>
       <c r="J213" t="n">
-        <v>7.917</v>
+        <v>6.902</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.07</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2456</v>
+        <v>0.2122</v>
       </c>
       <c r="J214" t="n">
-        <v>7.1224</v>
+        <v>6.1538</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1522</v>
+        <v>-0.1211</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.4138</v>
+        <v>-3.5119</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.9</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3606</v>
+        <v>-0.318</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.4574</v>
+        <v>-9.222</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5827</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J217" t="n">
-        <v>16.8983</v>
+        <v>15.1873</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3827</v>
+        <v>0.3271</v>
       </c>
       <c r="J218" t="n">
-        <v>11.0983</v>
+        <v>9.485900000000001</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0987</v>
+        <v>-0.082</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.8623</v>
+        <v>-2.378</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1466</v>
+        <v>-0.127</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.2514</v>
+        <v>-3.683</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.68</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3656</v>
+        <v>-0.3522</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.6024</v>
+        <v>-10.2138</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.32</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8548</v>
+        <v>0.835</v>
       </c>
       <c r="J222" t="n">
-        <v>30.7728</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8122</v>
+        <v>0.7882</v>
       </c>
       <c r="J223" t="n">
-        <v>29.2392</v>
+        <v>28.3752</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.85</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4672</v>
+        <v>-0.4246</v>
       </c>
       <c r="J224" t="n">
-        <v>-16.8192</v>
+        <v>-15.2856</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.78</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6315</v>
+        <v>-0.5941</v>
       </c>
       <c r="J225" t="n">
-        <v>-22.734</v>
+        <v>-21.3876</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.786</v>
+        <v>-0.7593</v>
       </c>
       <c r="J226" t="n">
-        <v>-28.296</v>
+        <v>-27.3348</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7335</v>
+        <v>0.6758</v>
       </c>
       <c r="J227" t="n">
-        <v>26.406</v>
+        <v>24.3288</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.39</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7044</v>
+        <v>0.6459</v>
       </c>
       <c r="J228" t="n">
-        <v>25.3584</v>
+        <v>23.2524</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.18</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3785</v>
+        <v>0.3252</v>
       </c>
       <c r="J229" t="n">
-        <v>13.626</v>
+        <v>11.7072</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.85</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2114</v>
+        <v>-0.1912</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.6104</v>
+        <v>-6.8832</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3107</v>
+        <v>-0.2944</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.1852</v>
+        <v>-10.5984</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.58</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1755</v>
+        <v>1.1912</v>
       </c>
       <c r="J232" t="n">
-        <v>24.6855</v>
+        <v>25.0152</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.53</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1109</v>
+        <v>1.1255</v>
       </c>
       <c r="J233" t="n">
-        <v>23.3289</v>
+        <v>23.6355</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.45</v>
       </c>
       <c r="I234" t="n">
-        <v>0.9998</v>
+        <v>1.0031</v>
       </c>
       <c r="J234" t="n">
-        <v>20.9958</v>
+        <v>21.0651</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.899</v>
+        <v>0.8905</v>
       </c>
       <c r="J235" t="n">
-        <v>18.879</v>
+        <v>18.7005</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.04</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1056</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>2.2176</v>
+        <v>1.6842</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>0.91</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1022</v>
+        <v>-0.0867</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.1462</v>
+        <v>-1.8207</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.87</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1498</v>
+        <v>-0.1341</v>
       </c>
       <c r="J238" t="n">
-        <v>-3.1458</v>
+        <v>-2.8161</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.74</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2833</v>
+        <v>-0.2687</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.9493</v>
+        <v>-5.6427</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.63</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3811</v>
+        <v>-0.3689</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.0031</v>
+        <v>-7.7469</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.43</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5569</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.6949</v>
+        <v>-11.823</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1652</v>
+        <v>1.1791</v>
       </c>
       <c r="J242" t="n">
-        <v>25.6344</v>
+        <v>25.9402</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>0.9813</v>
+        <v>0.9777</v>
       </c>
       <c r="J243" t="n">
-        <v>21.5886</v>
+        <v>21.5094</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.28</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7</v>
+        <v>0.6754</v>
       </c>
       <c r="J244" t="n">
-        <v>15.4</v>
+        <v>14.8588</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.24</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5908</v>
       </c>
       <c r="J245" t="n">
-        <v>13.6048</v>
+        <v>12.9976</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.99</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1103</v>
+        <v>-0.0906</v>
       </c>
       <c r="J246" t="n">
-        <v>-2.4266</v>
+        <v>-1.9932</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.3</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7205</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>15.851</v>
+        <v>15.3362</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.71</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3107</v>
+        <v>-0.2959</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.8354</v>
+        <v>-6.5098</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.59</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.418</v>
+        <v>-0.4081</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.196</v>
+        <v>-8.978199999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.58</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4269</v>
+        <v>-0.4177</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.3918</v>
+        <v>-9.189399999999999</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5407</v>
+        <v>-0.5446</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.8954</v>
+        <v>-11.9812</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.88</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5431</v>
+        <v>1.5777</v>
       </c>
       <c r="J252" t="n">
-        <v>35.4913</v>
+        <v>36.2871</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.58</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1724</v>
+        <v>1.1886</v>
       </c>
       <c r="J253" t="n">
-        <v>26.9652</v>
+        <v>27.3378</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.49</v>
       </c>
       <c r="I254" t="n">
-        <v>1.0555</v>
+        <v>1.0671</v>
       </c>
       <c r="J254" t="n">
-        <v>24.2765</v>
+        <v>24.5433</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.12</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3266</v>
+        <v>0.2941</v>
       </c>
       <c r="J255" t="n">
-        <v>7.5118</v>
+        <v>6.7643</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>1.03</v>
       </c>
       <c r="I256" t="n">
-        <v>0.0687</v>
+        <v>0.0456</v>
       </c>
       <c r="J256" t="n">
-        <v>1.5801</v>
+        <v>1.0488</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>0.79</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.2284</v>
+        <v>-0.2137</v>
       </c>
       <c r="J257" t="n">
-        <v>-5.2532</v>
+        <v>-4.9151</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.68</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.333</v>
+        <v>-0.3205</v>
       </c>
       <c r="J258" t="n">
-        <v>-7.659</v>
+        <v>-7.3715</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.66</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.35</v>
+        <v>-0.3377</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.7671</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.65</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3587</v>
+        <v>-0.3466</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.2501</v>
+        <v>-7.9718</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4027</v>
+        <v>-0.3924</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.2621</v>
+        <v>-9.0252</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0797</v>
+        <v>1.0895</v>
       </c>
       <c r="J262" t="n">
-        <v>23.7534</v>
+        <v>23.969</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9727</v>
+        <v>0.9663</v>
       </c>
       <c r="J263" t="n">
-        <v>21.3994</v>
+        <v>21.2586</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.29</v>
       </c>
       <c r="I264" t="n">
-        <v>0.724</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J264" t="n">
-        <v>15.928</v>
+        <v>15.3582</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.05</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1603</v>
+        <v>0.1344</v>
       </c>
       <c r="J265" t="n">
-        <v>3.5266</v>
+        <v>2.9568</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.02</v>
       </c>
       <c r="I266" t="n">
-        <v>0.0584</v>
+        <v>0.0421</v>
       </c>
       <c r="J266" t="n">
-        <v>1.2848</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.23</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4995</v>
+        <v>0.4418</v>
       </c>
       <c r="J267" t="n">
-        <v>10.989</v>
+        <v>9.7196</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.06</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1802</v>
+        <v>0.141</v>
       </c>
       <c r="J268" t="n">
-        <v>3.9644</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1192</v>
+        <v>-0.1019</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.6224</v>
+        <v>-2.2418</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2372</v>
+        <v>-0.2171</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.2184</v>
+        <v>-4.7762</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.7</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3425</v>
+        <v>-0.327</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.535</v>
+        <v>-7.194</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.25</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6731</v>
+        <v>0.6384</v>
       </c>
       <c r="J272" t="n">
-        <v>18.1737</v>
+        <v>17.2368</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6077</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="J273" t="n">
-        <v>16.4079</v>
+        <v>15.3927</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2997</v>
+        <v>0.2631</v>
       </c>
       <c r="J274" t="n">
-        <v>8.091900000000001</v>
+        <v>7.1037</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1879</v>
+        <v>0.1586</v>
       </c>
       <c r="J275" t="n">
-        <v>5.0733</v>
+        <v>4.2822</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5114</v>
+        <v>-0.4701</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.8078</v>
+        <v>-12.6927</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.5192</v>
+        <v>0.4602</v>
       </c>
       <c r="J277" t="n">
-        <v>14.0184</v>
+        <v>12.4254</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.25</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5192</v>
+        <v>0.4602</v>
       </c>
       <c r="J278" t="n">
-        <v>14.0184</v>
+        <v>12.4254</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.02</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0743</v>
+        <v>0.053</v>
       </c>
       <c r="J279" t="n">
-        <v>2.0061</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.3085</v>
+        <v>-1.8873</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.49</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5308</v>
+        <v>-0.5367</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.3316</v>
+        <v>-14.4909</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.41</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9991</v>
+        <v>0.9966</v>
       </c>
       <c r="J282" t="n">
-        <v>26.9757</v>
+        <v>26.9082</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.15</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4497</v>
+        <v>0.409</v>
       </c>
       <c r="J283" t="n">
-        <v>12.1419</v>
+        <v>11.043</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.09</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3006</v>
+        <v>0.2635</v>
       </c>
       <c r="J284" t="n">
-        <v>8.116199999999999</v>
+        <v>7.1145</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.88</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4101</v>
+        <v>-0.3671</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.0727</v>
+        <v>-9.9117</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.87</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4355</v>
+        <v>-0.3926</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.7585</v>
+        <v>-10.6002</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.09</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2403</v>
+        <v>0.1946</v>
       </c>
       <c r="J287" t="n">
-        <v>6.4881</v>
+        <v>5.2542</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1544</v>
+        <v>0.1188</v>
       </c>
       <c r="J288" t="n">
-        <v>4.1688</v>
+        <v>3.2076</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0043</v>
+        <v>0.0023</v>
       </c>
       <c r="J289" t="n">
-        <v>0.1161</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.92</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1204</v>
+        <v>-0.1027</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.2508</v>
+        <v>-2.7729</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.74</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3067</v>
+        <v>-0.289</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.280900000000001</v>
+        <v>-7.803</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.78</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.1984</v>
+        <v>-0.1769</v>
       </c>
       <c r="J292" t="n">
-        <v>-3.7696</v>
+        <v>-3.3611</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.57</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.4105</v>
+        <v>-0.4063</v>
       </c>
       <c r="J293" t="n">
-        <v>-7.7995</v>
+        <v>-7.7197</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.48</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4866</v>
+        <v>-0.485</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.2454</v>
+        <v>-9.215</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.43</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5306</v>
+        <v>-0.5324</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.0814</v>
+        <v>-10.1156</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.39</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5662</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.7578</v>
+        <v>-10.8699</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.26</v>
       </c>
       <c r="I297" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J297" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.8</v>
       </c>
       <c r="I298" t="n">
-        <v>1.4207</v>
+        <v>1.4492</v>
       </c>
       <c r="J298" t="n">
-        <v>26.9933</v>
+        <v>27.5348</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.34</v>
       </c>
       <c r="I299" t="n">
-        <v>0.7812</v>
+        <v>0.7698</v>
       </c>
       <c r="J299" t="n">
-        <v>14.8428</v>
+        <v>14.6262</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.3</v>
       </c>
       <c r="I300" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.6848</v>
       </c>
       <c r="J300" t="n">
-        <v>13.3399</v>
+        <v>13.0112</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.22</v>
       </c>
       <c r="I301" t="n">
-        <v>0.5354</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>10.1726</v>
+        <v>9.644399999999999</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.16</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3667</v>
+        <v>0.3119</v>
       </c>
       <c r="J302" t="n">
-        <v>11.001</v>
+        <v>9.356999999999999</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2742</v>
+        <v>0.2256</v>
       </c>
       <c r="J303" t="n">
-        <v>8.226000000000001</v>
+        <v>6.768</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1936</v>
+        <v>0.1532</v>
       </c>
       <c r="J304" t="n">
-        <v>5.808</v>
+        <v>4.596</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.87</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1791</v>
+        <v>-0.1587</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.373</v>
+        <v>-4.761</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.73</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3187</v>
+        <v>-0.3019</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.561</v>
+        <v>-9.057</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.33</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8406</v>
+        <v>0.8172</v>
       </c>
       <c r="J307" t="n">
-        <v>25.218</v>
+        <v>24.516</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.07</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2458</v>
+        <v>0.2124</v>
       </c>
       <c r="J308" t="n">
-        <v>7.374</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.05</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1875</v>
+        <v>0.1584</v>
       </c>
       <c r="J309" t="n">
-        <v>5.625</v>
+        <v>4.752</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.04</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1562</v>
+        <v>0.1299</v>
       </c>
       <c r="J310" t="n">
-        <v>4.686</v>
+        <v>3.897</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.97</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1518</v>
+        <v>-0.1208</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.554</v>
+        <v>-3.624</v>
       </c>
     </row>
   </sheetData>
